--- a/Planejamento Previsto.xlsx
+++ b/Planejamento Previsto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Viana e Moura\Downloads\Planejamento Emissário - LD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8220EF3-7CC8-483E-AF06-A6444AE33F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7169FE3A-BEAA-4ECC-AC5E-4DA9379B3AE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EEA59E8E-9647-43AC-97C3-E8656E227CAD}"/>
   </bookViews>
@@ -197,7 +197,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -283,11 +283,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -367,6 +378,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -986,7 +998,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="26">
-        <f>SUM(I4:U4)</f>
+        <f>SUM(I4:V4)</f>
         <v>800</v>
       </c>
       <c r="D4" s="21">
@@ -1025,7 +1037,7 @@
         <v>0</v>
       </c>
       <c r="Q4" s="2">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R4" s="2">
         <v>100</v>
@@ -1037,9 +1049,11 @@
         <v>100</v>
       </c>
       <c r="U4" s="2">
+        <v>100</v>
+      </c>
+      <c r="V4" s="2">
         <v>66</v>
       </c>
-      <c r="V4" s="2"/>
       <c r="W4" s="13"/>
       <c r="X4" s="13"/>
       <c r="Y4" s="13"/>
@@ -1340,7 +1354,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="26">
-        <f>SUM(L8:Z8)</f>
+        <f>SUM(L8:Y8)</f>
         <v>422</v>
       </c>
       <c r="D8" s="21">
@@ -1375,7 +1389,7 @@
         <v>20</v>
       </c>
       <c r="Q8" s="2">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="R8" s="2">
         <v>30</v>
@@ -1389,7 +1403,9 @@
       <c r="U8" s="2">
         <v>30</v>
       </c>
-      <c r="V8" s="2"/>
+      <c r="V8" s="2">
+        <v>30</v>
+      </c>
       <c r="W8" s="2">
         <v>30</v>
       </c>
@@ -1397,10 +1413,7 @@
         <v>30</v>
       </c>
       <c r="Y8" s="2">
-        <v>30</v>
-      </c>
-      <c r="Z8" s="2">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AA8" s="13"/>
       <c r="AB8" s="13"/>
@@ -1526,7 +1539,7 @@
       </c>
       <c r="C10" s="26">
         <f>SUM(M10:Z10)</f>
-        <v>63.29999999999999</v>
+        <v>63.3</v>
       </c>
       <c r="D10" s="21">
         <v>46084</v>
@@ -1558,7 +1571,7 @@
         <v>5</v>
       </c>
       <c r="Q10" s="3">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="R10" s="3">
         <v>4.8</v>
@@ -1572,18 +1585,20 @@
       <c r="U10" s="3">
         <v>4.8</v>
       </c>
-      <c r="V10" s="3"/>
+      <c r="V10" s="3">
+        <v>4.8</v>
+      </c>
       <c r="W10" s="3">
         <v>4.8</v>
       </c>
       <c r="X10" s="3">
-        <v>4.8</v>
+        <v>4.57</v>
       </c>
       <c r="Y10" s="3">
-        <v>4.8</v>
-      </c>
-      <c r="Z10" s="3">
-        <v>5.0999999999999996</v>
+        <v>4.57</v>
+      </c>
+      <c r="Z10" s="31">
+        <v>4.5599999999999996</v>
       </c>
       <c r="AA10" s="13"/>
       <c r="AB10" s="13"/>
@@ -1709,7 +1724,7 @@
       </c>
       <c r="C12" s="26">
         <f>SUM(N12:AA12)</f>
-        <v>63.199999999999989</v>
+        <v>63.29999999999999</v>
       </c>
       <c r="D12" s="21">
         <v>46085</v>
@@ -1739,7 +1754,7 @@
         <v>5</v>
       </c>
       <c r="Q12" s="3">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="R12" s="3">
         <v>4.8</v>
@@ -1753,7 +1768,9 @@
       <c r="U12" s="3">
         <v>4.8</v>
       </c>
-      <c r="V12" s="3"/>
+      <c r="V12" s="3">
+        <v>4.8</v>
+      </c>
       <c r="W12" s="3">
         <v>4.8</v>
       </c>
@@ -1764,12 +1781,12 @@
         <v>4.8</v>
       </c>
       <c r="Z12" s="3">
-        <v>4.8</v>
+        <v>4.57</v>
       </c>
       <c r="AA12" s="3">
-        <v>5</v>
-      </c>
-      <c r="AB12" s="3"/>
+        <v>4.33</v>
+      </c>
+      <c r="AB12" s="13"/>
       <c r="AC12" s="13"/>
       <c r="AD12" s="13"/>
       <c r="AE12" s="13"/>
@@ -1891,7 +1908,7 @@
         <v>1</v>
       </c>
       <c r="C14" s="26">
-        <f>SUM(L14:AA14)</f>
+        <f>SUM(L14:AB14)</f>
         <v>399.99999999999994</v>
       </c>
       <c r="D14" s="21">
@@ -1926,37 +1943,41 @@
         <v>6</v>
       </c>
       <c r="Q14" s="3">
-        <v>30.7</v>
+        <v>6</v>
       </c>
       <c r="R14" s="3">
-        <v>30.7</v>
+        <v>28.2</v>
       </c>
       <c r="S14" s="3">
-        <v>30.7</v>
+        <v>28.2</v>
       </c>
       <c r="T14" s="3">
-        <v>30.7</v>
+        <v>28.2</v>
       </c>
       <c r="U14" s="3">
-        <v>30.7</v>
-      </c>
-      <c r="V14" s="3"/>
+        <v>28.2</v>
+      </c>
+      <c r="V14" s="3">
+        <v>28.2</v>
+      </c>
       <c r="W14" s="3">
-        <v>30.7</v>
+        <v>28.2</v>
       </c>
       <c r="X14" s="3">
-        <v>30.7</v>
+        <v>28.2</v>
       </c>
       <c r="Y14" s="3">
-        <v>30.7</v>
+        <v>28.2</v>
       </c>
       <c r="Z14" s="3">
-        <v>30.7</v>
+        <v>28.2</v>
       </c>
       <c r="AA14" s="3">
-        <v>39.700000000000003</v>
-      </c>
-      <c r="AB14" s="3"/>
+        <v>28.2</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>28</v>
+      </c>
       <c r="AC14" s="13"/>
       <c r="AD14" s="13"/>
       <c r="AE14" s="13"/>
@@ -2078,8 +2099,8 @@
         <v>1</v>
       </c>
       <c r="C16" s="26">
-        <f>SUM(L16:AA16)</f>
-        <v>400</v>
+        <f>SUM(L16:AB16)</f>
+        <v>399.99999999999994</v>
       </c>
       <c r="D16" s="21">
         <v>46085</v>
@@ -2113,37 +2134,41 @@
         <v>6</v>
       </c>
       <c r="Q16" s="3">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="R16" s="3">
-        <v>30</v>
+        <v>28.2</v>
       </c>
       <c r="S16" s="3">
-        <v>30</v>
+        <v>28.2</v>
       </c>
       <c r="T16" s="3">
-        <v>30</v>
+        <v>28.2</v>
       </c>
       <c r="U16" s="3">
-        <v>30</v>
-      </c>
-      <c r="V16" s="3"/>
+        <v>28.2</v>
+      </c>
+      <c r="V16" s="3">
+        <v>28.2</v>
+      </c>
       <c r="W16" s="3">
-        <v>30</v>
+        <v>28.2</v>
       </c>
       <c r="X16" s="3">
-        <v>30</v>
+        <v>28.2</v>
       </c>
       <c r="Y16" s="3">
-        <v>30</v>
+        <v>28.2</v>
       </c>
       <c r="Z16" s="3">
-        <v>36</v>
+        <v>28.2</v>
       </c>
       <c r="AA16" s="3">
-        <v>40</v>
-      </c>
-      <c r="AB16" s="3"/>
+        <v>28.2</v>
+      </c>
+      <c r="AB16" s="3">
+        <v>28</v>
+      </c>
       <c r="AC16" s="13"/>
       <c r="AD16" s="13"/>
       <c r="AE16" s="13"/>
@@ -2265,8 +2290,8 @@
         <v>1</v>
       </c>
       <c r="C18" s="26">
-        <f>SUM(P18:Y18)</f>
-        <v>4</v>
+        <f>SUM(P18:AB18)</f>
+        <v>5</v>
       </c>
       <c r="D18" s="21">
         <v>46090</v>
@@ -2307,10 +2332,10 @@
       </c>
       <c r="Y18" s="3"/>
       <c r="Z18" s="3"/>
-      <c r="AA18" s="3">
+      <c r="AA18" s="3"/>
+      <c r="AB18" s="3">
         <v>1</v>
       </c>
-      <c r="AB18" s="3"/>
       <c r="AC18" s="13"/>
       <c r="AD18" s="13"/>
       <c r="AE18" s="13"/>
@@ -2467,39 +2492,43 @@
         <v>6</v>
       </c>
       <c r="Q20" s="3">
-        <v>26.5</v>
+        <v>0</v>
       </c>
       <c r="R20" s="3">
-        <v>26.5</v>
+        <v>25.25</v>
       </c>
       <c r="S20" s="3">
-        <v>26.5</v>
+        <v>25.25</v>
       </c>
       <c r="T20" s="3">
-        <v>26.5</v>
+        <v>25.25</v>
       </c>
       <c r="U20" s="3">
-        <v>26.5</v>
-      </c>
-      <c r="V20" s="3"/>
+        <v>25.25</v>
+      </c>
+      <c r="V20" s="3">
+        <v>25.25</v>
+      </c>
       <c r="W20" s="3">
-        <v>26.5</v>
+        <v>25.25</v>
       </c>
       <c r="X20" s="3">
-        <v>26.5</v>
+        <v>25.25</v>
       </c>
       <c r="Y20" s="3">
-        <v>26.5</v>
+        <v>25.25</v>
       </c>
       <c r="Z20" s="3">
-        <v>26.5</v>
+        <v>25.25</v>
       </c>
       <c r="AA20" s="3">
-        <v>32.25</v>
-      </c>
-      <c r="AB20" s="3"/>
+        <v>25.25</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>25.25</v>
+      </c>
       <c r="AC20" s="3">
-        <v>32.25</v>
+        <v>25.25</v>
       </c>
       <c r="AD20" s="13"/>
       <c r="AE20" s="13"/>
@@ -2662,7 +2691,9 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-      <c r="V22" s="3"/>
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
       <c r="W22" s="3">
         <v>0</v>
       </c>
@@ -2986,17 +3017,19 @@
       <c r="Y26" s="13"/>
       <c r="Z26" s="13"/>
       <c r="AA26" s="5">
-        <v>100</v>
-      </c>
-      <c r="AB26" s="5"/>
+        <v>80</v>
+      </c>
+      <c r="AB26" s="5">
+        <v>80</v>
+      </c>
       <c r="AC26" s="5">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AD26" s="5">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AE26" s="5">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AF26" s="5">
         <v>76</v>
@@ -3137,17 +3170,19 @@
       <c r="Y28" s="13"/>
       <c r="Z28" s="13"/>
       <c r="AA28" s="5">
-        <v>100</v>
-      </c>
-      <c r="AB28" s="5"/>
+        <v>80</v>
+      </c>
+      <c r="AB28" s="5">
+        <v>80</v>
+      </c>
       <c r="AC28" s="5">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AD28" s="5">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AE28" s="5">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AF28" s="5">
         <v>76</v>
@@ -3253,7 +3288,7 @@
         <v>2</v>
       </c>
       <c r="C30" s="24">
-        <f>SUM(AA30:AF30,AH30:AK30)</f>
+        <f>SUM(AB30:AF30,AH30:AM30)</f>
         <v>285.60000000000002</v>
       </c>
       <c r="D30" s="21">
@@ -3287,39 +3322,43 @@
       <c r="X30" s="13"/>
       <c r="Y30" s="13"/>
       <c r="Z30" s="13"/>
-      <c r="AA30" s="5">
-        <v>32</v>
-      </c>
-      <c r="AB30" s="5"/>
+      <c r="AA30" s="13"/>
+      <c r="AB30" s="5">
+        <v>26</v>
+      </c>
       <c r="AC30" s="5">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AD30" s="5">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AE30" s="5">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AF30" s="5">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AG30" s="6" t="s">
         <v>21</v>
       </c>
       <c r="AH30" s="5">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AI30" s="5">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AJ30" s="5">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AK30" s="5">
-        <v>29.6</v>
-      </c>
-      <c r="AL30" s="13"/>
-      <c r="AM30" s="13"/>
+        <v>26</v>
+      </c>
+      <c r="AL30" s="5">
+        <v>26</v>
+      </c>
+      <c r="AM30" s="5">
+        <v>25.6</v>
+      </c>
       <c r="AN30" s="13"/>
       <c r="AO30" s="13"/>
       <c r="AP30" s="13"/>
@@ -3412,7 +3451,7 @@
         <v>2</v>
       </c>
       <c r="C32" s="24">
-        <f>SUM(AC32:AF32,AH32:AL32)</f>
+        <f>SUM(AC32:AF32,AH32:AN32)</f>
         <v>43.3</v>
       </c>
       <c r="D32" s="21">
@@ -3449,37 +3488,41 @@
       <c r="AA32" s="6"/>
       <c r="AB32" s="6"/>
       <c r="AC32" s="8">
-        <v>4.8099999999999996</v>
+        <v>3.94</v>
       </c>
       <c r="AD32" s="8">
-        <v>4.8099999999999996</v>
+        <v>3.94</v>
       </c>
       <c r="AE32" s="8">
-        <v>4.8099999999999996</v>
+        <v>3.94</v>
       </c>
       <c r="AF32" s="8">
-        <v>4.8099999999999996</v>
+        <v>3.94</v>
       </c>
       <c r="AG32" s="6" t="s">
         <v>21</v>
       </c>
       <c r="AH32" s="8">
-        <v>4.8099999999999996</v>
+        <v>3.94</v>
       </c>
       <c r="AI32" s="8">
-        <v>4.8099999999999996</v>
+        <v>3.94</v>
       </c>
       <c r="AJ32" s="8">
-        <v>4.8099999999999996</v>
+        <v>3.94</v>
       </c>
       <c r="AK32" s="8">
-        <v>4.8099999999999996</v>
+        <v>3.94</v>
       </c>
       <c r="AL32" s="8">
-        <v>4.82</v>
-      </c>
-      <c r="AM32" s="8"/>
-      <c r="AN32" s="13"/>
+        <v>3.94</v>
+      </c>
+      <c r="AM32" s="8">
+        <v>3.94</v>
+      </c>
+      <c r="AN32" s="8">
+        <v>3.9</v>
+      </c>
       <c r="AO32" s="13"/>
       <c r="AP32" s="13"/>
       <c r="AQ32" s="13"/>
@@ -3571,7 +3614,7 @@
         <v>2</v>
       </c>
       <c r="C34" s="24">
-        <f>SUM(AD34:AF34,AH34:AN34)</f>
+        <f>SUM(AD34:AF34,AH34:AO34)</f>
         <v>43.3</v>
       </c>
       <c r="D34" s="21">
@@ -3609,37 +3652,41 @@
       <c r="AB34" s="6"/>
       <c r="AC34" s="6"/>
       <c r="AD34" s="8">
-        <v>4.8099999999999996</v>
+        <v>3.94</v>
       </c>
       <c r="AE34" s="8">
-        <v>4.8099999999999996</v>
+        <v>3.94</v>
       </c>
       <c r="AF34" s="8">
-        <v>4.8099999999999996</v>
+        <v>3.94</v>
       </c>
       <c r="AG34" s="6" t="s">
         <v>21</v>
       </c>
       <c r="AH34" s="8">
-        <v>4.8099999999999996</v>
+        <v>3.94</v>
       </c>
       <c r="AI34" s="8">
-        <v>4.8099999999999996</v>
+        <v>3.94</v>
       </c>
       <c r="AJ34" s="8">
-        <v>4.8099999999999996</v>
+        <v>3.94</v>
       </c>
       <c r="AK34" s="8">
-        <v>4.8099999999999996</v>
+        <v>3.94</v>
       </c>
       <c r="AL34" s="8">
-        <v>4.8099999999999996</v>
-      </c>
-      <c r="AM34" s="8"/>
+        <v>3.94</v>
+      </c>
+      <c r="AM34" s="8">
+        <v>3.94</v>
+      </c>
       <c r="AN34" s="8">
-        <v>4.82</v>
-      </c>
-      <c r="AO34" s="13"/>
+        <v>3.94</v>
+      </c>
+      <c r="AO34" s="8">
+        <v>3.9</v>
+      </c>
       <c r="AP34" s="13"/>
       <c r="AQ34" s="13"/>
       <c r="AR34" s="13"/>
@@ -3730,8 +3777,8 @@
         <v>2</v>
       </c>
       <c r="C36" s="24">
-        <f>SUM(AD36:AF36,AH36:AN36)</f>
-        <v>238.00000000000003</v>
+        <f>SUM(AD36:AF36,AH36:AO36)</f>
+        <v>237.99999999999997</v>
       </c>
       <c r="D36" s="21">
         <v>46097</v>
@@ -3768,37 +3815,41 @@
       <c r="AB36" s="6"/>
       <c r="AC36" s="6"/>
       <c r="AD36" s="8">
-        <v>26.4</v>
+        <v>21.6</v>
       </c>
       <c r="AE36" s="8">
-        <v>26.4</v>
+        <v>21.6</v>
       </c>
       <c r="AF36" s="8">
-        <v>26.4</v>
+        <v>21.6</v>
       </c>
       <c r="AG36" s="6" t="s">
         <v>21</v>
       </c>
       <c r="AH36" s="8">
-        <v>26.4</v>
+        <v>21.6</v>
       </c>
       <c r="AI36" s="8">
-        <v>26.4</v>
+        <v>21.6</v>
       </c>
       <c r="AJ36" s="8">
-        <v>26.4</v>
+        <v>21.6</v>
       </c>
       <c r="AK36" s="8">
-        <v>26.4</v>
+        <v>21.6</v>
       </c>
       <c r="AL36" s="8">
-        <v>26.4</v>
-      </c>
-      <c r="AM36" s="8"/>
+        <v>21.6</v>
+      </c>
+      <c r="AM36" s="8">
+        <v>21.6</v>
+      </c>
       <c r="AN36" s="8">
-        <v>26.8</v>
-      </c>
-      <c r="AO36" s="13"/>
+        <v>21.6</v>
+      </c>
+      <c r="AO36" s="8">
+        <v>22</v>
+      </c>
       <c r="AP36" s="13"/>
       <c r="AQ36" s="13"/>
       <c r="AR36" s="13"/>
@@ -3889,8 +3940,8 @@
         <v>2</v>
       </c>
       <c r="C38" s="24">
-        <f>SUM(AD38:AF38,AH38:AN38)</f>
-        <v>238.00000000000003</v>
+        <f>SUM(AD38:AF38,AH38:AO38)</f>
+        <v>237.99999999999997</v>
       </c>
       <c r="D38" s="21">
         <v>46097</v>
@@ -3927,37 +3978,41 @@
       <c r="AB38" s="6"/>
       <c r="AC38" s="6"/>
       <c r="AD38" s="8">
-        <v>26.4</v>
+        <v>21.6</v>
       </c>
       <c r="AE38" s="8">
-        <v>26.4</v>
+        <v>21.6</v>
       </c>
       <c r="AF38" s="8">
-        <v>26.4</v>
+        <v>21.6</v>
       </c>
       <c r="AG38" s="6" t="s">
         <v>21</v>
       </c>
       <c r="AH38" s="8">
-        <v>26.4</v>
+        <v>21.6</v>
       </c>
       <c r="AI38" s="8">
-        <v>26.4</v>
+        <v>21.6</v>
       </c>
       <c r="AJ38" s="8">
-        <v>26.4</v>
+        <v>21.6</v>
       </c>
       <c r="AK38" s="8">
-        <v>26.4</v>
+        <v>21.6</v>
       </c>
       <c r="AL38" s="8">
-        <v>26.4</v>
-      </c>
-      <c r="AM38" s="8"/>
+        <v>21.6</v>
+      </c>
+      <c r="AM38" s="8">
+        <v>21.6</v>
+      </c>
       <c r="AN38" s="8">
-        <v>26.8</v>
-      </c>
-      <c r="AO38" s="13"/>
+        <v>21.6</v>
+      </c>
+      <c r="AO38" s="8">
+        <v>22</v>
+      </c>
       <c r="AP38" s="13"/>
       <c r="AQ38" s="13"/>
       <c r="AR38" s="13"/>
@@ -4048,7 +4103,7 @@
         <v>2</v>
       </c>
       <c r="C40" s="24">
-        <f>SUM(AF40,AH40:AN40)</f>
+        <f>SUM(AF40,AH40:AO40)</f>
         <v>3</v>
       </c>
       <c r="D40" s="21">
@@ -4094,17 +4149,17 @@
         <v>21</v>
       </c>
       <c r="AH40" s="8"/>
-      <c r="AI40" s="8">
+      <c r="AI40" s="8"/>
+      <c r="AJ40" s="8"/>
+      <c r="AK40" s="8">
         <v>1</v>
       </c>
-      <c r="AJ40" s="8"/>
-      <c r="AK40" s="8"/>
       <c r="AL40" s="8"/>
       <c r="AM40" s="8"/>
-      <c r="AN40" s="8">
+      <c r="AN40" s="8"/>
+      <c r="AO40" s="8">
         <v>1</v>
       </c>
-      <c r="AO40" s="13"/>
       <c r="AP40" s="13"/>
       <c r="AQ40" s="13"/>
       <c r="AR40" s="13"/>
@@ -4196,7 +4251,7 @@
       </c>
       <c r="C42" s="24">
         <f>SUM(AD42:AF42,AH42:AO42)</f>
-        <v>255.99999999999997</v>
+        <v>234.30000000000004</v>
       </c>
       <c r="D42" s="21">
         <v>46097</v>
@@ -4233,40 +4288,44 @@
       <c r="AB42" s="6"/>
       <c r="AC42" s="6"/>
       <c r="AD42" s="8">
-        <v>25.6</v>
+        <v>21.3</v>
       </c>
       <c r="AE42" s="8">
-        <v>25.6</v>
+        <v>21.3</v>
       </c>
       <c r="AF42" s="8">
-        <v>25.6</v>
+        <v>21.3</v>
       </c>
       <c r="AG42" s="6" t="s">
         <v>21</v>
       </c>
       <c r="AH42" s="8">
-        <v>25.6</v>
+        <v>21.3</v>
       </c>
       <c r="AI42" s="8">
-        <v>25.6</v>
+        <v>21.3</v>
       </c>
       <c r="AJ42" s="8">
-        <v>25.6</v>
+        <v>21.3</v>
       </c>
       <c r="AK42" s="8">
-        <v>25.6</v>
+        <v>21.3</v>
       </c>
       <c r="AL42" s="8">
-        <v>25.6</v>
-      </c>
-      <c r="AM42" s="8"/>
+        <v>21.3</v>
+      </c>
+      <c r="AM42" s="8">
+        <v>21.3</v>
+      </c>
       <c r="AN42" s="8">
-        <v>25.6</v>
+        <v>21.3</v>
       </c>
       <c r="AO42" s="8">
-        <v>25.6</v>
-      </c>
-      <c r="AP42" s="13"/>
+        <v>21.3</v>
+      </c>
+      <c r="AP42" s="8">
+        <v>21.7</v>
+      </c>
       <c r="AQ42" s="13"/>
       <c r="AR42" s="13"/>
       <c r="AS42" s="13"/>
@@ -4418,7 +4477,9 @@
       <c r="AL44" s="8">
         <v>0</v>
       </c>
-      <c r="AM44" s="8"/>
+      <c r="AM44" s="8">
+        <v>0</v>
+      </c>
       <c r="AN44" s="8">
         <v>0</v>
       </c>
@@ -4513,7 +4574,7 @@
         <v>2</v>
       </c>
       <c r="C46" s="24">
-        <f>SUM(AO46)</f>
+        <f>SUM(AQ46)</f>
         <v>476</v>
       </c>
       <c r="D46" s="21">
@@ -4563,11 +4624,10 @@
       <c r="AL46" s="6"/>
       <c r="AM46" s="6"/>
       <c r="AN46" s="6"/>
-      <c r="AO46" s="8">
+      <c r="AP46" s="6"/>
+      <c r="AQ46" s="8">
         <v>476</v>
       </c>
-      <c r="AP46" s="6"/>
-      <c r="AQ46" s="6"/>
       <c r="AR46" s="6"/>
       <c r="AS46" s="6"/>
       <c r="AT46" s="6" t="s">
@@ -4656,7 +4716,7 @@
         <v>3</v>
       </c>
       <c r="C48" s="19">
-        <f>SUM(AP48:AQ48)</f>
+        <f>SUM(AQ48:AR48)</f>
         <v>126</v>
       </c>
       <c r="D48" s="21">
@@ -4707,13 +4767,13 @@
       <c r="AM48" s="13"/>
       <c r="AN48" s="13"/>
       <c r="AO48" s="13"/>
-      <c r="AP48" s="7">
-        <v>100</v>
-      </c>
+      <c r="AP48" s="13"/>
       <c r="AQ48" s="7">
-        <v>26</v>
-      </c>
-      <c r="AR48" s="4"/>
+        <v>63</v>
+      </c>
+      <c r="AR48" s="7">
+        <v>63</v>
+      </c>
       <c r="AS48" s="4"/>
       <c r="AT48" s="6" t="s">
         <v>21</v>
@@ -4777,7 +4837,7 @@
       <c r="AM49" s="13"/>
       <c r="AN49" s="13"/>
       <c r="AO49" s="13"/>
-      <c r="AP49" s="4"/>
+      <c r="AP49" s="13"/>
       <c r="AQ49" s="4"/>
       <c r="AR49" s="4"/>
       <c r="AS49" s="4"/>
@@ -4801,7 +4861,7 @@
         <v>3</v>
       </c>
       <c r="C50" s="19">
-        <f>SUM(AP50:AQ50)</f>
+        <f>SUM(AQ50:AR50)</f>
         <v>126</v>
       </c>
       <c r="D50" s="21">
@@ -4852,13 +4912,13 @@
       <c r="AM50" s="13"/>
       <c r="AN50" s="13"/>
       <c r="AO50" s="13"/>
-      <c r="AP50" s="7">
-        <v>100</v>
-      </c>
+      <c r="AP50" s="13"/>
       <c r="AQ50" s="7">
-        <v>26</v>
-      </c>
-      <c r="AR50" s="4"/>
+        <v>63</v>
+      </c>
+      <c r="AR50" s="7">
+        <v>63</v>
+      </c>
       <c r="AS50" s="4"/>
       <c r="AT50" s="6" t="s">
         <v>21</v>
@@ -4922,7 +4982,7 @@
       <c r="AM51" s="13"/>
       <c r="AN51" s="13"/>
       <c r="AO51" s="13"/>
-      <c r="AP51" s="4"/>
+      <c r="AP51" s="13"/>
       <c r="AQ51" s="4"/>
       <c r="AR51" s="4"/>
       <c r="AS51" s="4"/>
@@ -4946,7 +5006,7 @@
         <v>3</v>
       </c>
       <c r="C52" s="19">
-        <f>SUM(AP52:AQ52)</f>
+        <f>SUM(AQ52:AS52)</f>
         <v>75.599999999999994</v>
       </c>
       <c r="D52" s="21">
@@ -4997,14 +5057,16 @@
       <c r="AM52" s="13"/>
       <c r="AN52" s="13"/>
       <c r="AO52" s="13"/>
-      <c r="AP52" s="7">
-        <v>50</v>
-      </c>
+      <c r="AP52" s="13"/>
       <c r="AQ52" s="7">
-        <v>25.6</v>
-      </c>
-      <c r="AR52" s="6"/>
-      <c r="AS52" s="6"/>
+        <v>25.2</v>
+      </c>
+      <c r="AR52" s="7">
+        <v>25.2</v>
+      </c>
+      <c r="AS52" s="7">
+        <v>25.2</v>
+      </c>
       <c r="AT52" s="6" t="s">
         <v>21</v>
       </c>
@@ -5067,7 +5129,7 @@
       <c r="AM53" s="13"/>
       <c r="AN53" s="13"/>
       <c r="AO53" s="13"/>
-      <c r="AP53" s="6"/>
+      <c r="AP53" s="13"/>
       <c r="AQ53" s="6"/>
       <c r="AR53" s="6"/>
       <c r="AS53" s="6"/>
@@ -5091,8 +5153,8 @@
         <v>3</v>
       </c>
       <c r="C54" s="19">
-        <f>SUM(AQ54:AR54)</f>
-        <v>11.4</v>
+        <f>SUM(AR54:AS54,AV54)</f>
+        <v>11.399999999999999</v>
       </c>
       <c r="D54" s="21">
         <v>46097</v>
@@ -5142,21 +5204,23 @@
       <c r="AM54" s="13"/>
       <c r="AN54" s="13"/>
       <c r="AO54" s="13"/>
-      <c r="AP54" s="9"/>
-      <c r="AQ54" s="7">
-        <v>5.7</v>
-      </c>
+      <c r="AP54" s="13"/>
+      <c r="AQ54" s="9"/>
       <c r="AR54" s="7">
-        <v>5.7</v>
-      </c>
-      <c r="AS54" s="7"/>
+        <v>3.8</v>
+      </c>
+      <c r="AS54" s="7">
+        <v>3.8</v>
+      </c>
       <c r="AT54" s="6" t="s">
         <v>21</v>
       </c>
       <c r="AU54" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AV54" s="6"/>
+      <c r="AV54" s="7">
+        <v>3.8</v>
+      </c>
       <c r="AW54" s="6"/>
       <c r="AX54" s="13"/>
       <c r="AY54" s="13"/>
@@ -5212,7 +5276,7 @@
       <c r="AM55" s="13"/>
       <c r="AN55" s="13"/>
       <c r="AO55" s="13"/>
-      <c r="AP55" s="6"/>
+      <c r="AP55" s="13"/>
       <c r="AQ55" s="6"/>
       <c r="AR55" s="6"/>
       <c r="AS55" s="6"/>
@@ -5236,8 +5300,8 @@
         <v>3</v>
       </c>
       <c r="C56" s="19">
-        <f>SUM(AV56,AR56)</f>
-        <v>11.4</v>
+        <f>SUM(AV56:AW56,AS56)</f>
+        <v>11.399999999999999</v>
       </c>
       <c r="D56" s="21">
         <v>46097</v>
@@ -5287,12 +5351,12 @@
       <c r="AM56" s="13"/>
       <c r="AN56" s="13"/>
       <c r="AO56" s="13"/>
-      <c r="AP56" s="9"/>
+      <c r="AP56" s="13"/>
       <c r="AQ56" s="9"/>
-      <c r="AR56" s="7">
-        <v>5.7</v>
-      </c>
-      <c r="AS56" s="7"/>
+      <c r="AR56" s="9"/>
+      <c r="AS56" s="7">
+        <v>3.8</v>
+      </c>
       <c r="AT56" s="6" t="s">
         <v>21</v>
       </c>
@@ -5300,9 +5364,11 @@
         <v>21</v>
       </c>
       <c r="AV56" s="7">
-        <v>5.7</v>
-      </c>
-      <c r="AW56" s="6"/>
+        <v>3.8</v>
+      </c>
+      <c r="AW56" s="7">
+        <v>3.8</v>
+      </c>
       <c r="AX56" s="13"/>
       <c r="AY56" s="13"/>
       <c r="AZ56" s="13"/>
@@ -5357,7 +5423,7 @@
       <c r="AM57" s="13"/>
       <c r="AN57" s="13"/>
       <c r="AO57" s="13"/>
-      <c r="AP57" s="6"/>
+      <c r="AP57" s="13"/>
       <c r="AQ57" s="6"/>
       <c r="AR57" s="6"/>
       <c r="AS57" s="6"/>
@@ -5381,7 +5447,7 @@
         <v>3</v>
       </c>
       <c r="C58" s="19">
-        <f>SUM(AV58,AR58)</f>
+        <f>SUM(AV58:AW58,AS58)</f>
         <v>63</v>
       </c>
       <c r="D58" s="21">
@@ -5432,12 +5498,12 @@
       <c r="AM58" s="13"/>
       <c r="AN58" s="13"/>
       <c r="AO58" s="13"/>
-      <c r="AP58" s="6"/>
+      <c r="AP58" s="13"/>
       <c r="AQ58" s="6"/>
-      <c r="AR58" s="10">
-        <v>40</v>
-      </c>
-      <c r="AS58" s="10"/>
+      <c r="AR58" s="6"/>
+      <c r="AS58" s="10">
+        <v>21</v>
+      </c>
       <c r="AT58" s="6" t="s">
         <v>21</v>
       </c>
@@ -5445,9 +5511,11 @@
         <v>21</v>
       </c>
       <c r="AV58" s="10">
-        <v>23</v>
-      </c>
-      <c r="AW58" s="6"/>
+        <v>21</v>
+      </c>
+      <c r="AW58" s="10">
+        <v>21</v>
+      </c>
       <c r="AX58" s="13"/>
       <c r="AY58" s="13"/>
       <c r="AZ58" s="13"/>
@@ -5502,7 +5570,7 @@
       <c r="AM59" s="13"/>
       <c r="AN59" s="13"/>
       <c r="AO59" s="13"/>
-      <c r="AP59" s="6"/>
+      <c r="AP59" s="13"/>
       <c r="AQ59" s="6"/>
       <c r="AR59" s="6"/>
       <c r="AS59" s="6"/>
@@ -5526,7 +5594,7 @@
         <v>3</v>
       </c>
       <c r="C60" s="19">
-        <f>SUM(AV60,AR60)</f>
+        <f>SUM(AV60:AW60,AS60)</f>
         <v>63</v>
       </c>
       <c r="D60" s="21">
@@ -5577,12 +5645,12 @@
       <c r="AM60" s="13"/>
       <c r="AN60" s="13"/>
       <c r="AO60" s="13"/>
-      <c r="AP60" s="6"/>
+      <c r="AP60" s="13"/>
       <c r="AQ60" s="6"/>
-      <c r="AR60" s="10">
-        <v>40</v>
-      </c>
-      <c r="AS60" s="10"/>
+      <c r="AR60" s="6"/>
+      <c r="AS60" s="10">
+        <v>21</v>
+      </c>
       <c r="AT60" s="6" t="s">
         <v>21</v>
       </c>
@@ -5590,9 +5658,11 @@
         <v>21</v>
       </c>
       <c r="AV60" s="10">
-        <v>23</v>
-      </c>
-      <c r="AW60" s="6"/>
+        <v>21</v>
+      </c>
+      <c r="AW60" s="10">
+        <v>21</v>
+      </c>
       <c r="AX60" s="13"/>
       <c r="AY60" s="13"/>
       <c r="AZ60" s="13"/>
@@ -5671,7 +5741,7 @@
         <v>3</v>
       </c>
       <c r="C62" s="19">
-        <f>SUM(AV62)</f>
+        <f>SUM(AW62)</f>
         <v>1</v>
       </c>
       <c r="D62" s="21">
@@ -5732,10 +5802,9 @@
       <c r="AU62" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AV62" s="10">
+      <c r="AW62" s="10">
         <v>1</v>
       </c>
-      <c r="AW62" s="6"/>
       <c r="AX62" s="13"/>
       <c r="AY62" s="13"/>
       <c r="AZ62" s="13"/>
@@ -5814,7 +5883,7 @@
         <v>3</v>
       </c>
       <c r="C64" s="19">
-        <f>SUM(AV64:AW64)</f>
+        <f>SUM(AV64:AX64)</f>
         <v>55</v>
       </c>
       <c r="D64" s="21">
@@ -5876,12 +5945,14 @@
         <v>21</v>
       </c>
       <c r="AV64" s="10">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="AW64" s="10">
-        <v>25</v>
-      </c>
-      <c r="AX64" s="13"/>
+        <v>18</v>
+      </c>
+      <c r="AX64" s="10">
+        <v>18</v>
+      </c>
       <c r="AY64" s="13"/>
       <c r="AZ64" s="13"/>
       <c r="BA64" s="13"/>

--- a/Planejamento Previsto.xlsx
+++ b/Planejamento Previsto.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Viana e Moura\Downloads\Planejamento Emissário - LD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7169FE3A-BEAA-4ECC-AC5E-4DA9379B3AE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{910CB5B8-F8E5-44B7-A170-28F454BD0672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EEA59E8E-9647-43AC-97C3-E8656E227CAD}"/>
   </bookViews>
   <sheets>
-    <sheet name="Plan" sheetId="2" r:id="rId1"/>
+    <sheet name="Plan" sheetId="3" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,18 +36,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="28">
   <si>
     <t>Escavação (m³)</t>
   </si>
   <si>
     <t>Desmonte de Rocha (m³)</t>
-  </si>
-  <si>
-    <t>Limpeza de desmonte (m³)</t>
-  </si>
-  <si>
-    <t>Regularização de vala (m)</t>
   </si>
   <si>
     <t xml:space="preserve"> Assentamento de tubulação (m)</t>
@@ -124,6 +118,9 @@
   <si>
     <t>INTERDIÇÃO</t>
   </si>
+  <si>
+    <t>Sondagem (und)</t>
+  </si>
 </sst>
 </file>
 
@@ -197,7 +194,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -283,22 +280,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -327,6 +313,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -336,7 +340,19 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -348,37 +364,6 @@
     <xf numFmtId="2" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -712,8 +697,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C54AB731-4767-43DA-A651-BBAA70A72A62}">
-  <dimension ref="A2:BL69"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59AFFE89-FF8E-4E1D-AC6B-9E2FFA7EFAAA}">
+  <dimension ref="A2:BL59"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34.21875" bestFit="1" customWidth="1"/>
@@ -732,7 +717,9 @@
     <col min="31" max="31" width="6.6640625" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="5.5546875" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="8.21875" bestFit="1" customWidth="1"/>
-    <col min="34" max="36" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="5.5546875" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="6.5546875" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="6.44140625" bestFit="1" customWidth="1"/>
     <col min="39" max="39" width="6.44140625" customWidth="1"/>
@@ -745,100 +732,100 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="28" t="s">
+      <c r="F2" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="28" t="s">
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" s="27" t="s">
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27" t="s">
+      <c r="R2" s="21"/>
+      <c r="S2" s="21"/>
+      <c r="T2" s="21"/>
+      <c r="U2" s="21"/>
+      <c r="V2" s="22"/>
+      <c r="W2" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="27"/>
-      <c r="P2" s="27"/>
-      <c r="Q2" s="14" t="s">
+      <c r="X2" s="21"/>
+      <c r="Y2" s="21"/>
+      <c r="Z2" s="21"/>
+      <c r="AA2" s="21"/>
+      <c r="AB2" s="22"/>
+      <c r="AC2" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
-      <c r="T2" s="15"/>
-      <c r="U2" s="15"/>
-      <c r="V2" s="16"/>
-      <c r="W2" s="14" t="s">
+      <c r="AD2" s="14"/>
+      <c r="AE2" s="14"/>
+      <c r="AF2" s="14"/>
+      <c r="AG2" s="14"/>
+      <c r="AH2" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="X2" s="15"/>
-      <c r="Y2" s="15"/>
-      <c r="Z2" s="15"/>
-      <c r="AA2" s="15"/>
-      <c r="AB2" s="16"/>
-      <c r="AC2" s="27" t="s">
+      <c r="AI2" s="21"/>
+      <c r="AJ2" s="21"/>
+      <c r="AK2" s="21"/>
+      <c r="AL2" s="21"/>
+      <c r="AM2" s="22"/>
+      <c r="AN2" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="AD2" s="27"/>
-      <c r="AE2" s="27"/>
-      <c r="AF2" s="27"/>
-      <c r="AG2" s="27"/>
-      <c r="AH2" s="14" t="s">
+      <c r="AO2" s="21"/>
+      <c r="AP2" s="21"/>
+      <c r="AQ2" s="21"/>
+      <c r="AR2" s="21"/>
+      <c r="AS2" s="22"/>
+      <c r="AT2" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="AI2" s="15"/>
-      <c r="AJ2" s="15"/>
-      <c r="AK2" s="15"/>
-      <c r="AL2" s="15"/>
-      <c r="AM2" s="16"/>
-      <c r="AN2" s="14" t="s">
+      <c r="AU2" s="21"/>
+      <c r="AV2" s="21"/>
+      <c r="AW2" s="21"/>
+      <c r="AX2" s="21"/>
+      <c r="AY2" s="22"/>
+      <c r="AZ2" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="AO2" s="15"/>
-      <c r="AP2" s="15"/>
-      <c r="AQ2" s="15"/>
-      <c r="AR2" s="15"/>
-      <c r="AS2" s="16"/>
-      <c r="AT2" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="AU2" s="15"/>
-      <c r="AV2" s="15"/>
-      <c r="AW2" s="15"/>
-      <c r="AX2" s="15"/>
-      <c r="AY2" s="16"/>
-      <c r="AZ2" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="BA2" s="27"/>
-      <c r="BB2" s="27"/>
-      <c r="BC2" s="27"/>
-      <c r="BD2" s="27"/>
+      <c r="BA2" s="14"/>
+      <c r="BB2" s="14"/>
+      <c r="BC2" s="14"/>
+      <c r="BD2" s="14"/>
     </row>
     <row r="3" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A3" s="28"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
+      <c r="A3" s="23"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
       <c r="G3" s="12">
         <v>46083</v>
       </c>
@@ -991,24 +978,24 @@
       </c>
     </row>
     <row r="4" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A4" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="25">
+      <c r="A4" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="16">
         <v>1</v>
       </c>
-      <c r="C4" s="26">
-        <f>SUM(I4:V4)</f>
+      <c r="C4" s="17">
+        <f>SUM(I4:AA4)</f>
         <v>800</v>
       </c>
-      <c r="D4" s="21">
+      <c r="D4" s="18">
         <v>46083</v>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="18">
         <v>46122</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G4" s="9"/>
       <c r="H4" s="9"/>
@@ -1019,7 +1006,7 @@
         <v>112</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L4" s="2">
         <v>68</v>
@@ -1040,32 +1027,42 @@
         <v>0</v>
       </c>
       <c r="R4" s="2">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="S4" s="2">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T4" s="2">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U4" s="2">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V4" s="2">
-        <v>66</v>
-      </c>
-      <c r="W4" s="13"/>
-      <c r="X4" s="13"/>
-      <c r="Y4" s="13"/>
-      <c r="Z4" s="13"/>
-      <c r="AA4" s="13"/>
+        <v>34</v>
+      </c>
+      <c r="W4" s="2">
+        <v>65</v>
+      </c>
+      <c r="X4" s="2">
+        <v>65</v>
+      </c>
+      <c r="Y4" s="2">
+        <v>65</v>
+      </c>
+      <c r="Z4" s="2">
+        <v>65</v>
+      </c>
+      <c r="AA4" s="2">
+        <v>65</v>
+      </c>
       <c r="AB4" s="13"/>
       <c r="AC4" s="13"/>
       <c r="AD4" s="13"/>
       <c r="AE4" s="13"/>
       <c r="AF4" s="13"/>
       <c r="AG4" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AH4" s="13"/>
       <c r="AI4" s="13"/>
@@ -1080,10 +1077,10 @@
       <c r="AR4" s="13"/>
       <c r="AS4" s="13"/>
       <c r="AT4" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU4" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AV4" s="4"/>
       <c r="AW4" s="4"/>
@@ -1094,7 +1091,7 @@
       <c r="BB4" s="4"/>
       <c r="BC4" s="4"/>
       <c r="BD4" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BE4" s="1"/>
       <c r="BF4" s="1"/>
@@ -1106,13 +1103,13 @@
       <c r="BL4" s="1"/>
     </row>
     <row r="5" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A5" s="17"/>
-      <c r="B5" s="25"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
+      <c r="A5" s="15"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
       <c r="F5" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
@@ -1174,24 +1171,24 @@
       <c r="BL5" s="1"/>
     </row>
     <row r="6" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="16">
+        <v>1</v>
+      </c>
+      <c r="C6" s="17">
+        <f>SUM(W6:AA6)</f>
+        <v>325</v>
+      </c>
+      <c r="D6" s="18">
+        <v>46083</v>
+      </c>
+      <c r="E6" s="18">
+        <v>46122</v>
+      </c>
+      <c r="F6" s="11" t="s">
         <v>22</v>
-      </c>
-      <c r="B6" s="25">
-        <v>1</v>
-      </c>
-      <c r="C6" s="26">
-        <f>I6+J6+L6+M6+N6+O6+P6+Q6</f>
-        <v>0</v>
-      </c>
-      <c r="D6" s="21">
-        <v>46083</v>
-      </c>
-      <c r="E6" s="21">
-        <v>46122</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>24</v>
       </c>
       <c r="G6" s="9"/>
       <c r="H6" s="9"/>
@@ -1202,7 +1199,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L6" s="2">
         <v>0</v>
@@ -1227,18 +1224,28 @@
       <c r="T6" s="4"/>
       <c r="U6" s="4"/>
       <c r="V6" s="4"/>
-      <c r="W6" s="13"/>
-      <c r="X6" s="13"/>
-      <c r="Y6" s="13"/>
-      <c r="Z6" s="13"/>
-      <c r="AA6" s="13"/>
+      <c r="W6" s="2">
+        <v>65</v>
+      </c>
+      <c r="X6" s="2">
+        <v>65</v>
+      </c>
+      <c r="Y6" s="2">
+        <v>65</v>
+      </c>
+      <c r="Z6" s="2">
+        <v>65</v>
+      </c>
+      <c r="AA6" s="2">
+        <v>65</v>
+      </c>
       <c r="AB6" s="13"/>
       <c r="AC6" s="13"/>
       <c r="AD6" s="13"/>
       <c r="AE6" s="13"/>
       <c r="AF6" s="13"/>
       <c r="AG6" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AH6" s="13"/>
       <c r="AI6" s="13"/>
@@ -1253,10 +1260,10 @@
       <c r="AR6" s="13"/>
       <c r="AS6" s="13"/>
       <c r="AT6" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU6" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AV6" s="4"/>
       <c r="AW6" s="4"/>
@@ -1267,7 +1274,7 @@
       <c r="BB6" s="4"/>
       <c r="BC6" s="4"/>
       <c r="BD6" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BE6" s="1"/>
       <c r="BF6" s="1"/>
@@ -1279,13 +1286,13 @@
       <c r="BL6" s="1"/>
     </row>
     <row r="7" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A7" s="17"/>
-      <c r="B7" s="25"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
+      <c r="A7" s="15"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
       <c r="F7" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
@@ -1347,31 +1354,31 @@
       <c r="BL7" s="1"/>
     </row>
     <row r="8" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="16">
         <v>1</v>
       </c>
-      <c r="C8" s="26">
-        <f>SUM(L8:Y8)</f>
-        <v>422</v>
-      </c>
-      <c r="D8" s="21">
+      <c r="C8" s="17">
+        <f>SUM(L8:AB8)</f>
+        <v>422.00000000000011</v>
+      </c>
+      <c r="D8" s="18">
         <v>46083</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="18">
         <v>46122</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13"/>
       <c r="I8" s="13"/>
       <c r="J8" s="13"/>
       <c r="K8" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L8" s="2">
         <v>48</v>
@@ -1392,37 +1399,44 @@
         <v>34</v>
       </c>
       <c r="R8" s="2">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="S8" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="T8" s="2">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="U8" s="2">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="V8" s="2">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="W8" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="X8" s="2">
-        <v>30</v>
+        <v>25.6</v>
       </c>
       <c r="Y8" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA8" s="13"/>
-      <c r="AB8" s="13"/>
+        <v>25.6</v>
+      </c>
+      <c r="Z8" s="2">
+        <v>25.6</v>
+      </c>
+      <c r="AA8" s="2">
+        <v>25.6</v>
+      </c>
+      <c r="AB8" s="2">
+        <v>25.6</v>
+      </c>
       <c r="AC8" s="13"/>
       <c r="AD8" s="13"/>
       <c r="AE8" s="13"/>
       <c r="AF8" s="13"/>
       <c r="AG8" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AH8" s="13"/>
       <c r="AI8" s="13"/>
@@ -1437,10 +1451,10 @@
       <c r="AR8" s="13"/>
       <c r="AS8" s="13"/>
       <c r="AT8" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU8" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AV8" s="6"/>
       <c r="AW8" s="6"/>
@@ -1451,7 +1465,7 @@
       <c r="BB8" s="6"/>
       <c r="BC8" s="6"/>
       <c r="BD8" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BE8" s="1"/>
       <c r="BF8" s="1"/>
@@ -1463,13 +1477,13 @@
       <c r="BL8" s="1"/>
     </row>
     <row r="9" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A9" s="17"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
+      <c r="A9" s="15"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
       <c r="F9" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13"/>
@@ -1531,31 +1545,31 @@
       <c r="BL9" s="1"/>
     </row>
     <row r="10" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="25">
+      <c r="B10" s="16">
         <v>1</v>
       </c>
-      <c r="C10" s="26">
-        <f>SUM(M10:Z10)</f>
+      <c r="C10" s="17">
+        <f>SUM(M10:AI10)</f>
         <v>63.3</v>
       </c>
-      <c r="D10" s="21">
+      <c r="D10" s="18">
         <v>46084</v>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="18">
         <v>46125</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13"/>
       <c r="I10" s="13"/>
       <c r="J10" s="13"/>
       <c r="K10" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L10" s="6"/>
       <c r="M10" s="3">
@@ -1574,43 +1588,59 @@
         <v>1</v>
       </c>
       <c r="R10" s="3">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="S10" s="3">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="T10" s="3">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="U10" s="3">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="V10" s="3">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="W10" s="3">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="X10" s="3">
-        <v>4.57</v>
+        <v>2</v>
       </c>
       <c r="Y10" s="3">
-        <v>4.57</v>
-      </c>
-      <c r="Z10" s="31">
-        <v>4.5599999999999996</v>
-      </c>
-      <c r="AA10" s="13"/>
-      <c r="AB10" s="13"/>
-      <c r="AC10" s="13"/>
-      <c r="AD10" s="13"/>
-      <c r="AE10" s="13"/>
-      <c r="AF10" s="13"/>
+        <v>3</v>
+      </c>
+      <c r="Z10" s="3">
+        <v>2</v>
+      </c>
+      <c r="AA10" s="3">
+        <v>3</v>
+      </c>
+      <c r="AB10" s="3">
+        <v>2</v>
+      </c>
+      <c r="AC10" s="3">
+        <v>3</v>
+      </c>
+      <c r="AD10" s="3">
+        <v>2</v>
+      </c>
+      <c r="AE10" s="3">
+        <v>3</v>
+      </c>
+      <c r="AF10" s="3">
+        <v>2</v>
+      </c>
       <c r="AG10" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AH10" s="13"/>
-      <c r="AI10" s="13"/>
+        <v>19</v>
+      </c>
+      <c r="AH10" s="3">
+        <v>2</v>
+      </c>
+      <c r="AI10" s="3">
+        <v>4.5</v>
+      </c>
       <c r="AJ10" s="6"/>
       <c r="AK10" s="13"/>
       <c r="AL10" s="13"/>
@@ -1622,10 +1652,10 @@
       <c r="AR10" s="13"/>
       <c r="AS10" s="13"/>
       <c r="AT10" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU10" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AV10" s="6"/>
       <c r="AW10" s="6"/>
@@ -1636,7 +1666,7 @@
       <c r="BB10" s="6"/>
       <c r="BC10" s="6"/>
       <c r="BD10" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BE10" s="1"/>
       <c r="BF10" s="1"/>
@@ -1648,13 +1678,13 @@
       <c r="BL10" s="1"/>
     </row>
     <row r="11" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A11" s="17"/>
-      <c r="B11" s="25"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
+      <c r="A11" s="15"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
       <c r="F11" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
@@ -1716,88 +1746,110 @@
       <c r="BL11" s="1"/>
     </row>
     <row r="12" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="25">
+      <c r="B12" s="16">
         <v>1</v>
       </c>
-      <c r="C12" s="26">
-        <f>SUM(N12:AA12)</f>
-        <v>63.29999999999999</v>
-      </c>
-      <c r="D12" s="21">
+      <c r="C12" s="17">
+        <f>SUM(L12:AK12)</f>
+        <v>400</v>
+      </c>
+      <c r="D12" s="18">
         <v>46085</v>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="18">
         <v>46126</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
       <c r="I12" s="13"/>
       <c r="J12" s="13"/>
       <c r="K12" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
+        <v>19</v>
+      </c>
+      <c r="L12" s="3">
+        <v>30</v>
+      </c>
+      <c r="M12" s="3">
+        <v>6</v>
+      </c>
       <c r="N12" s="3">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="O12" s="3">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="P12" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q12" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R12" s="3">
-        <v>4.8</v>
+        <v>24</v>
       </c>
       <c r="S12" s="3">
-        <v>4.8</v>
+        <v>12</v>
       </c>
       <c r="T12" s="3">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="U12" s="3">
-        <v>4.8</v>
+        <v>42</v>
       </c>
       <c r="V12" s="3">
-        <v>4.8</v>
+        <v>12</v>
       </c>
       <c r="W12" s="3">
-        <v>4.8</v>
+        <v>16</v>
       </c>
       <c r="X12" s="3">
-        <v>4.8</v>
+        <v>16</v>
       </c>
       <c r="Y12" s="3">
-        <v>4.8</v>
+        <v>16</v>
       </c>
       <c r="Z12" s="3">
-        <v>4.57</v>
+        <v>16</v>
       </c>
       <c r="AA12" s="3">
-        <v>4.33</v>
-      </c>
-      <c r="AB12" s="13"/>
-      <c r="AC12" s="13"/>
-      <c r="AD12" s="13"/>
-      <c r="AE12" s="13"/>
-      <c r="AF12" s="13"/>
+        <v>16</v>
+      </c>
+      <c r="AB12" s="3">
+        <v>16</v>
+      </c>
+      <c r="AC12" s="3">
+        <v>16</v>
+      </c>
+      <c r="AD12" s="3">
+        <v>16</v>
+      </c>
+      <c r="AE12" s="3">
+        <v>16</v>
+      </c>
+      <c r="AF12" s="3">
+        <v>16</v>
+      </c>
       <c r="AG12" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AH12" s="13"/>
-      <c r="AI12" s="13"/>
-      <c r="AJ12" s="6"/>
-      <c r="AK12" s="13"/>
+        <v>19</v>
+      </c>
+      <c r="AH12" s="3">
+        <v>16</v>
+      </c>
+      <c r="AI12" s="3">
+        <v>16</v>
+      </c>
+      <c r="AJ12" s="3">
+        <v>16</v>
+      </c>
+      <c r="AK12" s="3">
+        <v>12</v>
+      </c>
       <c r="AL12" s="13"/>
       <c r="AM12" s="13"/>
       <c r="AN12" s="13"/>
@@ -1807,10 +1859,10 @@
       <c r="AR12" s="13"/>
       <c r="AS12" s="13"/>
       <c r="AT12" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU12" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AV12" s="6"/>
       <c r="AW12" s="6"/>
@@ -1821,7 +1873,7 @@
       <c r="BB12" s="6"/>
       <c r="BC12" s="6"/>
       <c r="BD12" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BE12" s="1"/>
       <c r="BF12" s="1"/>
@@ -1833,13 +1885,13 @@
       <c r="BL12" s="1"/>
     </row>
     <row r="13" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A13" s="17"/>
-      <c r="B13" s="25"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
+      <c r="A13" s="15"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
       <c r="F13" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
@@ -1901,94 +1953,70 @@
       <c r="BL13" s="1"/>
     </row>
     <row r="14" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="25">
+      <c r="B14" s="16">
         <v>1</v>
       </c>
-      <c r="C14" s="26">
-        <f>SUM(L14:AB14)</f>
-        <v>399.99999999999994</v>
-      </c>
-      <c r="D14" s="21">
-        <v>46085</v>
-      </c>
-      <c r="E14" s="21">
+      <c r="C14" s="17">
+        <f>SUM(P14:AK14)</f>
+        <v>5</v>
+      </c>
+      <c r="D14" s="18">
+        <v>46090</v>
+      </c>
+      <c r="E14" s="18">
         <v>46126</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
       <c r="I14" s="13"/>
       <c r="J14" s="13"/>
       <c r="K14" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="L14" s="3">
-        <v>30</v>
-      </c>
-      <c r="M14" s="3">
-        <v>6</v>
-      </c>
-      <c r="N14" s="3">
-        <v>30</v>
-      </c>
-      <c r="O14" s="3">
-        <v>12</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="6"/>
       <c r="P14" s="3">
-        <v>6</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>6</v>
-      </c>
-      <c r="R14" s="3">
-        <v>28.2</v>
-      </c>
-      <c r="S14" s="3">
-        <v>28.2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Q14" s="3"/>
+      <c r="R14" s="3"/>
+      <c r="S14" s="3"/>
       <c r="T14" s="3">
-        <v>28.2</v>
-      </c>
-      <c r="U14" s="3">
-        <v>28.2</v>
-      </c>
-      <c r="V14" s="3">
-        <v>28.2</v>
-      </c>
-      <c r="W14" s="3">
-        <v>28.2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="U14" s="3"/>
+      <c r="V14" s="3"/>
+      <c r="W14" s="3"/>
       <c r="X14" s="3">
-        <v>28.2</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>28.2</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>28.2</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>28.2</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>28</v>
-      </c>
-      <c r="AC14" s="13"/>
-      <c r="AD14" s="13"/>
-      <c r="AE14" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="Y14" s="3"/>
+      <c r="Z14" s="3"/>
+      <c r="AA14" s="3"/>
+      <c r="AB14" s="3"/>
+      <c r="AC14" s="3"/>
+      <c r="AD14" s="3"/>
+      <c r="AE14" s="3">
+        <v>1</v>
+      </c>
       <c r="AF14" s="13"/>
       <c r="AG14" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AH14" s="13"/>
       <c r="AI14" s="13"/>
       <c r="AJ14" s="6"/>
-      <c r="AK14" s="13"/>
+      <c r="AK14" s="3">
+        <v>1</v>
+      </c>
       <c r="AL14" s="13"/>
       <c r="AM14" s="13"/>
       <c r="AN14" s="13"/>
@@ -1998,10 +2026,10 @@
       <c r="AR14" s="13"/>
       <c r="AS14" s="13"/>
       <c r="AT14" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU14" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AV14" s="6"/>
       <c r="AW14" s="6"/>
@@ -2012,7 +2040,7 @@
       <c r="BB14" s="6"/>
       <c r="BC14" s="6"/>
       <c r="BD14" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BE14" s="1"/>
       <c r="BF14" s="1"/>
@@ -2024,13 +2052,13 @@
       <c r="BL14" s="1"/>
     </row>
     <row r="15" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A15" s="17"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
+      <c r="A15" s="15"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
       <c r="F15" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
@@ -2092,95 +2120,113 @@
       <c r="BL15" s="1"/>
     </row>
     <row r="16" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="25">
+      <c r="B16" s="16">
         <v>1</v>
       </c>
-      <c r="C16" s="26">
-        <f>SUM(L16:AB16)</f>
-        <v>399.99999999999994</v>
-      </c>
-      <c r="D16" s="21">
+      <c r="C16" s="17">
+        <f>SUM(L16:AL16)</f>
+        <v>372</v>
+      </c>
+      <c r="D16" s="18">
         <v>46085</v>
       </c>
-      <c r="E16" s="21">
-        <v>46126</v>
+      <c r="E16" s="18">
+        <v>46127</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
       <c r="I16" s="13"/>
       <c r="J16" s="13"/>
       <c r="K16" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L16" s="3">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="M16" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N16" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="O16" s="3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P16" s="3">
         <v>6</v>
       </c>
       <c r="Q16" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R16" s="3">
-        <v>28.2</v>
+        <v>0</v>
       </c>
       <c r="S16" s="3">
-        <v>28.2</v>
+        <v>17</v>
       </c>
       <c r="T16" s="3">
-        <v>28.2</v>
+        <v>20</v>
       </c>
       <c r="U16" s="3">
-        <v>28.2</v>
+        <v>17</v>
       </c>
       <c r="V16" s="3">
-        <v>28.2</v>
+        <v>31</v>
       </c>
       <c r="W16" s="3">
-        <v>28.2</v>
+        <v>14</v>
       </c>
       <c r="X16" s="3">
-        <v>28.2</v>
+        <v>14</v>
       </c>
       <c r="Y16" s="3">
-        <v>28.2</v>
+        <v>14</v>
       </c>
       <c r="Z16" s="3">
-        <v>28.2</v>
+        <v>14</v>
       </c>
       <c r="AA16" s="3">
-        <v>28.2</v>
+        <v>14</v>
       </c>
       <c r="AB16" s="3">
-        <v>28</v>
-      </c>
-      <c r="AC16" s="13"/>
-      <c r="AD16" s="13"/>
-      <c r="AE16" s="13"/>
-      <c r="AF16" s="13"/>
+        <v>14</v>
+      </c>
+      <c r="AC16" s="3">
+        <v>14</v>
+      </c>
+      <c r="AD16" s="3">
+        <v>15</v>
+      </c>
+      <c r="AE16" s="3">
+        <v>15</v>
+      </c>
+      <c r="AF16" s="3">
+        <v>15</v>
+      </c>
       <c r="AG16" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AH16" s="13"/>
-      <c r="AI16" s="13"/>
-      <c r="AJ16" s="6"/>
-      <c r="AK16" s="13"/>
-      <c r="AL16" s="13"/>
+        <v>19</v>
+      </c>
+      <c r="AH16" s="3">
+        <v>15</v>
+      </c>
+      <c r="AI16" s="3">
+        <v>15</v>
+      </c>
+      <c r="AJ16" s="3">
+        <v>15</v>
+      </c>
+      <c r="AK16" s="3">
+        <v>15</v>
+      </c>
+      <c r="AL16" s="3">
+        <v>15</v>
+      </c>
       <c r="AM16" s="13"/>
       <c r="AN16" s="13"/>
       <c r="AO16" s="13"/>
@@ -2189,10 +2235,10 @@
       <c r="AR16" s="13"/>
       <c r="AS16" s="13"/>
       <c r="AT16" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU16" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AV16" s="6"/>
       <c r="AW16" s="6"/>
@@ -2203,7 +2249,7 @@
       <c r="BB16" s="6"/>
       <c r="BC16" s="6"/>
       <c r="BD16" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BE16" s="1"/>
       <c r="BF16" s="1"/>
@@ -2215,23 +2261,23 @@
       <c r="BL16" s="1"/>
     </row>
     <row r="17" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A17" s="17"/>
-      <c r="B17" s="25"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
+      <c r="A17" s="15"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
       <c r="F17" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
       <c r="K17" s="4"/>
       <c r="L17" s="13"/>
       <c r="M17" s="13"/>
-      <c r="N17" s="6"/>
-      <c r="O17" s="6"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13"/>
       <c r="P17" s="6"/>
       <c r="Q17" s="6"/>
       <c r="R17" s="6"/>
@@ -2283,72 +2329,100 @@
       <c r="BL17" s="1"/>
     </row>
     <row r="18" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="25">
+      <c r="B18" s="16">
         <v>1</v>
       </c>
-      <c r="C18" s="26">
-        <f>SUM(P18:AB18)</f>
-        <v>5</v>
-      </c>
-      <c r="D18" s="21">
+      <c r="C18" s="17">
+        <f>SUM(P18:AM18)</f>
+        <v>325</v>
+      </c>
+      <c r="D18" s="18">
         <v>46090</v>
       </c>
-      <c r="E18" s="21">
-        <v>46126</v>
+      <c r="E18" s="18">
+        <v>46129</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
       <c r="K18" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L18" s="13"/>
       <c r="M18" s="13"/>
-      <c r="N18" s="6"/>
-      <c r="O18" s="6"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13"/>
       <c r="P18" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q18" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>0</v>
+      </c>
       <c r="R18" s="3">
-        <v>1</v>
-      </c>
-      <c r="S18" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="3">
+        <v>0</v>
+      </c>
       <c r="T18" s="3">
-        <v>1</v>
-      </c>
-      <c r="U18" s="3"/>
-      <c r="V18" s="3"/>
-      <c r="W18" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="3">
+        <v>0</v>
+      </c>
+      <c r="V18" s="3">
+        <v>0</v>
+      </c>
+      <c r="W18" s="3">
+        <v>0</v>
+      </c>
       <c r="X18" s="3">
-        <v>1</v>
-      </c>
-      <c r="Y18" s="3"/>
-      <c r="Z18" s="3"/>
-      <c r="AA18" s="3"/>
-      <c r="AB18" s="3">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="13"/>
+      <c r="AB18" s="13"/>
       <c r="AC18" s="13"/>
       <c r="AD18" s="13"/>
-      <c r="AE18" s="13"/>
-      <c r="AF18" s="13"/>
+      <c r="AE18" s="3">
+        <v>40</v>
+      </c>
+      <c r="AF18" s="3">
+        <v>41.25</v>
+      </c>
       <c r="AG18" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AH18" s="13"/>
-      <c r="AI18" s="13"/>
-      <c r="AJ18" s="6"/>
-      <c r="AK18" s="13"/>
-      <c r="AL18" s="13"/>
-      <c r="AM18" s="13"/>
+        <v>19</v>
+      </c>
+      <c r="AH18" s="3">
+        <v>40</v>
+      </c>
+      <c r="AI18" s="3">
+        <v>41.25</v>
+      </c>
+      <c r="AJ18" s="3">
+        <v>40</v>
+      </c>
+      <c r="AK18" s="3">
+        <v>41.25</v>
+      </c>
+      <c r="AL18" s="3">
+        <v>40</v>
+      </c>
+      <c r="AM18" s="3">
+        <v>41.25</v>
+      </c>
       <c r="AN18" s="13"/>
       <c r="AO18" s="13"/>
       <c r="AP18" s="13"/>
@@ -2356,10 +2430,10 @@
       <c r="AR18" s="13"/>
       <c r="AS18" s="13"/>
       <c r="AT18" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU18" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AV18" s="6"/>
       <c r="AW18" s="6"/>
@@ -2370,7 +2444,7 @@
       <c r="BB18" s="6"/>
       <c r="BC18" s="6"/>
       <c r="BD18" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BE18" s="1"/>
       <c r="BF18" s="1"/>
@@ -2382,23 +2456,23 @@
       <c r="BL18" s="1"/>
     </row>
     <row r="19" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A19" s="17"/>
-      <c r="B19" s="25"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
+      <c r="A19" s="15"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
       <c r="F19" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
       <c r="K19" s="4"/>
       <c r="L19" s="13"/>
       <c r="M19" s="13"/>
-      <c r="N19" s="6"/>
-      <c r="O19" s="6"/>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13"/>
       <c r="P19" s="6"/>
       <c r="Q19" s="6"/>
       <c r="R19" s="6"/>
@@ -2450,111 +2524,75 @@
       <c r="BL19" s="1"/>
     </row>
     <row r="20" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="25">
+      <c r="B20" s="16">
         <v>1</v>
       </c>
-      <c r="C20" s="26">
-        <f>SUM(L20:AC20)</f>
-        <v>372</v>
-      </c>
-      <c r="D20" s="21">
-        <v>46085</v>
-      </c>
-      <c r="E20" s="21">
-        <v>46127</v>
+      <c r="C20" s="17">
+        <f>SUM(X20:AQ20)</f>
+        <v>800</v>
+      </c>
+      <c r="D20" s="18">
+        <v>46097</v>
+      </c>
+      <c r="E20" s="18">
+        <v>46134</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
       <c r="K20" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="L20" s="3">
-        <v>27</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
-        <v>28</v>
-      </c>
-      <c r="O20" s="3">
-        <v>8</v>
-      </c>
-      <c r="P20" s="3">
-        <v>6</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
-        <v>25.25</v>
-      </c>
-      <c r="S20" s="3">
-        <v>25.25</v>
-      </c>
-      <c r="T20" s="3">
-        <v>25.25</v>
-      </c>
-      <c r="U20" s="3">
-        <v>25.25</v>
-      </c>
-      <c r="V20" s="3">
-        <v>25.25</v>
-      </c>
-      <c r="W20" s="3">
-        <v>25.25</v>
-      </c>
-      <c r="X20" s="3">
-        <v>25.25</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>25.25</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>25.25</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>25.25</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>25.25</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>25.25</v>
-      </c>
-      <c r="AD20" s="13"/>
-      <c r="AE20" s="13"/>
-      <c r="AF20" s="13"/>
+        <v>19</v>
+      </c>
+      <c r="L20" s="13"/>
+      <c r="M20" s="13"/>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13"/>
+      <c r="P20" s="6"/>
+      <c r="Q20" s="6"/>
+      <c r="R20" s="6"/>
+      <c r="S20" s="6"/>
+      <c r="T20" s="6"/>
+      <c r="U20" s="6"/>
+      <c r="V20" s="6"/>
+      <c r="X20" s="6"/>
+      <c r="Y20" s="6"/>
+      <c r="Z20" s="6"/>
+      <c r="AA20" s="6"/>
+      <c r="AB20" s="6"/>
+      <c r="AC20" s="6"/>
+      <c r="AD20" s="3">
+        <v>360</v>
+      </c>
+      <c r="AE20" s="6"/>
+      <c r="AF20" s="6"/>
       <c r="AG20" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AH20" s="13"/>
-      <c r="AI20" s="13"/>
-      <c r="AJ20" s="6"/>
+      <c r="AJ20" s="13"/>
       <c r="AK20" s="13"/>
       <c r="AL20" s="13"/>
       <c r="AM20" s="13"/>
       <c r="AN20" s="13"/>
       <c r="AO20" s="13"/>
-      <c r="AP20" s="13"/>
-      <c r="AQ20" s="13"/>
-      <c r="AR20" s="13"/>
-      <c r="AS20" s="13"/>
+      <c r="AQ20" s="3">
+        <v>440</v>
+      </c>
+      <c r="AS20" s="6"/>
       <c r="AT20" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU20" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AV20" s="6"/>
+        <v>19</v>
+      </c>
+      <c r="AV20" s="13"/>
       <c r="AW20" s="6"/>
       <c r="AX20" s="6"/>
       <c r="AY20" s="6"/>
@@ -2563,7 +2601,7 @@
       <c r="BB20" s="6"/>
       <c r="BC20" s="6"/>
       <c r="BD20" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BE20" s="1"/>
       <c r="BF20" s="1"/>
@@ -2575,13 +2613,13 @@
       <c r="BL20" s="1"/>
     </row>
     <row r="21" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A21" s="17"/>
-      <c r="B21" s="25"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="22"/>
+      <c r="A21" s="15"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
       <c r="F21" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
@@ -2603,28 +2641,28 @@
       <c r="X21" s="6"/>
       <c r="Y21" s="6"/>
       <c r="Z21" s="6"/>
-      <c r="AA21" s="13"/>
-      <c r="AB21" s="13"/>
-      <c r="AC21" s="13"/>
-      <c r="AD21" s="13"/>
-      <c r="AE21" s="13"/>
-      <c r="AF21" s="13"/>
+      <c r="AA21" s="6"/>
+      <c r="AB21" s="6"/>
+      <c r="AC21" s="6"/>
+      <c r="AD21" s="6"/>
+      <c r="AE21" s="6"/>
+      <c r="AF21" s="6"/>
       <c r="AG21" s="4"/>
       <c r="AH21" s="13"/>
       <c r="AI21" s="13"/>
-      <c r="AJ21" s="6"/>
+      <c r="AJ21" s="13"/>
       <c r="AK21" s="13"/>
       <c r="AL21" s="13"/>
       <c r="AM21" s="13"/>
       <c r="AN21" s="13"/>
       <c r="AO21" s="13"/>
-      <c r="AP21" s="13"/>
-      <c r="AQ21" s="13"/>
-      <c r="AR21" s="13"/>
-      <c r="AS21" s="13"/>
+      <c r="AP21" s="6"/>
+      <c r="AQ21" s="6"/>
+      <c r="AR21" s="6"/>
+      <c r="AS21" s="6"/>
       <c r="AT21" s="4"/>
       <c r="AU21" s="4"/>
-      <c r="AV21" s="6"/>
+      <c r="AV21" s="13"/>
       <c r="AW21" s="6"/>
       <c r="AX21" s="6"/>
       <c r="AY21" s="6"/>
@@ -2633,91 +2671,63 @@
       <c r="BB21" s="6"/>
       <c r="BC21" s="6"/>
       <c r="BD21" s="4"/>
-      <c r="BE21" s="1"/>
-      <c r="BF21" s="1"/>
-      <c r="BG21" s="1"/>
-      <c r="BH21" s="1"/>
-      <c r="BI21" s="1"/>
-      <c r="BJ21" s="1"/>
-      <c r="BK21" s="1"/>
-      <c r="BL21" s="1"/>
     </row>
     <row r="22" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A22" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" s="25">
-        <v>1</v>
-      </c>
-      <c r="C22" s="26">
-        <f>SUM(P22:Z22)</f>
-        <v>0</v>
-      </c>
-      <c r="D22" s="21">
-        <v>46090</v>
-      </c>
-      <c r="E22" s="21">
-        <v>46129</v>
+      <c r="A22" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" s="26">
+        <v>2</v>
+      </c>
+      <c r="C22" s="27">
+        <f>Y22</f>
+        <v>5</v>
+      </c>
+      <c r="D22" s="18">
+        <v>46097</v>
+      </c>
+      <c r="E22" s="18">
+        <v>46134</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
+        <v>22</v>
+      </c>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="13"/>
       <c r="K22" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L22" s="13"/>
       <c r="M22" s="13"/>
       <c r="N22" s="13"/>
       <c r="O22" s="13"/>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
-      <c r="S22" s="3">
-        <v>0</v>
-      </c>
-      <c r="T22" s="3">
-        <v>0</v>
-      </c>
-      <c r="U22" s="3">
-        <v>0</v>
-      </c>
-      <c r="V22" s="3">
-        <v>0</v>
-      </c>
-      <c r="W22" s="3">
-        <v>0</v>
-      </c>
-      <c r="X22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="13"/>
-      <c r="AB22" s="13"/>
-      <c r="AC22" s="13"/>
-      <c r="AD22" s="13"/>
-      <c r="AE22" s="13"/>
-      <c r="AF22" s="13"/>
+      <c r="P22" s="13"/>
+      <c r="Q22" s="13"/>
+      <c r="R22" s="13"/>
+      <c r="S22" s="13"/>
+      <c r="T22" s="13"/>
+      <c r="U22" s="13"/>
+      <c r="V22" s="13"/>
+      <c r="W22" s="13"/>
+      <c r="X22" s="13"/>
+      <c r="Y22" s="5">
+        <v>5</v>
+      </c>
+      <c r="Z22" s="6"/>
+      <c r="AA22" s="6"/>
+      <c r="AB22" s="6"/>
+      <c r="AC22" s="6"/>
+      <c r="AD22" s="6"/>
+      <c r="AE22" s="6"/>
+      <c r="AF22" s="6"/>
       <c r="AG22" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AH22" s="13"/>
       <c r="AI22" s="13"/>
-      <c r="AJ22" s="6"/>
+      <c r="AJ22" s="13"/>
       <c r="AK22" s="13"/>
       <c r="AL22" s="13"/>
       <c r="AM22" s="13"/>
@@ -2728,70 +2738,62 @@
       <c r="AR22" s="13"/>
       <c r="AS22" s="13"/>
       <c r="AT22" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU22" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AV22" s="6"/>
-      <c r="AW22" s="6"/>
-      <c r="AX22" s="6"/>
-      <c r="AY22" s="6"/>
-      <c r="AZ22" s="6"/>
-      <c r="BA22" s="6"/>
-      <c r="BB22" s="6"/>
-      <c r="BC22" s="6"/>
+        <v>19</v>
+      </c>
+      <c r="AV22" s="13"/>
+      <c r="AW22" s="13"/>
+      <c r="AX22" s="13"/>
+      <c r="AY22" s="13"/>
+      <c r="AZ22" s="13"/>
+      <c r="BA22" s="13"/>
+      <c r="BB22" s="13"/>
+      <c r="BC22" s="13"/>
       <c r="BD22" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="BE22" s="1"/>
-      <c r="BF22" s="1"/>
-      <c r="BG22" s="1"/>
-      <c r="BH22" s="1"/>
-      <c r="BI22" s="1"/>
-      <c r="BJ22" s="1"/>
-      <c r="BK22" s="1"/>
-      <c r="BL22" s="1"/>
+        <v>19</v>
+      </c>
     </row>
     <row r="23" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A23" s="17"/>
-      <c r="B23" s="25"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
+      <c r="A23" s="15"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
       <c r="F23" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
+        <v>23</v>
+      </c>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
+      <c r="J23" s="13"/>
       <c r="K23" s="4"/>
       <c r="L23" s="13"/>
       <c r="M23" s="13"/>
       <c r="N23" s="13"/>
       <c r="O23" s="13"/>
-      <c r="P23" s="6"/>
-      <c r="Q23" s="6"/>
-      <c r="R23" s="6"/>
-      <c r="S23" s="6"/>
-      <c r="T23" s="6"/>
-      <c r="U23" s="6"/>
-      <c r="V23" s="6"/>
-      <c r="W23" s="6"/>
-      <c r="X23" s="6"/>
-      <c r="Y23" s="6"/>
-      <c r="Z23" s="6"/>
-      <c r="AA23" s="13"/>
-      <c r="AB23" s="13"/>
-      <c r="AC23" s="13"/>
-      <c r="AD23" s="13"/>
-      <c r="AE23" s="13"/>
-      <c r="AF23" s="13"/>
+      <c r="P23" s="13"/>
+      <c r="Q23" s="13"/>
+      <c r="R23" s="13"/>
+      <c r="S23" s="13"/>
+      <c r="T23" s="13"/>
+      <c r="U23" s="13"/>
+      <c r="V23" s="13"/>
+      <c r="W23" s="13"/>
+      <c r="X23" s="13"/>
+      <c r="Y23" s="13"/>
+      <c r="Z23" s="13"/>
+      <c r="AA23" s="4"/>
+      <c r="AB23" s="4"/>
+      <c r="AC23" s="4"/>
+      <c r="AD23" s="4"/>
+      <c r="AE23" s="4"/>
+      <c r="AF23" s="4"/>
       <c r="AG23" s="4"/>
-      <c r="AH23" s="13"/>
-      <c r="AI23" s="13"/>
-      <c r="AJ23" s="6"/>
+      <c r="AH23" s="4"/>
+      <c r="AI23" s="4"/>
+      <c r="AJ23" s="13"/>
       <c r="AK23" s="13"/>
       <c r="AL23" s="13"/>
       <c r="AM23" s="13"/>
@@ -2803,203 +2805,197 @@
       <c r="AS23" s="13"/>
       <c r="AT23" s="4"/>
       <c r="AU23" s="4"/>
-      <c r="AV23" s="6"/>
-      <c r="AW23" s="6"/>
-      <c r="AX23" s="6"/>
-      <c r="AY23" s="6"/>
-      <c r="AZ23" s="6"/>
-      <c r="BA23" s="6"/>
-      <c r="BB23" s="6"/>
-      <c r="BC23" s="6"/>
+      <c r="AV23" s="13"/>
+      <c r="AW23" s="13"/>
+      <c r="AX23" s="13"/>
+      <c r="AY23" s="13"/>
+      <c r="AZ23" s="13"/>
+      <c r="BA23" s="13"/>
+      <c r="BB23" s="13"/>
+      <c r="BC23" s="13"/>
       <c r="BD23" s="4"/>
-      <c r="BE23" s="1"/>
-      <c r="BF23" s="1"/>
-      <c r="BG23" s="1"/>
-      <c r="BH23" s="1"/>
-      <c r="BI23" s="1"/>
-      <c r="BJ23" s="1"/>
-      <c r="BK23" s="1"/>
-      <c r="BL23" s="1"/>
     </row>
     <row r="24" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A24" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="B24" s="25">
-        <v>1</v>
-      </c>
-      <c r="C24" s="26">
-        <f>SUM(W24:AD24)</f>
-        <v>800</v>
-      </c>
-      <c r="D24" s="21">
+      <c r="A24" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="26">
+        <v>2</v>
+      </c>
+      <c r="C24" s="27">
+        <f>SUM(Z24:AI24)</f>
+        <v>476</v>
+      </c>
+      <c r="D24" s="18">
         <v>46097</v>
       </c>
-      <c r="E24" s="21">
+      <c r="E24" s="18">
         <v>46134</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
+        <v>22</v>
+      </c>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
       <c r="K24" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L24" s="13"/>
       <c r="M24" s="13"/>
       <c r="N24" s="13"/>
       <c r="O24" s="13"/>
-      <c r="P24" s="6"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="6"/>
-      <c r="S24" s="6"/>
-      <c r="T24" s="6"/>
-      <c r="U24" s="6"/>
-      <c r="V24" s="6"/>
-      <c r="W24" s="3">
-        <v>480</v>
-      </c>
-      <c r="X24" s="6"/>
-      <c r="Y24" s="6"/>
-      <c r="Z24" s="6"/>
-      <c r="AA24" s="6"/>
-      <c r="AB24" s="6"/>
-      <c r="AC24" s="6"/>
-      <c r="AD24" s="3">
-        <v>320</v>
-      </c>
-      <c r="AE24" s="6"/>
-      <c r="AF24" s="6"/>
+      <c r="P24" s="13"/>
+      <c r="Q24" s="13"/>
+      <c r="R24" s="13"/>
+      <c r="S24" s="13"/>
+      <c r="T24" s="13"/>
+      <c r="U24" s="13"/>
+      <c r="V24" s="13"/>
+      <c r="W24" s="13"/>
+      <c r="X24" s="13"/>
+      <c r="Y24" s="13"/>
+      <c r="Z24" s="5">
+        <v>68</v>
+      </c>
+      <c r="AA24" s="5">
+        <v>68</v>
+      </c>
+      <c r="AB24" s="5">
+        <v>68</v>
+      </c>
+      <c r="AC24" s="5">
+        <v>68</v>
+      </c>
+      <c r="AD24" s="5">
+        <v>68</v>
+      </c>
+      <c r="AE24" s="5">
+        <v>68</v>
+      </c>
+      <c r="AF24" s="5">
+        <v>68</v>
+      </c>
       <c r="AG24" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AH24" s="13"/>
-      <c r="AI24" s="13"/>
+        <v>19</v>
+      </c>
+      <c r="AH24" s="5"/>
+      <c r="AI24" s="5"/>
       <c r="AJ24" s="13"/>
       <c r="AK24" s="13"/>
       <c r="AL24" s="13"/>
       <c r="AM24" s="13"/>
       <c r="AN24" s="13"/>
       <c r="AO24" s="13"/>
-      <c r="AP24" s="6"/>
-      <c r="AQ24" s="6"/>
-      <c r="AR24" s="6"/>
-      <c r="AS24" s="6"/>
+      <c r="AP24" s="13"/>
+      <c r="AQ24" s="13"/>
+      <c r="AR24" s="13"/>
+      <c r="AS24" s="13"/>
       <c r="AT24" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU24" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AV24" s="13"/>
-      <c r="AW24" s="6"/>
-      <c r="AX24" s="6"/>
-      <c r="AY24" s="6"/>
-      <c r="AZ24" s="6"/>
-      <c r="BA24" s="6"/>
-      <c r="BB24" s="6"/>
-      <c r="BC24" s="6"/>
+      <c r="AW24" s="13"/>
+      <c r="AX24" s="13"/>
+      <c r="AY24" s="13"/>
+      <c r="AZ24" s="13"/>
+      <c r="BA24" s="13"/>
+      <c r="BB24" s="13"/>
+      <c r="BC24" s="13"/>
       <c r="BD24" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="BE24" s="1"/>
-      <c r="BF24" s="1"/>
-      <c r="BG24" s="1"/>
-      <c r="BH24" s="1"/>
-      <c r="BI24" s="1"/>
-      <c r="BJ24" s="1"/>
-      <c r="BK24" s="1"/>
-      <c r="BL24" s="1"/>
+        <v>19</v>
+      </c>
     </row>
     <row r="25" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A25" s="17"/>
-      <c r="B25" s="25"/>
-      <c r="C25" s="26"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="22"/>
+      <c r="A25" s="15"/>
+      <c r="B25" s="26"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
       <c r="F25" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="6"/>
+        <v>23</v>
+      </c>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="13"/>
       <c r="K25" s="4"/>
       <c r="L25" s="13"/>
       <c r="M25" s="13"/>
       <c r="N25" s="13"/>
       <c r="O25" s="13"/>
-      <c r="P25" s="6"/>
-      <c r="Q25" s="6"/>
-      <c r="R25" s="6"/>
-      <c r="S25" s="6"/>
-      <c r="T25" s="6"/>
-      <c r="U25" s="6"/>
-      <c r="V25" s="6"/>
-      <c r="W25" s="6"/>
-      <c r="X25" s="6"/>
-      <c r="Y25" s="6"/>
-      <c r="Z25" s="6"/>
-      <c r="AA25" s="6"/>
-      <c r="AB25" s="6"/>
-      <c r="AC25" s="6"/>
-      <c r="AD25" s="6"/>
-      <c r="AE25" s="6"/>
-      <c r="AF25" s="6"/>
+      <c r="P25" s="13"/>
+      <c r="Q25" s="13"/>
+      <c r="R25" s="13"/>
+      <c r="S25" s="13"/>
+      <c r="T25" s="13"/>
+      <c r="U25" s="13"/>
+      <c r="V25" s="13"/>
+      <c r="W25" s="13"/>
+      <c r="X25" s="13"/>
+      <c r="Y25" s="13"/>
+      <c r="Z25" s="13"/>
+      <c r="AA25" s="4"/>
+      <c r="AB25" s="4"/>
+      <c r="AC25" s="4"/>
+      <c r="AD25" s="4"/>
+      <c r="AE25" s="4"/>
+      <c r="AF25" s="4"/>
       <c r="AG25" s="4"/>
-      <c r="AH25" s="13"/>
-      <c r="AI25" s="13"/>
+      <c r="AH25" s="4"/>
+      <c r="AI25" s="4"/>
       <c r="AJ25" s="13"/>
       <c r="AK25" s="13"/>
       <c r="AL25" s="13"/>
       <c r="AM25" s="13"/>
       <c r="AN25" s="13"/>
       <c r="AO25" s="13"/>
-      <c r="AP25" s="6"/>
-      <c r="AQ25" s="6"/>
-      <c r="AR25" s="6"/>
-      <c r="AS25" s="6"/>
+      <c r="AP25" s="13"/>
+      <c r="AQ25" s="13"/>
+      <c r="AR25" s="13"/>
+      <c r="AS25" s="13"/>
       <c r="AT25" s="4"/>
       <c r="AU25" s="4"/>
       <c r="AV25" s="13"/>
-      <c r="AW25" s="6"/>
-      <c r="AX25" s="6"/>
-      <c r="AY25" s="6"/>
-      <c r="AZ25" s="6"/>
-      <c r="BA25" s="6"/>
-      <c r="BB25" s="6"/>
-      <c r="BC25" s="6"/>
+      <c r="AW25" s="13"/>
+      <c r="AX25" s="13"/>
+      <c r="AY25" s="13"/>
+      <c r="AZ25" s="13"/>
+      <c r="BA25" s="13"/>
+      <c r="BB25" s="13"/>
+      <c r="BC25" s="13"/>
       <c r="BD25" s="4"/>
     </row>
     <row r="26" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A26" s="17" t="s">
+      <c r="A26" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B26" s="26">
+        <v>2</v>
+      </c>
+      <c r="C26" s="27">
+        <f>SUM(Z26:AI26)</f>
+        <v>476</v>
+      </c>
+      <c r="D26" s="18">
+        <v>46097</v>
+      </c>
+      <c r="E26" s="18">
+        <v>46134</v>
+      </c>
+      <c r="F26" s="11" t="s">
         <v>22</v>
-      </c>
-      <c r="B26" s="23">
-        <v>2</v>
-      </c>
-      <c r="C26" s="24">
-        <f>SUM(AA26:AF26)</f>
-        <v>476</v>
-      </c>
-      <c r="D26" s="21">
-        <v>46097</v>
-      </c>
-      <c r="E26" s="21">
-        <v>46134</v>
-      </c>
-      <c r="F26" s="11" t="s">
-        <v>24</v>
       </c>
       <c r="G26" s="13"/>
       <c r="H26" s="13"/>
       <c r="I26" s="13"/>
       <c r="J26" s="13"/>
       <c r="K26" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L26" s="13"/>
       <c r="M26" s="13"/>
@@ -3015,30 +3011,32 @@
       <c r="W26" s="13"/>
       <c r="X26" s="13"/>
       <c r="Y26" s="13"/>
-      <c r="Z26" s="13"/>
+      <c r="Z26" s="5">
+        <v>68</v>
+      </c>
       <c r="AA26" s="5">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="AB26" s="5">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="AC26" s="5">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="AD26" s="5">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="AE26" s="5">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="AF26" s="5">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="AG26" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AH26" s="4"/>
-      <c r="AI26" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="AH26" s="5"/>
+      <c r="AI26" s="5"/>
       <c r="AJ26" s="13"/>
       <c r="AK26" s="13"/>
       <c r="AL26" s="13"/>
@@ -3050,10 +3048,10 @@
       <c r="AR26" s="13"/>
       <c r="AS26" s="13"/>
       <c r="AT26" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU26" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AV26" s="13"/>
       <c r="AW26" s="13"/>
@@ -3064,17 +3062,17 @@
       <c r="BB26" s="13"/>
       <c r="BC26" s="13"/>
       <c r="BD26" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A27" s="17"/>
-      <c r="B27" s="23"/>
-      <c r="C27" s="24"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="22"/>
+      <c r="A27" s="15"/>
+      <c r="B27" s="26"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
       <c r="F27" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G27" s="13"/>
       <c r="H27" s="13"/>
@@ -3128,31 +3126,31 @@
       <c r="BD27" s="4"/>
     </row>
     <row r="28" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A28" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B28" s="23">
+      <c r="A28" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B28" s="26">
         <v>2</v>
       </c>
-      <c r="C28" s="24">
-        <f>SUM(AA28:AF28)</f>
-        <v>476</v>
-      </c>
-      <c r="D28" s="21">
+      <c r="C28" s="27">
+        <f>SUM(AA28:AF28,AI28:AN28)</f>
+        <v>233.6</v>
+      </c>
+      <c r="D28" s="18">
         <v>46097</v>
       </c>
-      <c r="E28" s="21">
+      <c r="E28" s="18">
         <v>46134</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G28" s="13"/>
       <c r="H28" s="13"/>
       <c r="I28" s="13"/>
       <c r="J28" s="13"/>
       <c r="K28" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L28" s="13"/>
       <c r="M28" s="13"/>
@@ -3170,31 +3168,38 @@
       <c r="Y28" s="13"/>
       <c r="Z28" s="13"/>
       <c r="AA28" s="5">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="AB28" s="5">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="AC28" s="5">
-        <v>80</v>
+        <v>25.6</v>
       </c>
       <c r="AD28" s="5">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="AE28" s="5">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="AF28" s="5">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="AG28" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AH28" s="4"/>
-      <c r="AI28" s="4"/>
-      <c r="AJ28" s="13"/>
-      <c r="AK28" s="13"/>
-      <c r="AL28" s="13"/>
+        <v>19</v>
+      </c>
+      <c r="AH28" s="5">
+        <v>26</v>
+      </c>
+      <c r="AI28" s="5">
+        <v>26</v>
+      </c>
+      <c r="AJ28" s="5">
+        <v>26</v>
+      </c>
+      <c r="AK28" s="5">
+        <v>26</v>
+      </c>
       <c r="AM28" s="13"/>
       <c r="AN28" s="13"/>
       <c r="AO28" s="13"/>
@@ -3203,10 +3208,10 @@
       <c r="AR28" s="13"/>
       <c r="AS28" s="13"/>
       <c r="AT28" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU28" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AV28" s="13"/>
       <c r="AW28" s="13"/>
@@ -3217,17 +3222,17 @@
       <c r="BB28" s="13"/>
       <c r="BC28" s="13"/>
       <c r="BD28" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A29" s="17"/>
-      <c r="B29" s="23"/>
-      <c r="C29" s="24"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
+      <c r="A29" s="15"/>
+      <c r="B29" s="26"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
       <c r="F29" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G29" s="13"/>
       <c r="H29" s="13"/>
@@ -3249,16 +3254,16 @@
       <c r="X29" s="13"/>
       <c r="Y29" s="13"/>
       <c r="Z29" s="13"/>
-      <c r="AA29" s="4"/>
-      <c r="AB29" s="4"/>
-      <c r="AC29" s="4"/>
-      <c r="AD29" s="4"/>
-      <c r="AE29" s="4"/>
-      <c r="AF29" s="4"/>
+      <c r="AA29" s="6"/>
+      <c r="AB29" s="6"/>
+      <c r="AC29" s="6"/>
+      <c r="AD29" s="6"/>
+      <c r="AE29" s="6"/>
+      <c r="AF29" s="6"/>
       <c r="AG29" s="4"/>
-      <c r="AH29" s="4"/>
-      <c r="AI29" s="4"/>
-      <c r="AJ29" s="13"/>
+      <c r="AH29" s="6"/>
+      <c r="AI29" s="6"/>
+      <c r="AJ29" s="6"/>
       <c r="AK29" s="13"/>
       <c r="AL29" s="13"/>
       <c r="AM29" s="13"/>
@@ -3281,31 +3286,31 @@
       <c r="BD29" s="4"/>
     </row>
     <row r="30" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A30" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B30" s="23">
+      <c r="A30" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="B30" s="26">
         <v>2</v>
       </c>
-      <c r="C30" s="24">
-        <f>SUM(AB30:AF30,AH30:AM30)</f>
-        <v>285.60000000000002</v>
-      </c>
-      <c r="D30" s="21">
+      <c r="C30" s="27">
+        <f>SUM(AB30:AF30,AH30:BC30)</f>
+        <v>43.3</v>
+      </c>
+      <c r="D30" s="18">
         <v>46097</v>
       </c>
-      <c r="E30" s="21">
+      <c r="E30" s="18">
         <v>46134</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G30" s="13"/>
       <c r="H30" s="13"/>
       <c r="I30" s="13"/>
       <c r="J30" s="13"/>
       <c r="K30" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L30" s="13"/>
       <c r="M30" s="13"/>
@@ -3322,54 +3327,60 @@
       <c r="X30" s="13"/>
       <c r="Y30" s="13"/>
       <c r="Z30" s="13"/>
-      <c r="AA30" s="13"/>
-      <c r="AB30" s="5">
-        <v>26</v>
-      </c>
-      <c r="AC30" s="5">
-        <v>26</v>
-      </c>
-      <c r="AD30" s="5">
-        <v>26</v>
-      </c>
-      <c r="AE30" s="5">
-        <v>26</v>
-      </c>
-      <c r="AF30" s="5">
-        <v>26</v>
+      <c r="AA30" s="6"/>
+      <c r="AB30" s="8">
+        <v>3.94</v>
+      </c>
+      <c r="AC30" s="8">
+        <v>3.76</v>
+      </c>
+      <c r="AD30" s="8">
+        <v>3.94</v>
+      </c>
+      <c r="AE30" s="8">
+        <v>2</v>
+      </c>
+      <c r="AF30" s="8">
+        <v>3.94</v>
       </c>
       <c r="AG30" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AH30" s="5">
-        <v>26</v>
-      </c>
-      <c r="AI30" s="5">
-        <v>26</v>
-      </c>
-      <c r="AJ30" s="5">
-        <v>26</v>
-      </c>
-      <c r="AK30" s="5">
-        <v>26</v>
-      </c>
-      <c r="AL30" s="5">
-        <v>26</v>
-      </c>
-      <c r="AM30" s="5">
-        <v>25.6</v>
-      </c>
-      <c r="AN30" s="13"/>
-      <c r="AO30" s="13"/>
-      <c r="AP30" s="13"/>
+        <v>19</v>
+      </c>
+      <c r="AH30" s="8">
+        <v>2</v>
+      </c>
+      <c r="AI30" s="8">
+        <v>3.94</v>
+      </c>
+      <c r="AJ30" s="8">
+        <v>2</v>
+      </c>
+      <c r="AK30" s="8">
+        <v>3.94</v>
+      </c>
+      <c r="AL30" s="8">
+        <v>2</v>
+      </c>
+      <c r="AM30" s="8">
+        <v>3.94</v>
+      </c>
+      <c r="AN30" s="8">
+        <v>2</v>
+      </c>
+      <c r="AO30" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="AP30" s="8">
+        <v>2</v>
+      </c>
       <c r="AQ30" s="13"/>
       <c r="AR30" s="13"/>
       <c r="AS30" s="13"/>
       <c r="AT30" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU30" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AV30" s="13"/>
       <c r="AW30" s="13"/>
@@ -3380,17 +3391,17 @@
       <c r="BB30" s="13"/>
       <c r="BC30" s="13"/>
       <c r="BD30" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A31" s="17"/>
-      <c r="B31" s="23"/>
-      <c r="C31" s="24"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
+      <c r="A31" s="15"/>
+      <c r="B31" s="26"/>
+      <c r="C31" s="27"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
       <c r="F31" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G31" s="13"/>
       <c r="H31" s="13"/>
@@ -3421,9 +3432,9 @@
       <c r="AG31" s="4"/>
       <c r="AH31" s="6"/>
       <c r="AI31" s="6"/>
-      <c r="AJ31" s="13"/>
-      <c r="AK31" s="13"/>
-      <c r="AL31" s="13"/>
+      <c r="AJ31" s="6"/>
+      <c r="AK31" s="6"/>
+      <c r="AL31" s="6"/>
       <c r="AM31" s="13"/>
       <c r="AN31" s="13"/>
       <c r="AO31" s="13"/>
@@ -3444,31 +3455,31 @@
       <c r="BD31" s="4"/>
     </row>
     <row r="32" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A32" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="B32" s="23">
+      <c r="A32" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="24">
-        <f>SUM(AC32:AF32,AH32:AN32)</f>
-        <v>43.3</v>
-      </c>
-      <c r="D32" s="21">
+      <c r="B32" s="26">
+        <v>2</v>
+      </c>
+      <c r="C32" s="27">
+        <f>SUM(AC32:AF32,AH32:AU32)</f>
+        <v>238</v>
+      </c>
+      <c r="D32" s="18">
         <v>46097</v>
       </c>
-      <c r="E32" s="21">
+      <c r="E32" s="18">
         <v>46134</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G32" s="13"/>
       <c r="H32" s="13"/>
       <c r="I32" s="13"/>
       <c r="J32" s="13"/>
       <c r="K32" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L32" s="13"/>
       <c r="M32" s="13"/>
@@ -3488,53 +3499,60 @@
       <c r="AA32" s="6"/>
       <c r="AB32" s="6"/>
       <c r="AC32" s="8">
-        <v>3.94</v>
+        <v>16</v>
       </c>
       <c r="AD32" s="8">
-        <v>3.94</v>
+        <v>16</v>
       </c>
       <c r="AE32" s="8">
-        <v>3.94</v>
+        <v>16</v>
       </c>
       <c r="AF32" s="8">
-        <v>3.94</v>
+        <v>16</v>
       </c>
       <c r="AG32" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AH32" s="8">
-        <v>3.94</v>
+        <v>16</v>
       </c>
       <c r="AI32" s="8">
-        <v>3.94</v>
+        <v>16</v>
       </c>
       <c r="AJ32" s="8">
-        <v>3.94</v>
+        <v>16</v>
       </c>
       <c r="AK32" s="8">
-        <v>3.94</v>
+        <v>16</v>
       </c>
       <c r="AL32" s="8">
-        <v>3.94</v>
+        <v>16</v>
       </c>
       <c r="AM32" s="8">
-        <v>3.94</v>
+        <v>16</v>
       </c>
       <c r="AN32" s="8">
-        <v>3.9</v>
-      </c>
-      <c r="AO32" s="13"/>
-      <c r="AP32" s="13"/>
-      <c r="AQ32" s="13"/>
-      <c r="AR32" s="13"/>
+        <v>16</v>
+      </c>
+      <c r="AO32" s="8">
+        <v>16</v>
+      </c>
+      <c r="AP32" s="8">
+        <v>16</v>
+      </c>
+      <c r="AQ32" s="8">
+        <v>16</v>
+      </c>
+      <c r="AR32" s="8">
+        <v>14</v>
+      </c>
       <c r="AS32" s="13"/>
       <c r="AT32" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU32" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AV32" s="13"/>
+        <v>19</v>
+      </c>
       <c r="AW32" s="13"/>
       <c r="AX32" s="13"/>
       <c r="AY32" s="13"/>
@@ -3543,17 +3561,17 @@
       <c r="BB32" s="13"/>
       <c r="BC32" s="13"/>
       <c r="BD32" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A33" s="17"/>
-      <c r="B33" s="23"/>
-      <c r="C33" s="24"/>
-      <c r="D33" s="22"/>
-      <c r="E33" s="22"/>
+      <c r="A33" s="15"/>
+      <c r="B33" s="26"/>
+      <c r="C33" s="27"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
       <c r="F33" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G33" s="13"/>
       <c r="H33" s="13"/>
@@ -3586,7 +3604,7 @@
       <c r="AI33" s="6"/>
       <c r="AJ33" s="6"/>
       <c r="AK33" s="6"/>
-      <c r="AL33" s="13"/>
+      <c r="AL33" s="6"/>
       <c r="AM33" s="13"/>
       <c r="AN33" s="13"/>
       <c r="AO33" s="13"/>
@@ -3607,31 +3625,31 @@
       <c r="BD33" s="4"/>
     </row>
     <row r="34" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A34" s="17" t="s">
+      <c r="A34" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B34" s="26">
         <v>2</v>
       </c>
-      <c r="B34" s="23">
-        <v>2</v>
-      </c>
-      <c r="C34" s="24">
-        <f>SUM(AD34:AF34,AH34:AO34)</f>
-        <v>43.3</v>
-      </c>
-      <c r="D34" s="21">
+      <c r="C34" s="27">
+        <f>SUM(AH34:AU34)</f>
+        <v>3</v>
+      </c>
+      <c r="D34" s="18">
         <v>46097</v>
       </c>
-      <c r="E34" s="21">
+      <c r="E34" s="18">
         <v>46134</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G34" s="13"/>
       <c r="H34" s="13"/>
       <c r="I34" s="13"/>
       <c r="J34" s="13"/>
       <c r="K34" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L34" s="13"/>
       <c r="M34" s="13"/>
@@ -3651,53 +3669,36 @@
       <c r="AA34" s="6"/>
       <c r="AB34" s="6"/>
       <c r="AC34" s="6"/>
-      <c r="AD34" s="8">
-        <v>3.94</v>
-      </c>
-      <c r="AE34" s="8">
-        <v>3.94</v>
-      </c>
-      <c r="AF34" s="8">
-        <v>3.94</v>
-      </c>
+      <c r="AD34" s="6"/>
+      <c r="AE34" s="6"/>
+      <c r="AF34" s="6"/>
       <c r="AG34" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AH34" s="8">
-        <v>3.94</v>
-      </c>
-      <c r="AI34" s="8">
-        <v>3.94</v>
-      </c>
-      <c r="AJ34" s="8">
-        <v>3.94</v>
-      </c>
-      <c r="AK34" s="8">
-        <v>3.94</v>
-      </c>
-      <c r="AL34" s="8">
-        <v>3.94</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AI34" s="8"/>
+      <c r="AJ34" s="8"/>
+      <c r="AK34" s="8"/>
+      <c r="AL34" s="8"/>
       <c r="AM34" s="8">
-        <v>3.94</v>
-      </c>
-      <c r="AN34" s="8">
-        <v>3.94</v>
-      </c>
-      <c r="AO34" s="8">
-        <v>3.9</v>
-      </c>
-      <c r="AP34" s="13"/>
-      <c r="AQ34" s="13"/>
-      <c r="AR34" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="AN34" s="8"/>
+      <c r="AO34" s="8"/>
+      <c r="AP34" s="8"/>
+      <c r="AQ34" s="8"/>
+      <c r="AR34" s="8">
+        <v>1</v>
+      </c>
       <c r="AS34" s="13"/>
       <c r="AT34" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU34" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AV34" s="13"/>
+        <v>19</v>
+      </c>
       <c r="AW34" s="13"/>
       <c r="AX34" s="13"/>
       <c r="AY34" s="13"/>
@@ -3706,17 +3707,17 @@
       <c r="BB34" s="13"/>
       <c r="BC34" s="13"/>
       <c r="BD34" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A35" s="17"/>
-      <c r="B35" s="23"/>
-      <c r="C35" s="24"/>
-      <c r="D35" s="22"/>
-      <c r="E35" s="22"/>
+      <c r="A35" s="15"/>
+      <c r="B35" s="26"/>
+      <c r="C35" s="27"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
       <c r="F35" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G35" s="13"/>
       <c r="H35" s="13"/>
@@ -3749,7 +3750,7 @@
       <c r="AI35" s="6"/>
       <c r="AJ35" s="6"/>
       <c r="AK35" s="6"/>
-      <c r="AL35" s="13"/>
+      <c r="AL35" s="6"/>
       <c r="AM35" s="13"/>
       <c r="AN35" s="13"/>
       <c r="AO35" s="13"/>
@@ -3770,31 +3771,31 @@
       <c r="BD35" s="4"/>
     </row>
     <row r="36" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A36" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="B36" s="23">
+      <c r="A36" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" s="26">
         <v>2</v>
       </c>
-      <c r="C36" s="24">
-        <f>SUM(AD36:AF36,AH36:AO36)</f>
-        <v>237.99999999999997</v>
-      </c>
-      <c r="D36" s="21">
+      <c r="C36" s="27">
+        <f>SUM(AC36:AF36,AH36:AS36)</f>
+        <v>256</v>
+      </c>
+      <c r="D36" s="18">
         <v>46097</v>
       </c>
-      <c r="E36" s="21">
+      <c r="E36" s="18">
         <v>46134</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G36" s="13"/>
       <c r="H36" s="13"/>
       <c r="I36" s="13"/>
       <c r="J36" s="13"/>
       <c r="K36" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L36" s="13"/>
       <c r="M36" s="13"/>
@@ -3813,52 +3814,62 @@
       <c r="Z36" s="13"/>
       <c r="AA36" s="6"/>
       <c r="AB36" s="6"/>
-      <c r="AC36" s="6"/>
+      <c r="AC36" s="8">
+        <v>16</v>
+      </c>
       <c r="AD36" s="8">
-        <v>21.6</v>
+        <v>16</v>
       </c>
       <c r="AE36" s="8">
-        <v>21.6</v>
+        <v>16</v>
       </c>
       <c r="AF36" s="8">
-        <v>21.6</v>
+        <v>16</v>
       </c>
       <c r="AG36" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AH36" s="8">
-        <v>21.6</v>
+        <v>16</v>
       </c>
       <c r="AI36" s="8">
-        <v>21.6</v>
+        <v>16</v>
       </c>
       <c r="AJ36" s="8">
-        <v>21.6</v>
+        <v>16</v>
       </c>
       <c r="AK36" s="8">
-        <v>21.6</v>
+        <v>16</v>
       </c>
       <c r="AL36" s="8">
-        <v>21.6</v>
+        <v>16</v>
       </c>
       <c r="AM36" s="8">
-        <v>21.6</v>
+        <v>16</v>
       </c>
       <c r="AN36" s="8">
-        <v>21.6</v>
+        <v>16</v>
       </c>
       <c r="AO36" s="8">
-        <v>22</v>
-      </c>
-      <c r="AP36" s="13"/>
-      <c r="AQ36" s="13"/>
-      <c r="AR36" s="13"/>
-      <c r="AS36" s="13"/>
+        <v>16</v>
+      </c>
+      <c r="AP36" s="8">
+        <v>16</v>
+      </c>
+      <c r="AQ36" s="8">
+        <v>16</v>
+      </c>
+      <c r="AR36" s="8">
+        <v>16</v>
+      </c>
+      <c r="AS36" s="8">
+        <v>16</v>
+      </c>
       <c r="AT36" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU36" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AV36" s="13"/>
       <c r="AW36" s="13"/>
@@ -3869,17 +3880,17 @@
       <c r="BB36" s="13"/>
       <c r="BC36" s="13"/>
       <c r="BD36" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A37" s="17"/>
-      <c r="B37" s="23"/>
-      <c r="C37" s="24"/>
-      <c r="D37" s="22"/>
-      <c r="E37" s="22"/>
+      <c r="A37" s="15"/>
+      <c r="B37" s="26"/>
+      <c r="C37" s="27"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="19"/>
       <c r="F37" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G37" s="13"/>
       <c r="H37" s="13"/>
@@ -3912,10 +3923,10 @@
       <c r="AI37" s="6"/>
       <c r="AJ37" s="6"/>
       <c r="AK37" s="6"/>
-      <c r="AL37" s="13"/>
-      <c r="AM37" s="13"/>
-      <c r="AN37" s="13"/>
-      <c r="AO37" s="13"/>
+      <c r="AL37" s="6"/>
+      <c r="AM37" s="6"/>
+      <c r="AN37" s="6"/>
+      <c r="AO37" s="6"/>
       <c r="AP37" s="13"/>
       <c r="AQ37" s="13"/>
       <c r="AR37" s="13"/>
@@ -3933,31 +3944,31 @@
       <c r="BD37" s="4"/>
     </row>
     <row r="38" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A38" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="B38" s="23">
+      <c r="A38" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B38" s="26">
         <v>2</v>
       </c>
-      <c r="C38" s="24">
-        <f>SUM(AD38:AF38,AH38:AO38)</f>
-        <v>237.99999999999997</v>
-      </c>
-      <c r="D38" s="21">
+      <c r="C38" s="27">
+        <f>SUM(AH38:AS38)</f>
+        <v>476</v>
+      </c>
+      <c r="D38" s="18">
         <v>46097</v>
       </c>
-      <c r="E38" s="21">
+      <c r="E38" s="18">
         <v>46134</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G38" s="13"/>
       <c r="H38" s="13"/>
       <c r="I38" s="13"/>
       <c r="J38" s="13"/>
       <c r="K38" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L38" s="13"/>
       <c r="M38" s="13"/>
@@ -3977,51 +3988,47 @@
       <c r="AA38" s="6"/>
       <c r="AB38" s="6"/>
       <c r="AC38" s="6"/>
-      <c r="AD38" s="8">
-        <v>21.6</v>
-      </c>
-      <c r="AE38" s="8">
-        <v>21.6</v>
-      </c>
-      <c r="AF38" s="8">
-        <v>21.6</v>
-      </c>
+      <c r="AD38" s="6"/>
+      <c r="AE38" s="6"/>
+      <c r="AF38" s="8"/>
       <c r="AG38" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AH38" s="8">
-        <v>21.6</v>
-      </c>
-      <c r="AI38" s="8">
-        <v>21.6</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="AH38" s="8"/>
+      <c r="AI38" s="8"/>
       <c r="AJ38" s="8">
-        <v>21.6</v>
+        <v>40</v>
       </c>
       <c r="AK38" s="8">
-        <v>21.6</v>
+        <v>40</v>
       </c>
       <c r="AL38" s="8">
-        <v>21.6</v>
+        <v>40</v>
       </c>
       <c r="AM38" s="8">
-        <v>21.6</v>
-      </c>
-      <c r="AN38" s="8">
-        <v>21.6</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="AN38" s="8"/>
       <c r="AO38" s="8">
-        <v>22</v>
-      </c>
-      <c r="AP38" s="13"/>
-      <c r="AQ38" s="13"/>
-      <c r="AR38" s="13"/>
-      <c r="AS38" s="13"/>
+        <v>40</v>
+      </c>
+      <c r="AP38" s="8">
+        <v>40</v>
+      </c>
+      <c r="AQ38" s="8">
+        <v>80</v>
+      </c>
+      <c r="AR38" s="8">
+        <v>80</v>
+      </c>
+      <c r="AS38" s="8">
+        <v>76</v>
+      </c>
       <c r="AT38" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU38" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AV38" s="13"/>
       <c r="AW38" s="13"/>
@@ -4032,17 +4039,17 @@
       <c r="BB38" s="13"/>
       <c r="BC38" s="13"/>
       <c r="BD38" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A39" s="17"/>
-      <c r="B39" s="23"/>
-      <c r="C39" s="24"/>
-      <c r="D39" s="22"/>
-      <c r="E39" s="22"/>
+      <c r="A39" s="15"/>
+      <c r="B39" s="26"/>
+      <c r="C39" s="27"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="19"/>
       <c r="F39" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G39" s="13"/>
       <c r="H39" s="13"/>
@@ -4062,23 +4069,23 @@
       <c r="V39" s="13"/>
       <c r="W39" s="13"/>
       <c r="X39" s="13"/>
-      <c r="Y39" s="13"/>
-      <c r="Z39" s="13"/>
+      <c r="Y39" s="6"/>
+      <c r="Z39" s="6"/>
       <c r="AA39" s="6"/>
       <c r="AB39" s="6"/>
       <c r="AC39" s="6"/>
       <c r="AD39" s="6"/>
-      <c r="AE39" s="6"/>
-      <c r="AF39" s="6"/>
+      <c r="AE39" s="13"/>
+      <c r="AF39" s="13"/>
       <c r="AG39" s="4"/>
       <c r="AH39" s="6"/>
       <c r="AI39" s="6"/>
       <c r="AJ39" s="6"/>
       <c r="AK39" s="6"/>
-      <c r="AL39" s="13"/>
-      <c r="AM39" s="13"/>
-      <c r="AN39" s="13"/>
-      <c r="AO39" s="13"/>
+      <c r="AL39" s="6"/>
+      <c r="AM39" s="6"/>
+      <c r="AN39" s="6"/>
+      <c r="AO39" s="6"/>
       <c r="AP39" s="13"/>
       <c r="AQ39" s="13"/>
       <c r="AR39" s="13"/>
@@ -4096,31 +4103,31 @@
       <c r="BD39" s="4"/>
     </row>
     <row r="40" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A40" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="B40" s="23">
+      <c r="A40" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="B40" s="26">
         <v>2</v>
       </c>
-      <c r="C40" s="24">
-        <f>SUM(AF40,AH40:AO40)</f>
-        <v>3</v>
-      </c>
-      <c r="D40" s="21">
+      <c r="C40" s="27">
+        <f>SUM(AS40:AX40)</f>
+        <v>476</v>
+      </c>
+      <c r="D40" s="18">
         <v>46097</v>
       </c>
-      <c r="E40" s="21">
+      <c r="E40" s="18">
         <v>46134</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G40" s="13"/>
       <c r="H40" s="13"/>
       <c r="I40" s="13"/>
       <c r="J40" s="13"/>
       <c r="K40" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L40" s="13"/>
       <c r="M40" s="13"/>
@@ -4137,59 +4144,55 @@
       <c r="X40" s="13"/>
       <c r="Y40" s="13"/>
       <c r="Z40" s="13"/>
-      <c r="AA40" s="6"/>
-      <c r="AB40" s="6"/>
-      <c r="AC40" s="6"/>
-      <c r="AD40" s="6"/>
-      <c r="AE40" s="6"/>
-      <c r="AF40" s="8">
-        <v>1</v>
-      </c>
+      <c r="AA40" s="13"/>
+      <c r="AB40" s="13"/>
+      <c r="AC40" s="13"/>
+      <c r="AD40" s="13"/>
+      <c r="AE40" s="13"/>
+      <c r="AF40" s="13"/>
       <c r="AG40" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AH40" s="8"/>
-      <c r="AI40" s="8"/>
-      <c r="AJ40" s="8"/>
-      <c r="AK40" s="8">
-        <v>1</v>
-      </c>
-      <c r="AL40" s="8"/>
-      <c r="AM40" s="8"/>
-      <c r="AN40" s="8"/>
-      <c r="AO40" s="8">
-        <v>1</v>
-      </c>
-      <c r="AP40" s="13"/>
-      <c r="AQ40" s="13"/>
-      <c r="AR40" s="13"/>
-      <c r="AS40" s="13"/>
+        <v>19</v>
+      </c>
+      <c r="AH40" s="6"/>
+      <c r="AI40" s="6"/>
+      <c r="AJ40" s="6"/>
+      <c r="AK40" s="6"/>
+      <c r="AL40" s="6"/>
+      <c r="AM40" s="6"/>
+      <c r="AN40" s="6"/>
+      <c r="AO40" s="6"/>
+      <c r="AQ40" s="6"/>
+      <c r="AS40" s="8">
+        <v>160</v>
+      </c>
       <c r="AT40" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU40" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AV40" s="13"/>
       <c r="AW40" s="13"/>
-      <c r="AX40" s="13"/>
+      <c r="AX40" s="8">
+        <v>316</v>
+      </c>
       <c r="AY40" s="13"/>
       <c r="AZ40" s="13"/>
       <c r="BA40" s="13"/>
       <c r="BB40" s="13"/>
       <c r="BC40" s="13"/>
       <c r="BD40" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A41" s="17"/>
-      <c r="B41" s="23"/>
-      <c r="C41" s="24"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
+      <c r="A41" s="15"/>
+      <c r="B41" s="26"/>
+      <c r="C41" s="27"/>
+      <c r="D41" s="19"/>
+      <c r="E41" s="19"/>
       <c r="F41" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G41" s="13"/>
       <c r="H41" s="13"/>
@@ -4211,28 +4214,28 @@
       <c r="X41" s="13"/>
       <c r="Y41" s="13"/>
       <c r="Z41" s="13"/>
-      <c r="AA41" s="6"/>
-      <c r="AB41" s="6"/>
+      <c r="AA41" s="13"/>
+      <c r="AB41" s="13"/>
       <c r="AC41" s="6"/>
       <c r="AD41" s="6"/>
       <c r="AE41" s="6"/>
       <c r="AF41" s="6"/>
       <c r="AG41" s="4"/>
-      <c r="AH41" s="6"/>
-      <c r="AI41" s="6"/>
-      <c r="AJ41" s="6"/>
-      <c r="AK41" s="6"/>
-      <c r="AL41" s="13"/>
-      <c r="AM41" s="13"/>
-      <c r="AN41" s="13"/>
-      <c r="AO41" s="13"/>
-      <c r="AP41" s="13"/>
-      <c r="AQ41" s="13"/>
-      <c r="AR41" s="13"/>
-      <c r="AS41" s="13"/>
+      <c r="AH41" s="13"/>
+      <c r="AI41" s="13"/>
+      <c r="AJ41" s="13"/>
+      <c r="AK41" s="13"/>
+      <c r="AL41" s="6"/>
+      <c r="AM41" s="6"/>
+      <c r="AN41" s="6"/>
+      <c r="AO41" s="6"/>
+      <c r="AP41" s="6"/>
+      <c r="AQ41" s="6"/>
+      <c r="AR41" s="6"/>
+      <c r="AS41" s="6"/>
       <c r="AT41" s="4"/>
       <c r="AU41" s="4"/>
-      <c r="AV41" s="13"/>
+      <c r="AV41" s="6"/>
       <c r="AW41" s="13"/>
       <c r="AX41" s="13"/>
       <c r="AY41" s="13"/>
@@ -4243,31 +4246,31 @@
       <c r="BD41" s="4"/>
     </row>
     <row r="42" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A42" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="B42" s="23">
-        <v>2</v>
-      </c>
-      <c r="C42" s="24">
-        <f>SUM(AD42:AF42,AH42:AO42)</f>
-        <v>234.30000000000004</v>
-      </c>
-      <c r="D42" s="21">
+      <c r="A42" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B42" s="28">
+        <v>3</v>
+      </c>
+      <c r="C42" s="29">
+        <f>SUM(AH42:AI42)</f>
+        <v>126</v>
+      </c>
+      <c r="D42" s="18">
         <v>46097</v>
       </c>
-      <c r="E42" s="21">
+      <c r="E42" s="18">
         <v>46134</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G42" s="13"/>
       <c r="H42" s="13"/>
       <c r="I42" s="13"/>
       <c r="J42" s="13"/>
       <c r="K42" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L42" s="13"/>
       <c r="M42" s="13"/>
@@ -4284,59 +4287,39 @@
       <c r="X42" s="13"/>
       <c r="Y42" s="13"/>
       <c r="Z42" s="13"/>
-      <c r="AA42" s="6"/>
-      <c r="AB42" s="6"/>
-      <c r="AC42" s="6"/>
-      <c r="AD42" s="8">
-        <v>21.3</v>
-      </c>
-      <c r="AE42" s="8">
-        <v>21.3</v>
-      </c>
-      <c r="AF42" s="8">
-        <v>21.3</v>
-      </c>
+      <c r="AA42" s="13"/>
+      <c r="AB42" s="13"/>
+      <c r="AC42" s="13"/>
+      <c r="AD42" s="13"/>
+      <c r="AE42" s="13"/>
+      <c r="AF42" s="13"/>
       <c r="AG42" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AH42" s="8">
-        <v>21.3</v>
-      </c>
-      <c r="AI42" s="8">
-        <v>21.3</v>
-      </c>
-      <c r="AJ42" s="8">
-        <v>21.3</v>
-      </c>
-      <c r="AK42" s="8">
-        <v>21.3</v>
-      </c>
-      <c r="AL42" s="8">
-        <v>21.3</v>
-      </c>
-      <c r="AM42" s="8">
-        <v>21.3</v>
-      </c>
-      <c r="AN42" s="8">
-        <v>21.3</v>
-      </c>
-      <c r="AO42" s="8">
-        <v>21.3</v>
-      </c>
-      <c r="AP42" s="8">
-        <v>21.7</v>
-      </c>
-      <c r="AQ42" s="13"/>
-      <c r="AR42" s="13"/>
-      <c r="AS42" s="13"/>
+        <v>19</v>
+      </c>
+      <c r="AH42" s="7">
+        <v>63</v>
+      </c>
+      <c r="AI42" s="7">
+        <v>63</v>
+      </c>
+      <c r="AJ42" s="4"/>
+      <c r="AK42" s="13"/>
+      <c r="AL42" s="13"/>
+      <c r="AM42" s="13"/>
+      <c r="AN42" s="13"/>
+      <c r="AO42" s="13"/>
+      <c r="AP42" s="13"/>
+      <c r="AQ42" s="6"/>
+      <c r="AR42" s="6"/>
+      <c r="AS42" s="6"/>
       <c r="AT42" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU42" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AV42" s="13"/>
-      <c r="AW42" s="13"/>
+        <v>19</v>
+      </c>
+      <c r="AV42" s="4"/>
+      <c r="AW42" s="4"/>
       <c r="AX42" s="13"/>
       <c r="AY42" s="13"/>
       <c r="AZ42" s="13"/>
@@ -4344,17 +4327,17 @@
       <c r="BB42" s="13"/>
       <c r="BC42" s="13"/>
       <c r="BD42" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A43" s="17"/>
-      <c r="B43" s="23"/>
-      <c r="C43" s="24"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="22"/>
+      <c r="A43" s="15"/>
+      <c r="B43" s="28"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="19"/>
+      <c r="E43" s="19"/>
       <c r="F43" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G43" s="13"/>
       <c r="H43" s="13"/>
@@ -4376,29 +4359,29 @@
       <c r="X43" s="13"/>
       <c r="Y43" s="13"/>
       <c r="Z43" s="13"/>
-      <c r="AA43" s="6"/>
-      <c r="AB43" s="6"/>
-      <c r="AC43" s="6"/>
-      <c r="AD43" s="6"/>
-      <c r="AE43" s="6"/>
-      <c r="AF43" s="6"/>
+      <c r="AA43" s="13"/>
+      <c r="AB43" s="13"/>
+      <c r="AC43" s="13"/>
+      <c r="AD43" s="13"/>
+      <c r="AE43" s="13"/>
+      <c r="AF43" s="13"/>
       <c r="AG43" s="4"/>
-      <c r="AH43" s="6"/>
-      <c r="AI43" s="6"/>
-      <c r="AJ43" s="6"/>
-      <c r="AK43" s="6"/>
-      <c r="AL43" s="6"/>
-      <c r="AM43" s="6"/>
-      <c r="AN43" s="6"/>
+      <c r="AH43" s="4"/>
+      <c r="AI43" s="4"/>
+      <c r="AJ43" s="4"/>
+      <c r="AK43" s="13"/>
+      <c r="AL43" s="13"/>
+      <c r="AM43" s="13"/>
+      <c r="AN43" s="13"/>
       <c r="AO43" s="13"/>
       <c r="AP43" s="13"/>
-      <c r="AQ43" s="13"/>
-      <c r="AR43" s="13"/>
-      <c r="AS43" s="13"/>
+      <c r="AQ43" s="6"/>
+      <c r="AR43" s="6"/>
+      <c r="AS43" s="6"/>
       <c r="AT43" s="4"/>
       <c r="AU43" s="4"/>
-      <c r="AV43" s="13"/>
-      <c r="AW43" s="13"/>
+      <c r="AV43" s="4"/>
+      <c r="AW43" s="4"/>
       <c r="AX43" s="13"/>
       <c r="AY43" s="13"/>
       <c r="AZ43" s="13"/>
@@ -4408,31 +4391,31 @@
       <c r="BD43" s="4"/>
     </row>
     <row r="44" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A44" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="B44" s="23">
-        <v>2</v>
-      </c>
-      <c r="C44" s="24">
-        <f>SUM(AE44:AF44,AH44:AN44)</f>
-        <v>0</v>
-      </c>
-      <c r="D44" s="21">
+      <c r="A44" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B44" s="28">
+        <v>3</v>
+      </c>
+      <c r="C44" s="29">
+        <f>SUM(AH44:AI44)</f>
+        <v>126</v>
+      </c>
+      <c r="D44" s="18">
         <v>46097</v>
       </c>
-      <c r="E44" s="21">
+      <c r="E44" s="18">
         <v>46134</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G44" s="13"/>
       <c r="H44" s="13"/>
       <c r="I44" s="13"/>
       <c r="J44" s="13"/>
       <c r="K44" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L44" s="13"/>
       <c r="M44" s="13"/>
@@ -4449,53 +4432,39 @@
       <c r="X44" s="13"/>
       <c r="Y44" s="13"/>
       <c r="Z44" s="13"/>
-      <c r="AA44" s="6"/>
-      <c r="AB44" s="6"/>
-      <c r="AC44" s="6"/>
-      <c r="AD44" s="6"/>
-      <c r="AE44" s="8">
-        <v>0</v>
-      </c>
-      <c r="AF44" s="8">
-        <v>0</v>
-      </c>
+      <c r="AA44" s="13"/>
+      <c r="AB44" s="13"/>
+      <c r="AC44" s="13"/>
+      <c r="AD44" s="13"/>
+      <c r="AE44" s="13"/>
+      <c r="AF44" s="13"/>
       <c r="AG44" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AH44" s="8">
-        <v>0</v>
-      </c>
-      <c r="AI44" s="8">
-        <v>0</v>
-      </c>
-      <c r="AJ44" s="8">
-        <v>0</v>
-      </c>
-      <c r="AK44" s="8">
-        <v>0</v>
-      </c>
-      <c r="AL44" s="8">
-        <v>0</v>
-      </c>
-      <c r="AM44" s="8">
-        <v>0</v>
-      </c>
-      <c r="AN44" s="8">
-        <v>0</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="AH44" s="7">
+        <v>63</v>
+      </c>
+      <c r="AI44" s="7">
+        <v>63</v>
+      </c>
+      <c r="AJ44" s="4"/>
+      <c r="AK44" s="13"/>
+      <c r="AL44" s="13"/>
+      <c r="AM44" s="13"/>
+      <c r="AN44" s="13"/>
       <c r="AO44" s="13"/>
       <c r="AP44" s="13"/>
-      <c r="AQ44" s="13"/>
-      <c r="AR44" s="13"/>
-      <c r="AS44" s="13"/>
+      <c r="AQ44" s="6"/>
+      <c r="AR44" s="6"/>
+      <c r="AS44" s="6"/>
       <c r="AT44" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU44" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AV44" s="13"/>
-      <c r="AW44" s="13"/>
+        <v>19</v>
+      </c>
+      <c r="AV44" s="4"/>
+      <c r="AW44" s="4"/>
       <c r="AX44" s="13"/>
       <c r="AY44" s="13"/>
       <c r="AZ44" s="13"/>
@@ -4503,17 +4472,17 @@
       <c r="BB44" s="13"/>
       <c r="BC44" s="13"/>
       <c r="BD44" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A45" s="17"/>
-      <c r="B45" s="23"/>
-      <c r="C45" s="24"/>
-      <c r="D45" s="22"/>
-      <c r="E45" s="22"/>
+      <c r="A45" s="15"/>
+      <c r="B45" s="28"/>
+      <c r="C45" s="30"/>
+      <c r="D45" s="19"/>
+      <c r="E45" s="19"/>
       <c r="F45" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G45" s="13"/>
       <c r="H45" s="13"/>
@@ -4533,31 +4502,31 @@
       <c r="V45" s="13"/>
       <c r="W45" s="13"/>
       <c r="X45" s="13"/>
-      <c r="Y45" s="6"/>
-      <c r="Z45" s="6"/>
-      <c r="AA45" s="6"/>
-      <c r="AB45" s="6"/>
-      <c r="AC45" s="6"/>
-      <c r="AD45" s="6"/>
+      <c r="Y45" s="13"/>
+      <c r="Z45" s="13"/>
+      <c r="AA45" s="13"/>
+      <c r="AB45" s="13"/>
+      <c r="AC45" s="13"/>
+      <c r="AD45" s="13"/>
       <c r="AE45" s="13"/>
       <c r="AF45" s="13"/>
       <c r="AG45" s="4"/>
-      <c r="AH45" s="6"/>
-      <c r="AI45" s="6"/>
-      <c r="AJ45" s="6"/>
-      <c r="AK45" s="6"/>
-      <c r="AL45" s="6"/>
-      <c r="AM45" s="6"/>
-      <c r="AN45" s="6"/>
+      <c r="AH45" s="4"/>
+      <c r="AI45" s="4"/>
+      <c r="AJ45" s="4"/>
+      <c r="AK45" s="13"/>
+      <c r="AL45" s="13"/>
+      <c r="AM45" s="13"/>
+      <c r="AN45" s="13"/>
       <c r="AO45" s="13"/>
       <c r="AP45" s="13"/>
-      <c r="AQ45" s="13"/>
-      <c r="AR45" s="13"/>
-      <c r="AS45" s="13"/>
+      <c r="AQ45" s="6"/>
+      <c r="AR45" s="6"/>
+      <c r="AS45" s="6"/>
       <c r="AT45" s="4"/>
       <c r="AU45" s="4"/>
-      <c r="AV45" s="13"/>
-      <c r="AW45" s="13"/>
+      <c r="AV45" s="4"/>
+      <c r="AW45" s="4"/>
       <c r="AX45" s="13"/>
       <c r="AY45" s="13"/>
       <c r="AZ45" s="13"/>
@@ -4567,31 +4536,31 @@
       <c r="BD45" s="4"/>
     </row>
     <row r="46" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A46" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="B46" s="23">
-        <v>2</v>
-      </c>
-      <c r="C46" s="24">
-        <f>SUM(AQ46)</f>
-        <v>476</v>
-      </c>
-      <c r="D46" s="21">
+      <c r="A46" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B46" s="28">
+        <v>3</v>
+      </c>
+      <c r="C46" s="29">
+        <f>SUM(AH46:AJ46)</f>
+        <v>75.599999999999994</v>
+      </c>
+      <c r="D46" s="18">
         <v>46097</v>
       </c>
-      <c r="E46" s="21">
+      <c r="E46" s="18">
         <v>46134</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G46" s="13"/>
       <c r="H46" s="13"/>
       <c r="I46" s="13"/>
       <c r="J46" s="13"/>
       <c r="K46" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L46" s="13"/>
       <c r="M46" s="13"/>
@@ -4615,29 +4584,34 @@
       <c r="AE46" s="13"/>
       <c r="AF46" s="13"/>
       <c r="AG46" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AH46" s="6"/>
-      <c r="AI46" s="6"/>
-      <c r="AJ46" s="6"/>
-      <c r="AK46" s="6"/>
-      <c r="AL46" s="6"/>
-      <c r="AM46" s="6"/>
-      <c r="AN46" s="6"/>
-      <c r="AP46" s="6"/>
-      <c r="AQ46" s="8">
-        <v>476</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="AH46" s="7">
+        <v>25.2</v>
+      </c>
+      <c r="AI46" s="7">
+        <v>25.2</v>
+      </c>
+      <c r="AJ46" s="7">
+        <v>25.2</v>
+      </c>
+      <c r="AK46" s="13"/>
+      <c r="AL46" s="13"/>
+      <c r="AM46" s="13"/>
+      <c r="AN46" s="13"/>
+      <c r="AO46" s="13"/>
+      <c r="AP46" s="13"/>
+      <c r="AQ46" s="6"/>
       <c r="AR46" s="6"/>
       <c r="AS46" s="6"/>
       <c r="AT46" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU46" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AV46" s="6"/>
-      <c r="AW46" s="13"/>
+      <c r="AW46" s="6"/>
       <c r="AX46" s="13"/>
       <c r="AY46" s="13"/>
       <c r="AZ46" s="13"/>
@@ -4645,17 +4619,17 @@
       <c r="BB46" s="13"/>
       <c r="BC46" s="13"/>
       <c r="BD46" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A47" s="17"/>
-      <c r="B47" s="23"/>
-      <c r="C47" s="24"/>
-      <c r="D47" s="22"/>
-      <c r="E47" s="22"/>
+      <c r="A47" s="15"/>
+      <c r="B47" s="28"/>
+      <c r="C47" s="30"/>
+      <c r="D47" s="19"/>
+      <c r="E47" s="19"/>
       <c r="F47" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G47" s="13"/>
       <c r="H47" s="13"/>
@@ -4679,27 +4653,27 @@
       <c r="Z47" s="13"/>
       <c r="AA47" s="13"/>
       <c r="AB47" s="13"/>
-      <c r="AC47" s="6"/>
-      <c r="AD47" s="6"/>
-      <c r="AE47" s="6"/>
-      <c r="AF47" s="6"/>
+      <c r="AC47" s="13"/>
+      <c r="AD47" s="13"/>
+      <c r="AE47" s="13"/>
+      <c r="AF47" s="13"/>
       <c r="AG47" s="4"/>
-      <c r="AH47" s="13"/>
-      <c r="AI47" s="13"/>
-      <c r="AJ47" s="13"/>
+      <c r="AH47" s="6"/>
+      <c r="AI47" s="6"/>
+      <c r="AJ47" s="6"/>
       <c r="AK47" s="13"/>
-      <c r="AL47" s="6"/>
-      <c r="AM47" s="6"/>
-      <c r="AN47" s="6"/>
-      <c r="AO47" s="6"/>
-      <c r="AP47" s="6"/>
+      <c r="AL47" s="13"/>
+      <c r="AM47" s="13"/>
+      <c r="AN47" s="13"/>
+      <c r="AO47" s="13"/>
+      <c r="AP47" s="13"/>
       <c r="AQ47" s="6"/>
       <c r="AR47" s="6"/>
       <c r="AS47" s="6"/>
       <c r="AT47" s="4"/>
       <c r="AU47" s="4"/>
       <c r="AV47" s="6"/>
-      <c r="AW47" s="13"/>
+      <c r="AW47" s="6"/>
       <c r="AX47" s="13"/>
       <c r="AY47" s="13"/>
       <c r="AZ47" s="13"/>
@@ -4709,31 +4683,31 @@
       <c r="BD47" s="4"/>
     </row>
     <row r="48" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A48" s="17" t="s">
+      <c r="A48" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="B48" s="28">
+        <v>3</v>
+      </c>
+      <c r="C48" s="29">
+        <f>SUM(AI48:AJ48,AK48)</f>
+        <v>11.399999999999999</v>
+      </c>
+      <c r="D48" s="18">
+        <v>46097</v>
+      </c>
+      <c r="E48" s="18">
+        <v>46134</v>
+      </c>
+      <c r="F48" s="11" t="s">
         <v>22</v>
-      </c>
-      <c r="B48" s="18">
-        <v>3</v>
-      </c>
-      <c r="C48" s="19">
-        <f>SUM(AQ48:AR48)</f>
-        <v>126</v>
-      </c>
-      <c r="D48" s="21">
-        <v>46097</v>
-      </c>
-      <c r="E48" s="21">
-        <v>46134</v>
-      </c>
-      <c r="F48" s="11" t="s">
-        <v>24</v>
       </c>
       <c r="G48" s="13"/>
       <c r="H48" s="13"/>
       <c r="I48" s="13"/>
       <c r="J48" s="13"/>
       <c r="K48" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L48" s="13"/>
       <c r="M48" s="13"/>
@@ -4757,32 +4731,34 @@
       <c r="AE48" s="13"/>
       <c r="AF48" s="13"/>
       <c r="AG48" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AH48" s="13"/>
-      <c r="AI48" s="13"/>
-      <c r="AJ48" s="13"/>
-      <c r="AK48" s="13"/>
-      <c r="AL48" s="13"/>
+        <v>19</v>
+      </c>
+      <c r="AH48" s="9"/>
+      <c r="AI48" s="7">
+        <v>3.8</v>
+      </c>
+      <c r="AJ48" s="7">
+        <v>3.8</v>
+      </c>
+      <c r="AK48" s="7">
+        <v>3.8</v>
+      </c>
+      <c r="AL48" s="6"/>
       <c r="AM48" s="13"/>
       <c r="AN48" s="13"/>
       <c r="AO48" s="13"/>
       <c r="AP48" s="13"/>
-      <c r="AQ48" s="7">
-        <v>63</v>
-      </c>
-      <c r="AR48" s="7">
-        <v>63</v>
-      </c>
-      <c r="AS48" s="4"/>
+      <c r="AQ48" s="6"/>
+      <c r="AR48" s="6"/>
+      <c r="AS48" s="6"/>
       <c r="AT48" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU48" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AV48" s="4"/>
-      <c r="AW48" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="AV48" s="6"/>
+      <c r="AW48" s="6"/>
       <c r="AX48" s="13"/>
       <c r="AY48" s="13"/>
       <c r="AZ48" s="13"/>
@@ -4790,17 +4766,17 @@
       <c r="BB48" s="13"/>
       <c r="BC48" s="13"/>
       <c r="BD48" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A49" s="17"/>
-      <c r="B49" s="18"/>
-      <c r="C49" s="20"/>
-      <c r="D49" s="22"/>
-      <c r="E49" s="22"/>
+      <c r="A49" s="15"/>
+      <c r="B49" s="28"/>
+      <c r="C49" s="30"/>
+      <c r="D49" s="19"/>
+      <c r="E49" s="19"/>
       <c r="F49" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G49" s="13"/>
       <c r="H49" s="13"/>
@@ -4829,22 +4805,22 @@
       <c r="AE49" s="13"/>
       <c r="AF49" s="13"/>
       <c r="AG49" s="4"/>
-      <c r="AH49" s="13"/>
-      <c r="AI49" s="13"/>
-      <c r="AJ49" s="13"/>
-      <c r="AK49" s="13"/>
-      <c r="AL49" s="13"/>
+      <c r="AH49" s="6"/>
+      <c r="AI49" s="6"/>
+      <c r="AJ49" s="6"/>
+      <c r="AK49" s="6"/>
+      <c r="AL49" s="6"/>
       <c r="AM49" s="13"/>
       <c r="AN49" s="13"/>
       <c r="AO49" s="13"/>
       <c r="AP49" s="13"/>
-      <c r="AQ49" s="4"/>
-      <c r="AR49" s="4"/>
-      <c r="AS49" s="4"/>
+      <c r="AQ49" s="6"/>
+      <c r="AR49" s="6"/>
+      <c r="AS49" s="6"/>
       <c r="AT49" s="4"/>
       <c r="AU49" s="4"/>
-      <c r="AV49" s="4"/>
-      <c r="AW49" s="4"/>
+      <c r="AV49" s="6"/>
+      <c r="AW49" s="6"/>
       <c r="AX49" s="13"/>
       <c r="AY49" s="13"/>
       <c r="AZ49" s="13"/>
@@ -4854,31 +4830,31 @@
       <c r="BD49" s="4"/>
     </row>
     <row r="50" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A50" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B50" s="18">
+      <c r="A50" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="B50" s="28">
         <v>3</v>
       </c>
-      <c r="C50" s="19">
-        <f>SUM(AQ50:AR50)</f>
-        <v>126</v>
-      </c>
-      <c r="D50" s="21">
+      <c r="C50" s="29">
+        <f>SUM(AJ50:AM50)</f>
+        <v>63</v>
+      </c>
+      <c r="D50" s="18">
         <v>46097</v>
       </c>
-      <c r="E50" s="21">
+      <c r="E50" s="18">
         <v>46134</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G50" s="13"/>
       <c r="H50" s="13"/>
       <c r="I50" s="13"/>
       <c r="J50" s="13"/>
       <c r="K50" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L50" s="13"/>
       <c r="M50" s="13"/>
@@ -4902,32 +4878,36 @@
       <c r="AE50" s="13"/>
       <c r="AF50" s="13"/>
       <c r="AG50" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AH50" s="13"/>
-      <c r="AI50" s="13"/>
-      <c r="AJ50" s="13"/>
-      <c r="AK50" s="13"/>
-      <c r="AL50" s="13"/>
-      <c r="AM50" s="13"/>
+        <v>19</v>
+      </c>
+      <c r="AH50" s="6"/>
+      <c r="AI50" s="6"/>
+      <c r="AJ50" s="10">
+        <v>15.75</v>
+      </c>
+      <c r="AK50" s="10">
+        <v>15.75</v>
+      </c>
+      <c r="AL50" s="10">
+        <v>15.75</v>
+      </c>
+      <c r="AM50" s="10">
+        <v>15.75</v>
+      </c>
       <c r="AN50" s="13"/>
       <c r="AO50" s="13"/>
       <c r="AP50" s="13"/>
-      <c r="AQ50" s="7">
-        <v>63</v>
-      </c>
-      <c r="AR50" s="7">
-        <v>63</v>
-      </c>
-      <c r="AS50" s="4"/>
+      <c r="AQ50" s="6"/>
+      <c r="AR50" s="6"/>
+      <c r="AS50" s="6"/>
       <c r="AT50" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU50" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AV50" s="4"/>
-      <c r="AW50" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="AV50" s="6"/>
+      <c r="AW50" s="6"/>
       <c r="AX50" s="13"/>
       <c r="AY50" s="13"/>
       <c r="AZ50" s="13"/>
@@ -4935,17 +4915,17 @@
       <c r="BB50" s="13"/>
       <c r="BC50" s="13"/>
       <c r="BD50" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A51" s="17"/>
-      <c r="B51" s="18"/>
-      <c r="C51" s="20"/>
-      <c r="D51" s="22"/>
-      <c r="E51" s="22"/>
+      <c r="A51" s="15"/>
+      <c r="B51" s="28"/>
+      <c r="C51" s="30"/>
+      <c r="D51" s="19"/>
+      <c r="E51" s="19"/>
       <c r="F51" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G51" s="13"/>
       <c r="H51" s="13"/>
@@ -4977,19 +4957,19 @@
       <c r="AH51" s="13"/>
       <c r="AI51" s="13"/>
       <c r="AJ51" s="13"/>
-      <c r="AK51" s="13"/>
-      <c r="AL51" s="13"/>
+      <c r="AK51" s="6"/>
+      <c r="AL51" s="6"/>
       <c r="AM51" s="13"/>
       <c r="AN51" s="13"/>
       <c r="AO51" s="13"/>
       <c r="AP51" s="13"/>
-      <c r="AQ51" s="4"/>
-      <c r="AR51" s="4"/>
-      <c r="AS51" s="4"/>
+      <c r="AQ51" s="13"/>
+      <c r="AR51" s="13"/>
+      <c r="AS51" s="13"/>
       <c r="AT51" s="4"/>
       <c r="AU51" s="4"/>
-      <c r="AV51" s="4"/>
-      <c r="AW51" s="4"/>
+      <c r="AV51" s="6"/>
+      <c r="AW51" s="6"/>
       <c r="AX51" s="13"/>
       <c r="AY51" s="13"/>
       <c r="AZ51" s="13"/>
@@ -4999,31 +4979,31 @@
       <c r="BD51" s="4"/>
     </row>
     <row r="52" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A52" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B52" s="18">
+      <c r="A52" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C52" s="19">
-        <f>SUM(AQ52:AS52)</f>
-        <v>75.599999999999994</v>
-      </c>
-      <c r="D52" s="21">
+      <c r="B52" s="28">
+        <v>3</v>
+      </c>
+      <c r="C52" s="29">
+        <f>SUM(AM52)</f>
+        <v>1</v>
+      </c>
+      <c r="D52" s="18">
         <v>46097</v>
       </c>
-      <c r="E52" s="21">
+      <c r="E52" s="18">
         <v>46134</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G52" s="13"/>
       <c r="H52" s="13"/>
       <c r="I52" s="13"/>
       <c r="J52" s="13"/>
       <c r="K52" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L52" s="13"/>
       <c r="M52" s="13"/>
@@ -5047,31 +5027,27 @@
       <c r="AE52" s="13"/>
       <c r="AF52" s="13"/>
       <c r="AG52" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AH52" s="13"/>
       <c r="AI52" s="13"/>
       <c r="AJ52" s="13"/>
       <c r="AK52" s="13"/>
       <c r="AL52" s="13"/>
-      <c r="AM52" s="13"/>
+      <c r="AM52" s="10">
+        <v>1</v>
+      </c>
       <c r="AN52" s="13"/>
       <c r="AO52" s="13"/>
       <c r="AP52" s="13"/>
-      <c r="AQ52" s="7">
-        <v>25.2</v>
-      </c>
-      <c r="AR52" s="7">
-        <v>25.2</v>
-      </c>
-      <c r="AS52" s="7">
-        <v>25.2</v>
-      </c>
+      <c r="AQ52" s="13"/>
+      <c r="AR52" s="13"/>
+      <c r="AS52" s="13"/>
       <c r="AT52" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU52" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AV52" s="6"/>
       <c r="AW52" s="6"/>
@@ -5082,17 +5058,17 @@
       <c r="BB52" s="13"/>
       <c r="BC52" s="13"/>
       <c r="BD52" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A53" s="17"/>
-      <c r="B53" s="18"/>
-      <c r="C53" s="20"/>
-      <c r="D53" s="22"/>
-      <c r="E53" s="22"/>
+      <c r="A53" s="15"/>
+      <c r="B53" s="28"/>
+      <c r="C53" s="30"/>
+      <c r="D53" s="19"/>
+      <c r="E53" s="19"/>
       <c r="F53" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G53" s="13"/>
       <c r="H53" s="13"/>
@@ -5124,15 +5100,15 @@
       <c r="AH53" s="13"/>
       <c r="AI53" s="13"/>
       <c r="AJ53" s="13"/>
-      <c r="AK53" s="13"/>
-      <c r="AL53" s="13"/>
+      <c r="AK53" s="6"/>
+      <c r="AL53" s="6"/>
       <c r="AM53" s="13"/>
       <c r="AN53" s="13"/>
       <c r="AO53" s="13"/>
       <c r="AP53" s="13"/>
-      <c r="AQ53" s="6"/>
-      <c r="AR53" s="6"/>
-      <c r="AS53" s="6"/>
+      <c r="AQ53" s="13"/>
+      <c r="AR53" s="13"/>
+      <c r="AS53" s="13"/>
       <c r="AT53" s="4"/>
       <c r="AU53" s="4"/>
       <c r="AV53" s="6"/>
@@ -5146,31 +5122,31 @@
       <c r="BD53" s="4"/>
     </row>
     <row r="54" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A54" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="B54" s="18">
+      <c r="A54" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B54" s="28">
         <v>3</v>
       </c>
-      <c r="C54" s="19">
-        <f>SUM(AR54:AS54,AV54)</f>
-        <v>11.399999999999999</v>
-      </c>
-      <c r="D54" s="21">
+      <c r="C54" s="29">
+        <f>SUM(AK54:AN54)</f>
+        <v>55</v>
+      </c>
+      <c r="D54" s="18">
         <v>46097</v>
       </c>
-      <c r="E54" s="21">
+      <c r="E54" s="18">
         <v>46134</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G54" s="13"/>
       <c r="H54" s="13"/>
       <c r="I54" s="13"/>
       <c r="J54" s="13"/>
       <c r="K54" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L54" s="13"/>
       <c r="M54" s="13"/>
@@ -5194,33 +5170,33 @@
       <c r="AE54" s="13"/>
       <c r="AF54" s="13"/>
       <c r="AG54" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AH54" s="13"/>
       <c r="AI54" s="13"/>
       <c r="AJ54" s="13"/>
-      <c r="AK54" s="13"/>
-      <c r="AL54" s="13"/>
-      <c r="AM54" s="13"/>
+      <c r="AK54" s="10">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="AL54" s="10">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="AM54" s="10">
+        <v>18.2</v>
+      </c>
       <c r="AN54" s="13"/>
       <c r="AO54" s="13"/>
       <c r="AP54" s="13"/>
-      <c r="AQ54" s="9"/>
-      <c r="AR54" s="7">
-        <v>3.8</v>
-      </c>
-      <c r="AS54" s="7">
-        <v>3.8</v>
-      </c>
+      <c r="AQ54" s="13"/>
+      <c r="AR54" s="13"/>
+      <c r="AS54" s="13"/>
       <c r="AT54" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU54" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AV54" s="7">
-        <v>3.8</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="AV54" s="6"/>
       <c r="AW54" s="6"/>
       <c r="AX54" s="13"/>
       <c r="AY54" s="13"/>
@@ -5229,17 +5205,17 @@
       <c r="BB54" s="13"/>
       <c r="BC54" s="13"/>
       <c r="BD54" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A55" s="17"/>
-      <c r="B55" s="18"/>
-      <c r="C55" s="20"/>
-      <c r="D55" s="22"/>
-      <c r="E55" s="22"/>
+      <c r="A55" s="15"/>
+      <c r="B55" s="28"/>
+      <c r="C55" s="30"/>
+      <c r="D55" s="19"/>
+      <c r="E55" s="19"/>
       <c r="F55" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G55" s="13"/>
       <c r="H55" s="13"/>
@@ -5271,15 +5247,15 @@
       <c r="AH55" s="13"/>
       <c r="AI55" s="13"/>
       <c r="AJ55" s="13"/>
-      <c r="AK55" s="13"/>
-      <c r="AL55" s="13"/>
+      <c r="AK55" s="6"/>
+      <c r="AL55" s="6"/>
       <c r="AM55" s="13"/>
       <c r="AN55" s="13"/>
       <c r="AO55" s="13"/>
       <c r="AP55" s="13"/>
-      <c r="AQ55" s="6"/>
-      <c r="AR55" s="6"/>
-      <c r="AS55" s="6"/>
+      <c r="AQ55" s="13"/>
+      <c r="AR55" s="13"/>
+      <c r="AS55" s="13"/>
       <c r="AT55" s="4"/>
       <c r="AU55" s="4"/>
       <c r="AV55" s="6"/>
@@ -5293,31 +5269,31 @@
       <c r="BD55" s="4"/>
     </row>
     <row r="56" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A56" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="B56" s="18">
+      <c r="A56" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B56" s="28">
         <v>3</v>
       </c>
-      <c r="C56" s="19">
-        <f>SUM(AV56:AW56,AS56)</f>
-        <v>11.399999999999999</v>
-      </c>
-      <c r="D56" s="21">
+      <c r="C56" s="29">
+        <f>SUM(AM56:AO56)</f>
+        <v>126</v>
+      </c>
+      <c r="D56" s="18">
         <v>46097</v>
       </c>
-      <c r="E56" s="21">
+      <c r="E56" s="18">
         <v>46134</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G56" s="13"/>
       <c r="H56" s="13"/>
       <c r="I56" s="13"/>
       <c r="J56" s="13"/>
       <c r="K56" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L56" s="13"/>
       <c r="M56" s="13"/>
@@ -5341,34 +5317,34 @@
       <c r="AE56" s="13"/>
       <c r="AF56" s="13"/>
       <c r="AG56" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AH56" s="13"/>
       <c r="AI56" s="13"/>
       <c r="AJ56" s="13"/>
-      <c r="AK56" s="13"/>
-      <c r="AL56" s="13"/>
-      <c r="AM56" s="13"/>
-      <c r="AN56" s="13"/>
-      <c r="AO56" s="13"/>
+      <c r="AK56" s="6"/>
+      <c r="AL56" s="6"/>
+      <c r="AM56" s="10">
+        <v>42</v>
+      </c>
+      <c r="AN56" s="10">
+        <v>42</v>
+      </c>
+      <c r="AO56" s="10">
+        <v>42</v>
+      </c>
       <c r="AP56" s="13"/>
-      <c r="AQ56" s="9"/>
-      <c r="AR56" s="9"/>
-      <c r="AS56" s="7">
-        <v>3.8</v>
-      </c>
+      <c r="AQ56" s="13"/>
+      <c r="AR56" s="13"/>
+      <c r="AS56" s="13"/>
       <c r="AT56" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU56" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AV56" s="7">
-        <v>3.8</v>
-      </c>
-      <c r="AW56" s="7">
-        <v>3.8</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="AV56" s="6"/>
+      <c r="AW56" s="6"/>
       <c r="AX56" s="13"/>
       <c r="AY56" s="13"/>
       <c r="AZ56" s="13"/>
@@ -5376,17 +5352,17 @@
       <c r="BB56" s="13"/>
       <c r="BC56" s="13"/>
       <c r="BD56" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A57" s="17"/>
-      <c r="B57" s="18"/>
-      <c r="C57" s="20"/>
-      <c r="D57" s="22"/>
-      <c r="E57" s="22"/>
+      <c r="A57" s="15"/>
+      <c r="B57" s="28"/>
+      <c r="C57" s="30"/>
+      <c r="D57" s="19"/>
+      <c r="E57" s="19"/>
       <c r="F57" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G57" s="13"/>
       <c r="H57" s="13"/>
@@ -5440,31 +5416,31 @@
       <c r="BD57" s="4"/>
     </row>
     <row r="58" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A58" s="17" t="s">
+      <c r="A58" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="B58" s="28">
         <v>3</v>
       </c>
-      <c r="B58" s="18">
-        <v>3</v>
-      </c>
-      <c r="C58" s="19">
-        <f>SUM(AV58:AW58,AS58)</f>
-        <v>63</v>
-      </c>
-      <c r="D58" s="21">
+      <c r="C58" s="29">
+        <f>SUM(AS58)</f>
+        <v>126</v>
+      </c>
+      <c r="D58" s="18">
         <v>46097</v>
       </c>
-      <c r="E58" s="21">
+      <c r="E58" s="18">
         <v>46134</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G58" s="13"/>
       <c r="H58" s="13"/>
       <c r="I58" s="13"/>
       <c r="J58" s="13"/>
       <c r="K58" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L58" s="13"/>
       <c r="M58" s="13"/>
@@ -5488,7 +5464,7 @@
       <c r="AE58" s="13"/>
       <c r="AF58" s="13"/>
       <c r="AG58" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AH58" s="13"/>
       <c r="AI58" s="13"/>
@@ -5497,25 +5473,20 @@
       <c r="AL58" s="13"/>
       <c r="AM58" s="13"/>
       <c r="AN58" s="13"/>
-      <c r="AO58" s="13"/>
-      <c r="AP58" s="13"/>
-      <c r="AQ58" s="6"/>
-      <c r="AR58" s="6"/>
+      <c r="AO58" s="6"/>
+      <c r="AQ58" s="13"/>
+      <c r="AR58" s="13"/>
       <c r="AS58" s="10">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="AT58" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU58" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AV58" s="10">
-        <v>21</v>
-      </c>
-      <c r="AW58" s="10">
-        <v>21</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="AV58" s="6"/>
+      <c r="AW58" s="6"/>
       <c r="AX58" s="13"/>
       <c r="AY58" s="13"/>
       <c r="AZ58" s="13"/>
@@ -5523,17 +5494,17 @@
       <c r="BB58" s="13"/>
       <c r="BC58" s="13"/>
       <c r="BD58" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="59" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A59" s="17"/>
-      <c r="B59" s="18"/>
-      <c r="C59" s="20"/>
-      <c r="D59" s="22"/>
-      <c r="E59" s="22"/>
+      <c r="A59" s="15"/>
+      <c r="B59" s="28"/>
+      <c r="C59" s="30"/>
+      <c r="D59" s="19"/>
+      <c r="E59" s="19"/>
       <c r="F59" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G59" s="13"/>
       <c r="H59" s="13"/>
@@ -5571,13 +5542,13 @@
       <c r="AN59" s="13"/>
       <c r="AO59" s="13"/>
       <c r="AP59" s="13"/>
-      <c r="AQ59" s="6"/>
-      <c r="AR59" s="6"/>
-      <c r="AS59" s="6"/>
+      <c r="AQ59" s="13"/>
+      <c r="AR59" s="13"/>
+      <c r="AS59" s="13"/>
       <c r="AT59" s="4"/>
       <c r="AU59" s="4"/>
       <c r="AV59" s="6"/>
-      <c r="AW59" s="6"/>
+      <c r="AW59" s="13"/>
       <c r="AX59" s="13"/>
       <c r="AY59" s="13"/>
       <c r="AZ59" s="13"/>
@@ -5586,750 +5557,133 @@
       <c r="BC59" s="13"/>
       <c r="BD59" s="4"/>
     </row>
-    <row r="60" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A60" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="B60" s="18">
-        <v>3</v>
-      </c>
-      <c r="C60" s="19">
-        <f>SUM(AV60:AW60,AS60)</f>
-        <v>63</v>
-      </c>
-      <c r="D60" s="21">
-        <v>46097</v>
-      </c>
-      <c r="E60" s="21">
-        <v>46134</v>
-      </c>
-      <c r="F60" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G60" s="13"/>
-      <c r="H60" s="13"/>
-      <c r="I60" s="13"/>
-      <c r="J60" s="13"/>
-      <c r="K60" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="L60" s="13"/>
-      <c r="M60" s="13"/>
-      <c r="N60" s="13"/>
-      <c r="O60" s="13"/>
-      <c r="P60" s="13"/>
-      <c r="Q60" s="13"/>
-      <c r="R60" s="13"/>
-      <c r="S60" s="13"/>
-      <c r="T60" s="13"/>
-      <c r="U60" s="13"/>
-      <c r="V60" s="13"/>
-      <c r="W60" s="13"/>
-      <c r="X60" s="13"/>
-      <c r="Y60" s="13"/>
-      <c r="Z60" s="13"/>
-      <c r="AA60" s="13"/>
-      <c r="AB60" s="13"/>
-      <c r="AC60" s="13"/>
-      <c r="AD60" s="13"/>
-      <c r="AE60" s="13"/>
-      <c r="AF60" s="13"/>
-      <c r="AG60" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AH60" s="13"/>
-      <c r="AI60" s="13"/>
-      <c r="AJ60" s="13"/>
-      <c r="AK60" s="13"/>
-      <c r="AL60" s="13"/>
-      <c r="AM60" s="13"/>
-      <c r="AN60" s="13"/>
-      <c r="AO60" s="13"/>
-      <c r="AP60" s="13"/>
-      <c r="AQ60" s="6"/>
-      <c r="AR60" s="6"/>
-      <c r="AS60" s="10">
-        <v>21</v>
-      </c>
-      <c r="AT60" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AU60" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AV60" s="10">
-        <v>21</v>
-      </c>
-      <c r="AW60" s="10">
-        <v>21</v>
-      </c>
-      <c r="AX60" s="13"/>
-      <c r="AY60" s="13"/>
-      <c r="AZ60" s="13"/>
-      <c r="BA60" s="13"/>
-      <c r="BB60" s="13"/>
-      <c r="BC60" s="13"/>
-      <c r="BD60" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="61" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A61" s="17"/>
-      <c r="B61" s="18"/>
-      <c r="C61" s="20"/>
-      <c r="D61" s="22"/>
-      <c r="E61" s="22"/>
-      <c r="F61" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="G61" s="13"/>
-      <c r="H61" s="13"/>
-      <c r="I61" s="13"/>
-      <c r="J61" s="13"/>
-      <c r="K61" s="4"/>
-      <c r="L61" s="13"/>
-      <c r="M61" s="13"/>
-      <c r="N61" s="13"/>
-      <c r="O61" s="13"/>
-      <c r="P61" s="13"/>
-      <c r="Q61" s="13"/>
-      <c r="R61" s="13"/>
-      <c r="S61" s="13"/>
-      <c r="T61" s="13"/>
-      <c r="U61" s="13"/>
-      <c r="V61" s="13"/>
-      <c r="W61" s="13"/>
-      <c r="X61" s="13"/>
-      <c r="Y61" s="13"/>
-      <c r="Z61" s="13"/>
-      <c r="AA61" s="13"/>
-      <c r="AB61" s="13"/>
-      <c r="AC61" s="13"/>
-      <c r="AD61" s="13"/>
-      <c r="AE61" s="13"/>
-      <c r="AF61" s="13"/>
-      <c r="AG61" s="4"/>
-      <c r="AH61" s="13"/>
-      <c r="AI61" s="13"/>
-      <c r="AJ61" s="13"/>
-      <c r="AK61" s="13"/>
-      <c r="AL61" s="13"/>
-      <c r="AM61" s="13"/>
-      <c r="AN61" s="6"/>
-      <c r="AO61" s="6"/>
-      <c r="AP61" s="6"/>
-      <c r="AQ61" s="13"/>
-      <c r="AR61" s="13"/>
-      <c r="AS61" s="13"/>
-      <c r="AT61" s="4"/>
-      <c r="AU61" s="4"/>
-      <c r="AV61" s="6"/>
-      <c r="AW61" s="6"/>
-      <c r="AX61" s="13"/>
-      <c r="AY61" s="13"/>
-      <c r="AZ61" s="13"/>
-      <c r="BA61" s="13"/>
-      <c r="BB61" s="13"/>
-      <c r="BC61" s="13"/>
-      <c r="BD61" s="4"/>
-    </row>
-    <row r="62" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A62" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="B62" s="18">
-        <v>3</v>
-      </c>
-      <c r="C62" s="19">
-        <f>SUM(AW62)</f>
-        <v>1</v>
-      </c>
-      <c r="D62" s="21">
-        <v>46097</v>
-      </c>
-      <c r="E62" s="21">
-        <v>46134</v>
-      </c>
-      <c r="F62" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G62" s="13"/>
-      <c r="H62" s="13"/>
-      <c r="I62" s="13"/>
-      <c r="J62" s="13"/>
-      <c r="K62" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="L62" s="13"/>
-      <c r="M62" s="13"/>
-      <c r="N62" s="13"/>
-      <c r="O62" s="13"/>
-      <c r="P62" s="13"/>
-      <c r="Q62" s="13"/>
-      <c r="R62" s="13"/>
-      <c r="S62" s="13"/>
-      <c r="T62" s="13"/>
-      <c r="U62" s="13"/>
-      <c r="V62" s="13"/>
-      <c r="W62" s="13"/>
-      <c r="X62" s="13"/>
-      <c r="Y62" s="13"/>
-      <c r="Z62" s="13"/>
-      <c r="AA62" s="13"/>
-      <c r="AB62" s="13"/>
-      <c r="AC62" s="13"/>
-      <c r="AD62" s="13"/>
-      <c r="AE62" s="13"/>
-      <c r="AF62" s="13"/>
-      <c r="AG62" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AH62" s="13"/>
-      <c r="AI62" s="13"/>
-      <c r="AJ62" s="13"/>
-      <c r="AK62" s="13"/>
-      <c r="AL62" s="13"/>
-      <c r="AM62" s="13"/>
-      <c r="AN62" s="6"/>
-      <c r="AO62" s="6"/>
-      <c r="AP62" s="6"/>
-      <c r="AQ62" s="13"/>
-      <c r="AR62" s="13"/>
-      <c r="AS62" s="13"/>
-      <c r="AT62" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AU62" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AW62" s="10">
-        <v>1</v>
-      </c>
-      <c r="AX62" s="13"/>
-      <c r="AY62" s="13"/>
-      <c r="AZ62" s="13"/>
-      <c r="BA62" s="13"/>
-      <c r="BB62" s="13"/>
-      <c r="BC62" s="13"/>
-      <c r="BD62" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="63" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A63" s="17"/>
-      <c r="B63" s="18"/>
-      <c r="C63" s="20"/>
-      <c r="D63" s="22"/>
-      <c r="E63" s="22"/>
-      <c r="F63" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="G63" s="13"/>
-      <c r="H63" s="13"/>
-      <c r="I63" s="13"/>
-      <c r="J63" s="13"/>
-      <c r="K63" s="4"/>
-      <c r="L63" s="13"/>
-      <c r="M63" s="13"/>
-      <c r="N63" s="13"/>
-      <c r="O63" s="13"/>
-      <c r="P63" s="13"/>
-      <c r="Q63" s="13"/>
-      <c r="R63" s="13"/>
-      <c r="S63" s="13"/>
-      <c r="T63" s="13"/>
-      <c r="U63" s="13"/>
-      <c r="V63" s="13"/>
-      <c r="W63" s="13"/>
-      <c r="X63" s="13"/>
-      <c r="Y63" s="13"/>
-      <c r="Z63" s="13"/>
-      <c r="AA63" s="13"/>
-      <c r="AB63" s="13"/>
-      <c r="AC63" s="13"/>
-      <c r="AD63" s="13"/>
-      <c r="AE63" s="13"/>
-      <c r="AF63" s="13"/>
-      <c r="AG63" s="4"/>
-      <c r="AH63" s="13"/>
-      <c r="AI63" s="13"/>
-      <c r="AJ63" s="13"/>
-      <c r="AK63" s="13"/>
-      <c r="AL63" s="13"/>
-      <c r="AM63" s="13"/>
-      <c r="AN63" s="6"/>
-      <c r="AO63" s="6"/>
-      <c r="AP63" s="6"/>
-      <c r="AQ63" s="13"/>
-      <c r="AR63" s="13"/>
-      <c r="AS63" s="13"/>
-      <c r="AT63" s="4"/>
-      <c r="AU63" s="4"/>
-      <c r="AV63" s="6"/>
-      <c r="AW63" s="6"/>
-      <c r="AX63" s="13"/>
-      <c r="AY63" s="13"/>
-      <c r="AZ63" s="13"/>
-      <c r="BA63" s="13"/>
-      <c r="BB63" s="13"/>
-      <c r="BC63" s="13"/>
-      <c r="BD63" s="4"/>
-    </row>
-    <row r="64" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A64" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="B64" s="18">
-        <v>3</v>
-      </c>
-      <c r="C64" s="19">
-        <f>SUM(AV64:AX64)</f>
-        <v>55</v>
-      </c>
-      <c r="D64" s="21">
-        <v>46097</v>
-      </c>
-      <c r="E64" s="21">
-        <v>46134</v>
-      </c>
-      <c r="F64" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G64" s="13"/>
-      <c r="H64" s="13"/>
-      <c r="I64" s="13"/>
-      <c r="J64" s="13"/>
-      <c r="K64" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="L64" s="13"/>
-      <c r="M64" s="13"/>
-      <c r="N64" s="13"/>
-      <c r="O64" s="13"/>
-      <c r="P64" s="13"/>
-      <c r="Q64" s="13"/>
-      <c r="R64" s="13"/>
-      <c r="S64" s="13"/>
-      <c r="T64" s="13"/>
-      <c r="U64" s="13"/>
-      <c r="V64" s="13"/>
-      <c r="W64" s="13"/>
-      <c r="X64" s="13"/>
-      <c r="Y64" s="13"/>
-      <c r="Z64" s="13"/>
-      <c r="AA64" s="13"/>
-      <c r="AB64" s="13"/>
-      <c r="AC64" s="13"/>
-      <c r="AD64" s="13"/>
-      <c r="AE64" s="13"/>
-      <c r="AF64" s="13"/>
-      <c r="AG64" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AH64" s="13"/>
-      <c r="AI64" s="13"/>
-      <c r="AJ64" s="13"/>
-      <c r="AK64" s="13"/>
-      <c r="AL64" s="13"/>
-      <c r="AM64" s="13"/>
-      <c r="AN64" s="6"/>
-      <c r="AO64" s="6"/>
-      <c r="AP64" s="6"/>
-      <c r="AQ64" s="13"/>
-      <c r="AR64" s="13"/>
-      <c r="AS64" s="13"/>
-      <c r="AT64" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AU64" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AV64" s="10">
-        <v>19</v>
-      </c>
-      <c r="AW64" s="10">
-        <v>18</v>
-      </c>
-      <c r="AX64" s="10">
-        <v>18</v>
-      </c>
-      <c r="AY64" s="13"/>
-      <c r="AZ64" s="13"/>
-      <c r="BA64" s="13"/>
-      <c r="BB64" s="13"/>
-      <c r="BC64" s="13"/>
-      <c r="BD64" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="65" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A65" s="17"/>
-      <c r="B65" s="18"/>
-      <c r="C65" s="20"/>
-      <c r="D65" s="22"/>
-      <c r="E65" s="22"/>
-      <c r="F65" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="G65" s="13"/>
-      <c r="H65" s="13"/>
-      <c r="I65" s="13"/>
-      <c r="J65" s="13"/>
-      <c r="K65" s="4"/>
-      <c r="L65" s="13"/>
-      <c r="M65" s="13"/>
-      <c r="N65" s="13"/>
-      <c r="O65" s="13"/>
-      <c r="P65" s="13"/>
-      <c r="Q65" s="13"/>
-      <c r="R65" s="13"/>
-      <c r="S65" s="13"/>
-      <c r="T65" s="13"/>
-      <c r="U65" s="13"/>
-      <c r="V65" s="13"/>
-      <c r="W65" s="13"/>
-      <c r="X65" s="13"/>
-      <c r="Y65" s="13"/>
-      <c r="Z65" s="13"/>
-      <c r="AA65" s="13"/>
-      <c r="AB65" s="13"/>
-      <c r="AC65" s="13"/>
-      <c r="AD65" s="13"/>
-      <c r="AE65" s="13"/>
-      <c r="AF65" s="13"/>
-      <c r="AG65" s="4"/>
-      <c r="AH65" s="13"/>
-      <c r="AI65" s="13"/>
-      <c r="AJ65" s="13"/>
-      <c r="AK65" s="13"/>
-      <c r="AL65" s="13"/>
-      <c r="AM65" s="13"/>
-      <c r="AN65" s="6"/>
-      <c r="AO65" s="6"/>
-      <c r="AP65" s="6"/>
-      <c r="AQ65" s="13"/>
-      <c r="AR65" s="13"/>
-      <c r="AS65" s="13"/>
-      <c r="AT65" s="4"/>
-      <c r="AU65" s="4"/>
-      <c r="AV65" s="6"/>
-      <c r="AW65" s="6"/>
-      <c r="AX65" s="13"/>
-      <c r="AY65" s="13"/>
-      <c r="AZ65" s="13"/>
-      <c r="BA65" s="13"/>
-      <c r="BB65" s="13"/>
-      <c r="BC65" s="13"/>
-      <c r="BD65" s="4"/>
-    </row>
-    <row r="66" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A66" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="B66" s="18">
-        <v>3</v>
-      </c>
-      <c r="C66" s="19">
-        <f>SUM(AW66:AX66)</f>
-        <v>126</v>
-      </c>
-      <c r="D66" s="21">
-        <v>46097</v>
-      </c>
-      <c r="E66" s="21">
-        <v>46134</v>
-      </c>
-      <c r="F66" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G66" s="13"/>
-      <c r="H66" s="13"/>
-      <c r="I66" s="13"/>
-      <c r="J66" s="13"/>
-      <c r="K66" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="L66" s="13"/>
-      <c r="M66" s="13"/>
-      <c r="N66" s="13"/>
-      <c r="O66" s="13"/>
-      <c r="P66" s="13"/>
-      <c r="Q66" s="13"/>
-      <c r="R66" s="13"/>
-      <c r="S66" s="13"/>
-      <c r="T66" s="13"/>
-      <c r="U66" s="13"/>
-      <c r="V66" s="13"/>
-      <c r="W66" s="13"/>
-      <c r="X66" s="13"/>
-      <c r="Y66" s="13"/>
-      <c r="Z66" s="13"/>
-      <c r="AA66" s="13"/>
-      <c r="AB66" s="13"/>
-      <c r="AC66" s="13"/>
-      <c r="AD66" s="13"/>
-      <c r="AE66" s="13"/>
-      <c r="AF66" s="13"/>
-      <c r="AG66" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AH66" s="13"/>
-      <c r="AI66" s="13"/>
-      <c r="AJ66" s="13"/>
-      <c r="AK66" s="13"/>
-      <c r="AL66" s="13"/>
-      <c r="AM66" s="13"/>
-      <c r="AN66" s="6"/>
-      <c r="AO66" s="6"/>
-      <c r="AP66" s="6"/>
-      <c r="AQ66" s="13"/>
-      <c r="AR66" s="13"/>
-      <c r="AS66" s="13"/>
-      <c r="AT66" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AU66" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AV66" s="6"/>
-      <c r="AW66" s="10">
-        <v>63</v>
-      </c>
-      <c r="AX66" s="10">
-        <v>63</v>
-      </c>
-      <c r="AY66" s="6"/>
-      <c r="AZ66" s="13"/>
-      <c r="BA66" s="13"/>
-      <c r="BB66" s="13"/>
-      <c r="BC66" s="13"/>
-      <c r="BD66" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="67" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A67" s="17"/>
-      <c r="B67" s="18"/>
-      <c r="C67" s="20"/>
-      <c r="D67" s="22"/>
-      <c r="E67" s="22"/>
-      <c r="F67" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="G67" s="13"/>
-      <c r="H67" s="13"/>
-      <c r="I67" s="13"/>
-      <c r="J67" s="13"/>
-      <c r="K67" s="4"/>
-      <c r="L67" s="13"/>
-      <c r="M67" s="13"/>
-      <c r="N67" s="13"/>
-      <c r="O67" s="13"/>
-      <c r="P67" s="13"/>
-      <c r="Q67" s="13"/>
-      <c r="R67" s="13"/>
-      <c r="S67" s="13"/>
-      <c r="T67" s="13"/>
-      <c r="U67" s="13"/>
-      <c r="V67" s="13"/>
-      <c r="W67" s="13"/>
-      <c r="X67" s="13"/>
-      <c r="Y67" s="13"/>
-      <c r="Z67" s="13"/>
-      <c r="AA67" s="13"/>
-      <c r="AB67" s="13"/>
-      <c r="AC67" s="13"/>
-      <c r="AD67" s="13"/>
-      <c r="AE67" s="13"/>
-      <c r="AF67" s="13"/>
-      <c r="AG67" s="4"/>
-      <c r="AH67" s="13"/>
-      <c r="AI67" s="13"/>
-      <c r="AJ67" s="13"/>
-      <c r="AK67" s="6"/>
-      <c r="AL67" s="6"/>
-      <c r="AM67" s="6"/>
-      <c r="AN67" s="6"/>
-      <c r="AO67" s="6"/>
-      <c r="AP67" s="6"/>
-      <c r="AQ67" s="6"/>
-      <c r="AR67" s="6"/>
-      <c r="AS67" s="6"/>
-      <c r="AT67" s="4"/>
-      <c r="AU67" s="4"/>
-      <c r="AV67" s="13"/>
-      <c r="AW67" s="13"/>
-      <c r="AX67" s="13"/>
-      <c r="AY67" s="13"/>
-      <c r="AZ67" s="13"/>
-      <c r="BA67" s="13"/>
-      <c r="BB67" s="13"/>
-      <c r="BC67" s="13"/>
-      <c r="BD67" s="4"/>
-    </row>
-    <row r="68" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A68" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="B68" s="18">
-        <v>3</v>
-      </c>
-      <c r="C68" s="19">
-        <f>SUM(BA68)</f>
-        <v>126</v>
-      </c>
-      <c r="D68" s="21">
-        <v>46097</v>
-      </c>
-      <c r="E68" s="21">
-        <v>46134</v>
-      </c>
-      <c r="F68" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G68" s="13"/>
-      <c r="H68" s="13"/>
-      <c r="I68" s="13"/>
-      <c r="J68" s="13"/>
-      <c r="K68" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="L68" s="13"/>
-      <c r="M68" s="13"/>
-      <c r="N68" s="13"/>
-      <c r="O68" s="13"/>
-      <c r="P68" s="13"/>
-      <c r="Q68" s="13"/>
-      <c r="R68" s="13"/>
-      <c r="S68" s="13"/>
-      <c r="T68" s="13"/>
-      <c r="U68" s="13"/>
-      <c r="V68" s="13"/>
-      <c r="W68" s="13"/>
-      <c r="X68" s="13"/>
-      <c r="Y68" s="13"/>
-      <c r="Z68" s="13"/>
-      <c r="AA68" s="13"/>
-      <c r="AB68" s="13"/>
-      <c r="AC68" s="13"/>
-      <c r="AD68" s="13"/>
-      <c r="AE68" s="13"/>
-      <c r="AF68" s="13"/>
-      <c r="AG68" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AH68" s="13"/>
-      <c r="AI68" s="13"/>
-      <c r="AJ68" s="13"/>
-      <c r="AK68" s="13"/>
-      <c r="AL68" s="13"/>
-      <c r="AM68" s="13"/>
-      <c r="AN68" s="13"/>
-      <c r="AO68" s="13"/>
-      <c r="AP68" s="13"/>
-      <c r="AQ68" s="13"/>
-      <c r="AR68" s="13"/>
-      <c r="AS68" s="13"/>
-      <c r="AT68" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AU68" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AV68" s="13"/>
-      <c r="AW68" s="13"/>
-      <c r="AX68" s="13"/>
-      <c r="AY68" s="13"/>
-      <c r="AZ68" s="6"/>
-      <c r="BA68" s="10">
-        <v>126</v>
-      </c>
-      <c r="BB68" s="13"/>
-      <c r="BC68" s="13"/>
-      <c r="BD68" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="69" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A69" s="17"/>
-      <c r="B69" s="18"/>
-      <c r="C69" s="20"/>
-      <c r="D69" s="22"/>
-      <c r="E69" s="22"/>
-      <c r="F69" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="G69" s="13"/>
-      <c r="H69" s="13"/>
-      <c r="I69" s="13"/>
-      <c r="J69" s="13"/>
-      <c r="K69" s="4"/>
-      <c r="L69" s="13"/>
-      <c r="M69" s="13"/>
-      <c r="N69" s="13"/>
-      <c r="O69" s="13"/>
-      <c r="P69" s="13"/>
-      <c r="Q69" s="13"/>
-      <c r="R69" s="13"/>
-      <c r="S69" s="13"/>
-      <c r="T69" s="13"/>
-      <c r="U69" s="13"/>
-      <c r="V69" s="13"/>
-      <c r="W69" s="13"/>
-      <c r="X69" s="13"/>
-      <c r="Y69" s="13"/>
-      <c r="Z69" s="13"/>
-      <c r="AA69" s="13"/>
-      <c r="AB69" s="13"/>
-      <c r="AC69" s="13"/>
-      <c r="AD69" s="13"/>
-      <c r="AE69" s="13"/>
-      <c r="AF69" s="13"/>
-      <c r="AG69" s="4"/>
-      <c r="AH69" s="13"/>
-      <c r="AI69" s="13"/>
-      <c r="AJ69" s="13"/>
-      <c r="AK69" s="13"/>
-      <c r="AL69" s="13"/>
-      <c r="AM69" s="13"/>
-      <c r="AN69" s="13"/>
-      <c r="AO69" s="13"/>
-      <c r="AP69" s="13"/>
-      <c r="AQ69" s="13"/>
-      <c r="AR69" s="13"/>
-      <c r="AS69" s="13"/>
-      <c r="AT69" s="4"/>
-      <c r="AU69" s="4"/>
-      <c r="AV69" s="6"/>
-      <c r="AW69" s="13"/>
-      <c r="AX69" s="13"/>
-      <c r="AY69" s="13"/>
-      <c r="AZ69" s="13"/>
-      <c r="BA69" s="13"/>
-      <c r="BB69" s="13"/>
-      <c r="BC69" s="13"/>
-      <c r="BD69" s="4"/>
-    </row>
   </sheetData>
-  <mergeCells count="180">
-    <mergeCell ref="AZ2:BD2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="Q2:V2"/>
-    <mergeCell ref="W2:AB2"/>
-    <mergeCell ref="G2:K2"/>
-    <mergeCell ref="L2:P2"/>
-    <mergeCell ref="AC2:AG2"/>
-    <mergeCell ref="AH2:AM2"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
+  <mergeCells count="155">
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="D56:D57"/>
+    <mergeCell ref="E56:E57"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="E52:E53"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="E54:E55"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="E50:E51"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="E48:E49"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="E44:E45"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="E46:E47"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="C6:C7"/>
@@ -6340,158 +5694,26 @@
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="E8:E9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="E44:E45"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="E46:E47"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="E48:E49"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="D50:D51"/>
-    <mergeCell ref="E50:E51"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="D52:D53"/>
-    <mergeCell ref="E52:E53"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="E58:E59"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="D60:D61"/>
-    <mergeCell ref="E60:E61"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="E54:E55"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="D56:D57"/>
-    <mergeCell ref="E56:E57"/>
     <mergeCell ref="AN2:AS2"/>
     <mergeCell ref="AT2:AY2"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="D66:D67"/>
-    <mergeCell ref="E66:E67"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="D68:D69"/>
-    <mergeCell ref="E68:E69"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="D62:D63"/>
-    <mergeCell ref="E62:E63"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="D64:D65"/>
-    <mergeCell ref="E64:E65"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="AZ2:BD2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="G2:K2"/>
+    <mergeCell ref="L2:P2"/>
+    <mergeCell ref="Q2:V2"/>
+    <mergeCell ref="W2:AB2"/>
+    <mergeCell ref="AC2:AG2"/>
+    <mergeCell ref="AH2:AM2"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Planejamento Previsto.xlsx
+++ b/Planejamento Previsto.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Viana e Moura\Downloads\Planejamento Emissário - LD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Viana e Moura\Desktop\Antigravity\Controle_Emissario_CA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{910CB5B8-F8E5-44B7-A170-28F454BD0672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F24A710-DE81-48A3-83D4-001A6B2E385A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EEA59E8E-9647-43AC-97C3-E8656E227CAD}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EEA59E8E-9647-43AC-97C3-E8656E227CAD}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan" sheetId="3" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="31">
   <si>
     <t>Escavação (m³)</t>
   </si>
@@ -120,6 +120,15 @@
   </si>
   <si>
     <t>Sondagem (und)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EQUIPE </t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
   </si>
 </sst>
 </file>
@@ -284,7 +293,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -313,22 +322,40 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -340,6 +367,9 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -349,19 +379,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -698,339 +719,344 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59AFFE89-FF8E-4E1D-AC6B-9E2FFA7EFAAA}">
-  <dimension ref="A2:BL59"/>
+  <dimension ref="A2:BM59"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.21875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="21" width="7" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7" customWidth="1"/>
-    <col min="23" max="27" width="7" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="7" customWidth="1"/>
-    <col min="29" max="30" width="7" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="8.21875" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="6.44140625" customWidth="1"/>
-    <col min="40" max="44" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="6.44140625" customWidth="1"/>
-    <col min="46" max="47" width="8.21875" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="49" max="55" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" customWidth="1"/>
+    <col min="5" max="6" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="22" width="7" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7" customWidth="1"/>
+    <col min="24" max="28" width="7" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="7" customWidth="1"/>
+    <col min="30" max="31" width="7" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="6.44140625" customWidth="1"/>
+    <col min="41" max="45" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="6.44140625" customWidth="1"/>
+    <col min="47" max="48" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="50" max="56" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="8.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A2" s="23" t="s">
+    <row r="2" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="A2" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="14"/>
+      <c r="E2" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="F2" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="G2" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="H2" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14" t="s">
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="14"/>
-      <c r="N2" s="14"/>
-      <c r="O2" s="14"/>
-      <c r="P2" s="14"/>
-      <c r="Q2" s="20" t="s">
+      <c r="N2" s="29"/>
+      <c r="O2" s="29"/>
+      <c r="P2" s="29"/>
+      <c r="Q2" s="29"/>
+      <c r="R2" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="R2" s="21"/>
-      <c r="S2" s="21"/>
-      <c r="T2" s="21"/>
-      <c r="U2" s="21"/>
-      <c r="V2" s="22"/>
-      <c r="W2" s="20" t="s">
+      <c r="S2" s="27"/>
+      <c r="T2" s="27"/>
+      <c r="U2" s="27"/>
+      <c r="V2" s="27"/>
+      <c r="W2" s="28"/>
+      <c r="X2" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="X2" s="21"/>
-      <c r="Y2" s="21"/>
-      <c r="Z2" s="21"/>
-      <c r="AA2" s="21"/>
-      <c r="AB2" s="22"/>
-      <c r="AC2" s="14" t="s">
+      <c r="Y2" s="27"/>
+      <c r="Z2" s="27"/>
+      <c r="AA2" s="27"/>
+      <c r="AB2" s="27"/>
+      <c r="AC2" s="28"/>
+      <c r="AD2" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="AD2" s="14"/>
-      <c r="AE2" s="14"/>
-      <c r="AF2" s="14"/>
-      <c r="AG2" s="14"/>
-      <c r="AH2" s="20" t="s">
+      <c r="AE2" s="29"/>
+      <c r="AF2" s="29"/>
+      <c r="AG2" s="29"/>
+      <c r="AH2" s="29"/>
+      <c r="AI2" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="AI2" s="21"/>
-      <c r="AJ2" s="21"/>
-      <c r="AK2" s="21"/>
-      <c r="AL2" s="21"/>
-      <c r="AM2" s="22"/>
-      <c r="AN2" s="20" t="s">
+      <c r="AJ2" s="27"/>
+      <c r="AK2" s="27"/>
+      <c r="AL2" s="27"/>
+      <c r="AM2" s="27"/>
+      <c r="AN2" s="28"/>
+      <c r="AO2" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="AO2" s="21"/>
-      <c r="AP2" s="21"/>
-      <c r="AQ2" s="21"/>
-      <c r="AR2" s="21"/>
-      <c r="AS2" s="22"/>
-      <c r="AT2" s="20" t="s">
+      <c r="AP2" s="27"/>
+      <c r="AQ2" s="27"/>
+      <c r="AR2" s="27"/>
+      <c r="AS2" s="27"/>
+      <c r="AT2" s="28"/>
+      <c r="AU2" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="AU2" s="21"/>
-      <c r="AV2" s="21"/>
-      <c r="AW2" s="21"/>
-      <c r="AX2" s="21"/>
-      <c r="AY2" s="22"/>
-      <c r="AZ2" s="14" t="s">
+      <c r="AV2" s="27"/>
+      <c r="AW2" s="27"/>
+      <c r="AX2" s="27"/>
+      <c r="AY2" s="27"/>
+      <c r="AZ2" s="28"/>
+      <c r="BA2" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="BA2" s="14"/>
-      <c r="BB2" s="14"/>
-      <c r="BC2" s="14"/>
-      <c r="BD2" s="14"/>
+      <c r="BB2" s="29"/>
+      <c r="BC2" s="29"/>
+      <c r="BD2" s="29"/>
+      <c r="BE2" s="29"/>
     </row>
-    <row r="3" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A3" s="23"/>
-      <c r="B3" s="23"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="12">
+    <row r="3" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="A3" s="30"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="12">
         <v>46083</v>
       </c>
-      <c r="H3" s="12">
+      <c r="I3" s="12">
         <v>46084</v>
       </c>
-      <c r="I3" s="12">
+      <c r="J3" s="12">
         <v>46085</v>
       </c>
-      <c r="J3" s="12">
+      <c r="K3" s="12">
         <v>46086</v>
       </c>
-      <c r="K3" s="12">
+      <c r="L3" s="12">
         <v>46087</v>
       </c>
-      <c r="L3" s="12">
+      <c r="M3" s="12">
         <v>46090</v>
       </c>
-      <c r="M3" s="12">
+      <c r="N3" s="12">
         <v>46091</v>
       </c>
-      <c r="N3" s="12">
+      <c r="O3" s="12">
         <v>46092</v>
       </c>
-      <c r="O3" s="12">
+      <c r="P3" s="12">
         <v>46093</v>
       </c>
-      <c r="P3" s="12">
+      <c r="Q3" s="12">
         <v>46094</v>
       </c>
-      <c r="Q3" s="12">
+      <c r="R3" s="12">
         <v>46097</v>
       </c>
-      <c r="R3" s="12">
+      <c r="S3" s="12">
         <v>46098</v>
       </c>
-      <c r="S3" s="12">
+      <c r="T3" s="12">
         <v>46099</v>
       </c>
-      <c r="T3" s="12">
+      <c r="U3" s="12">
         <v>46100</v>
       </c>
-      <c r="U3" s="12">
+      <c r="V3" s="12">
         <v>46101</v>
       </c>
-      <c r="V3" s="12">
+      <c r="W3" s="12">
         <v>46102</v>
       </c>
-      <c r="W3" s="12">
+      <c r="X3" s="12">
         <v>46104</v>
       </c>
-      <c r="X3" s="12">
+      <c r="Y3" s="12">
         <v>46105</v>
       </c>
-      <c r="Y3" s="12">
+      <c r="Z3" s="12">
         <v>46106</v>
       </c>
-      <c r="Z3" s="12">
+      <c r="AA3" s="12">
         <v>46107</v>
       </c>
-      <c r="AA3" s="12">
+      <c r="AB3" s="12">
         <v>46108</v>
       </c>
-      <c r="AB3" s="12">
+      <c r="AC3" s="12">
         <v>46109</v>
       </c>
-      <c r="AC3" s="12">
+      <c r="AD3" s="12">
         <v>46111</v>
       </c>
-      <c r="AD3" s="12">
+      <c r="AE3" s="12">
         <v>46112</v>
       </c>
-      <c r="AE3" s="12">
+      <c r="AF3" s="12">
         <v>46113</v>
       </c>
-      <c r="AF3" s="12">
+      <c r="AG3" s="12">
         <v>46114</v>
       </c>
-      <c r="AG3" s="12">
+      <c r="AH3" s="12">
         <v>46115</v>
       </c>
-      <c r="AH3" s="12">
+      <c r="AI3" s="12">
         <v>46118</v>
       </c>
-      <c r="AI3" s="12">
+      <c r="AJ3" s="12">
         <v>46119</v>
       </c>
-      <c r="AJ3" s="12">
+      <c r="AK3" s="12">
         <v>46120</v>
       </c>
-      <c r="AK3" s="12">
+      <c r="AL3" s="12">
         <v>46121</v>
       </c>
-      <c r="AL3" s="12">
+      <c r="AM3" s="12">
         <v>46122</v>
       </c>
-      <c r="AM3" s="12">
+      <c r="AN3" s="12">
         <v>46123</v>
       </c>
-      <c r="AN3" s="12">
+      <c r="AO3" s="12">
         <v>46125</v>
       </c>
-      <c r="AO3" s="12">
+      <c r="AP3" s="12">
         <v>46126</v>
       </c>
-      <c r="AP3" s="12">
+      <c r="AQ3" s="12">
         <v>46127</v>
       </c>
-      <c r="AQ3" s="12">
+      <c r="AR3" s="12">
         <v>46128</v>
       </c>
-      <c r="AR3" s="12">
+      <c r="AS3" s="12">
         <v>46129</v>
       </c>
-      <c r="AS3" s="12">
+      <c r="AT3" s="12">
         <v>46130</v>
       </c>
-      <c r="AT3" s="12">
+      <c r="AU3" s="12">
         <v>46132</v>
       </c>
-      <c r="AU3" s="12">
+      <c r="AV3" s="12">
         <v>46133</v>
       </c>
-      <c r="AV3" s="12">
+      <c r="AW3" s="12">
         <v>46134</v>
       </c>
-      <c r="AW3" s="12">
+      <c r="AX3" s="12">
         <v>46135</v>
       </c>
-      <c r="AX3" s="12">
+      <c r="AY3" s="12">
         <v>46136</v>
       </c>
-      <c r="AY3" s="12">
+      <c r="AZ3" s="12">
         <v>46137</v>
       </c>
-      <c r="AZ3" s="12">
+      <c r="BA3" s="12">
         <v>46139</v>
       </c>
-      <c r="BA3" s="12">
+      <c r="BB3" s="12">
         <v>46140</v>
       </c>
-      <c r="BB3" s="12">
+      <c r="BC3" s="12">
         <v>46141</v>
       </c>
-      <c r="BC3" s="12">
+      <c r="BD3" s="12">
         <v>46142</v>
       </c>
-      <c r="BD3" s="12">
+      <c r="BE3" s="12">
         <v>46143</v>
       </c>
     </row>
-    <row r="4" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
+    <row r="4" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="A4" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="16">
+      <c r="B4" s="24">
         <v>1</v>
       </c>
-      <c r="C4" s="17">
-        <f>SUM(I4:AA4)</f>
+      <c r="C4" s="25">
+        <f>SUM(J4:AB4)</f>
         <v>800</v>
       </c>
-      <c r="D4" s="18">
+      <c r="D4" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="19">
         <v>46083</v>
       </c>
-      <c r="E4" s="18">
+      <c r="F4" s="19">
         <v>46122</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="G4" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="9"/>
       <c r="H4" s="9"/>
-      <c r="I4" s="2">
+      <c r="I4" s="9"/>
+      <c r="J4" s="2">
         <v>0</v>
       </c>
-      <c r="J4" s="2">
+      <c r="K4" s="2">
         <v>112</v>
       </c>
-      <c r="K4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="L4" s="2">
+      <c r="L4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M4" s="2">
         <v>68</v>
       </c>
-      <c r="M4" s="2">
+      <c r="N4" s="2">
         <v>72</v>
       </c>
-      <c r="N4" s="2">
+      <c r="O4" s="2">
         <v>0</v>
       </c>
-      <c r="O4" s="2">
+      <c r="P4" s="2">
         <v>82</v>
-      </c>
-      <c r="P4" s="2">
-        <v>0</v>
       </c>
       <c r="Q4" s="2">
         <v>0</v>
       </c>
       <c r="R4" s="2">
+        <v>0</v>
+      </c>
+      <c r="S4" s="2">
         <v>107</v>
-      </c>
-      <c r="S4" s="2">
-        <v>0</v>
       </c>
       <c r="T4" s="2">
         <v>0</v>
@@ -1039,10 +1065,10 @@
         <v>0</v>
       </c>
       <c r="V4" s="2">
+        <v>0</v>
+      </c>
+      <c r="W4" s="2">
         <v>34</v>
-      </c>
-      <c r="W4" s="2">
-        <v>65</v>
       </c>
       <c r="X4" s="2">
         <v>65</v>
@@ -1056,18 +1082,20 @@
       <c r="AA4" s="2">
         <v>65</v>
       </c>
-      <c r="AB4" s="13"/>
+      <c r="AB4" s="2">
+        <v>65</v>
+      </c>
       <c r="AC4" s="13"/>
       <c r="AD4" s="13"/>
       <c r="AE4" s="13"/>
       <c r="AF4" s="13"/>
-      <c r="AG4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH4" s="13"/>
+      <c r="AG4" s="13"/>
+      <c r="AH4" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="AI4" s="13"/>
-      <c r="AJ4" s="4"/>
-      <c r="AK4" s="13"/>
+      <c r="AJ4" s="13"/>
+      <c r="AK4" s="4"/>
       <c r="AL4" s="13"/>
       <c r="AM4" s="13"/>
       <c r="AN4" s="13"/>
@@ -1076,13 +1104,13 @@
       <c r="AQ4" s="13"/>
       <c r="AR4" s="13"/>
       <c r="AS4" s="13"/>
-      <c r="AT4" s="6" t="s">
-        <v>19</v>
-      </c>
+      <c r="AT4" s="13"/>
       <c r="AU4" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="AV4" s="4"/>
+      <c r="AV4" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="AW4" s="4"/>
       <c r="AX4" s="4"/>
       <c r="AY4" s="4"/>
@@ -1090,10 +1118,10 @@
       <c r="BA4" s="4"/>
       <c r="BB4" s="4"/>
       <c r="BC4" s="4"/>
-      <c r="BD4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="BE4" s="1"/>
+      <c r="BD4" s="4"/>
+      <c r="BE4" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="BF4" s="1"/>
       <c r="BG4" s="1"/>
       <c r="BH4" s="1"/>
@@ -1101,17 +1129,18 @@
       <c r="BJ4" s="1"/>
       <c r="BK4" s="1"/>
       <c r="BL4" s="1"/>
+      <c r="BM4" s="1"/>
     </row>
-    <row r="5" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A5" s="15"/>
-      <c r="B5" s="16"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="11" t="s">
+    <row r="5" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="A5" s="16"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="4"/>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
@@ -1127,7 +1156,7 @@
       <c r="T5" s="4"/>
       <c r="U5" s="4"/>
       <c r="V5" s="4"/>
-      <c r="W5" s="13"/>
+      <c r="W5" s="4"/>
       <c r="X5" s="13"/>
       <c r="Y5" s="13"/>
       <c r="Z5" s="13"/>
@@ -1137,11 +1166,11 @@
       <c r="AD5" s="13"/>
       <c r="AE5" s="13"/>
       <c r="AF5" s="13"/>
-      <c r="AG5" s="4"/>
-      <c r="AH5" s="13"/>
+      <c r="AG5" s="13"/>
+      <c r="AH5" s="4"/>
       <c r="AI5" s="13"/>
-      <c r="AJ5" s="4"/>
-      <c r="AK5" s="13"/>
+      <c r="AJ5" s="13"/>
+      <c r="AK5" s="4"/>
       <c r="AL5" s="13"/>
       <c r="AM5" s="13"/>
       <c r="AN5" s="13"/>
@@ -1150,7 +1179,7 @@
       <c r="AQ5" s="13"/>
       <c r="AR5" s="13"/>
       <c r="AS5" s="13"/>
-      <c r="AT5" s="4"/>
+      <c r="AT5" s="13"/>
       <c r="AU5" s="4"/>
       <c r="AV5" s="4"/>
       <c r="AW5" s="4"/>
@@ -1161,7 +1190,7 @@
       <c r="BB5" s="4"/>
       <c r="BC5" s="4"/>
       <c r="BD5" s="4"/>
-      <c r="BE5" s="1"/>
+      <c r="BE5" s="4"/>
       <c r="BF5" s="1"/>
       <c r="BG5" s="1"/>
       <c r="BH5" s="1"/>
@@ -1169,40 +1198,41 @@
       <c r="BJ5" s="1"/>
       <c r="BK5" s="1"/>
       <c r="BL5" s="1"/>
+      <c r="BM5" s="1"/>
     </row>
-    <row r="6" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A6" s="15" t="s">
+    <row r="6" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="A6" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="24">
         <v>1</v>
       </c>
-      <c r="C6" s="17">
-        <f>SUM(W6:AA6)</f>
+      <c r="C6" s="25">
+        <f>SUM(X6:AB6)</f>
         <v>325</v>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="19">
         <v>46083</v>
       </c>
-      <c r="E6" s="18">
+      <c r="F6" s="19">
         <v>46122</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="G6" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="9"/>
       <c r="H6" s="9"/>
-      <c r="I6" s="2">
-        <v>0</v>
-      </c>
+      <c r="I6" s="9"/>
       <c r="J6" s="2">
         <v>0</v>
       </c>
-      <c r="K6" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="L6" s="2">
+      <c r="K6" s="2">
         <v>0</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>19</v>
       </c>
       <c r="M6" s="2">
         <v>0</v>
@@ -1219,14 +1249,14 @@
       <c r="Q6" s="2">
         <v>0</v>
       </c>
-      <c r="R6" s="4"/>
+      <c r="R6" s="2">
+        <v>0</v>
+      </c>
       <c r="S6" s="4"/>
       <c r="T6" s="4"/>
       <c r="U6" s="4"/>
       <c r="V6" s="4"/>
-      <c r="W6" s="2">
-        <v>65</v>
-      </c>
+      <c r="W6" s="4"/>
       <c r="X6" s="2">
         <v>65</v>
       </c>
@@ -1239,18 +1269,20 @@
       <c r="AA6" s="2">
         <v>65</v>
       </c>
-      <c r="AB6" s="13"/>
+      <c r="AB6" s="2">
+        <v>65</v>
+      </c>
       <c r="AC6" s="13"/>
       <c r="AD6" s="13"/>
       <c r="AE6" s="13"/>
       <c r="AF6" s="13"/>
-      <c r="AG6" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH6" s="13"/>
+      <c r="AG6" s="13"/>
+      <c r="AH6" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="AI6" s="13"/>
-      <c r="AJ6" s="4"/>
-      <c r="AK6" s="13"/>
+      <c r="AJ6" s="13"/>
+      <c r="AK6" s="4"/>
       <c r="AL6" s="13"/>
       <c r="AM6" s="13"/>
       <c r="AN6" s="13"/>
@@ -1259,13 +1291,13 @@
       <c r="AQ6" s="13"/>
       <c r="AR6" s="13"/>
       <c r="AS6" s="13"/>
-      <c r="AT6" s="6" t="s">
-        <v>19</v>
-      </c>
+      <c r="AT6" s="13"/>
       <c r="AU6" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="AV6" s="4"/>
+      <c r="AV6" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="AW6" s="4"/>
       <c r="AX6" s="4"/>
       <c r="AY6" s="4"/>
@@ -1273,10 +1305,10 @@
       <c r="BA6" s="4"/>
       <c r="BB6" s="4"/>
       <c r="BC6" s="4"/>
-      <c r="BD6" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="BE6" s="1"/>
+      <c r="BD6" s="4"/>
+      <c r="BE6" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="BF6" s="1"/>
       <c r="BG6" s="1"/>
       <c r="BH6" s="1"/>
@@ -1284,17 +1316,18 @@
       <c r="BJ6" s="1"/>
       <c r="BK6" s="1"/>
       <c r="BL6" s="1"/>
+      <c r="BM6" s="1"/>
     </row>
-    <row r="7" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A7" s="15"/>
-      <c r="B7" s="16"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="11" t="s">
+    <row r="7" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="A7" s="16"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="4"/>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
@@ -1310,7 +1343,7 @@
       <c r="T7" s="4"/>
       <c r="U7" s="4"/>
       <c r="V7" s="4"/>
-      <c r="W7" s="13"/>
+      <c r="W7" s="4"/>
       <c r="X7" s="13"/>
       <c r="Y7" s="13"/>
       <c r="Z7" s="13"/>
@@ -1320,11 +1353,11 @@
       <c r="AD7" s="13"/>
       <c r="AE7" s="13"/>
       <c r="AF7" s="13"/>
-      <c r="AG7" s="4"/>
-      <c r="AH7" s="13"/>
+      <c r="AG7" s="13"/>
+      <c r="AH7" s="4"/>
       <c r="AI7" s="13"/>
-      <c r="AJ7" s="4"/>
-      <c r="AK7" s="13"/>
+      <c r="AJ7" s="13"/>
+      <c r="AK7" s="4"/>
       <c r="AL7" s="13"/>
       <c r="AM7" s="13"/>
       <c r="AN7" s="13"/>
@@ -1333,7 +1366,7 @@
       <c r="AQ7" s="13"/>
       <c r="AR7" s="13"/>
       <c r="AS7" s="13"/>
-      <c r="AT7" s="4"/>
+      <c r="AT7" s="13"/>
       <c r="AU7" s="4"/>
       <c r="AV7" s="4"/>
       <c r="AW7" s="4"/>
@@ -1344,7 +1377,7 @@
       <c r="BB7" s="4"/>
       <c r="BC7" s="4"/>
       <c r="BD7" s="4"/>
-      <c r="BE7" s="1"/>
+      <c r="BE7" s="4"/>
       <c r="BF7" s="1"/>
       <c r="BG7" s="1"/>
       <c r="BH7" s="1"/>
@@ -1352,72 +1385,73 @@
       <c r="BJ7" s="1"/>
       <c r="BK7" s="1"/>
       <c r="BL7" s="1"/>
+      <c r="BM7" s="1"/>
     </row>
-    <row r="8" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A8" s="15" t="s">
+    <row r="8" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="A8" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="16">
+      <c r="B8" s="24">
         <v>1</v>
       </c>
-      <c r="C8" s="17">
-        <f>SUM(L8:AB8)</f>
+      <c r="C8" s="25">
+        <f>SUM(M8:AC8)</f>
         <v>422.00000000000011</v>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="19">
         <v>46083</v>
       </c>
-      <c r="E8" s="18">
+      <c r="F8" s="19">
         <v>46122</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="G8" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="13"/>
       <c r="H8" s="13"/>
       <c r="I8" s="13"/>
       <c r="J8" s="13"/>
-      <c r="K8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="L8" s="2">
+      <c r="K8" s="13"/>
+      <c r="L8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M8" s="2">
         <v>48</v>
       </c>
-      <c r="M8" s="2">
+      <c r="N8" s="2">
         <v>42</v>
       </c>
-      <c r="N8" s="2">
+      <c r="O8" s="2">
         <v>25</v>
-      </c>
-      <c r="O8" s="2">
-        <v>20</v>
       </c>
       <c r="P8" s="2">
         <v>20</v>
       </c>
       <c r="Q8" s="2">
+        <v>20</v>
+      </c>
+      <c r="R8" s="2">
         <v>34</v>
       </c>
-      <c r="R8" s="2">
+      <c r="S8" s="2">
         <v>13</v>
       </c>
-      <c r="S8" s="2">
+      <c r="T8" s="2">
         <v>28</v>
       </c>
-      <c r="T8" s="2">
+      <c r="U8" s="2">
         <v>25</v>
       </c>
-      <c r="U8" s="2">
+      <c r="V8" s="2">
         <v>15</v>
       </c>
-      <c r="V8" s="2">
+      <c r="W8" s="2">
         <v>24</v>
       </c>
-      <c r="W8" s="2">
+      <c r="X8" s="2">
         <v>0</v>
-      </c>
-      <c r="X8" s="2">
-        <v>25.6</v>
       </c>
       <c r="Y8" s="2">
         <v>25.6</v>
@@ -1431,17 +1465,19 @@
       <c r="AB8" s="2">
         <v>25.6</v>
       </c>
-      <c r="AC8" s="13"/>
+      <c r="AC8" s="2">
+        <v>25.6</v>
+      </c>
       <c r="AD8" s="13"/>
       <c r="AE8" s="13"/>
       <c r="AF8" s="13"/>
-      <c r="AG8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH8" s="13"/>
+      <c r="AG8" s="13"/>
+      <c r="AH8" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="AI8" s="13"/>
-      <c r="AJ8" s="6"/>
-      <c r="AK8" s="13"/>
+      <c r="AJ8" s="13"/>
+      <c r="AK8" s="6"/>
       <c r="AL8" s="13"/>
       <c r="AM8" s="13"/>
       <c r="AN8" s="13"/>
@@ -1450,13 +1486,13 @@
       <c r="AQ8" s="13"/>
       <c r="AR8" s="13"/>
       <c r="AS8" s="13"/>
-      <c r="AT8" s="6" t="s">
-        <v>19</v>
-      </c>
+      <c r="AT8" s="13"/>
       <c r="AU8" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="AV8" s="6"/>
+      <c r="AV8" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="AW8" s="6"/>
       <c r="AX8" s="6"/>
       <c r="AY8" s="6"/>
@@ -1464,10 +1500,10 @@
       <c r="BA8" s="6"/>
       <c r="BB8" s="6"/>
       <c r="BC8" s="6"/>
-      <c r="BD8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="BE8" s="1"/>
+      <c r="BD8" s="6"/>
+      <c r="BE8" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="BF8" s="1"/>
       <c r="BG8" s="1"/>
       <c r="BH8" s="1"/>
@@ -1475,22 +1511,23 @@
       <c r="BJ8" s="1"/>
       <c r="BK8" s="1"/>
       <c r="BL8" s="1"/>
+      <c r="BM8" s="1"/>
     </row>
-    <row r="9" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A9" s="15"/>
-      <c r="B9" s="16"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="11" t="s">
+    <row r="9" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="A9" s="16"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G9" s="13"/>
       <c r="H9" s="13"/>
       <c r="I9" s="13"/>
       <c r="J9" s="13"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="6"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="4"/>
       <c r="M9" s="6"/>
       <c r="N9" s="6"/>
       <c r="O9" s="6"/>
@@ -1505,17 +1542,17 @@
       <c r="X9" s="6"/>
       <c r="Y9" s="6"/>
       <c r="Z9" s="6"/>
-      <c r="AA9" s="13"/>
+      <c r="AA9" s="6"/>
       <c r="AB9" s="13"/>
       <c r="AC9" s="13"/>
       <c r="AD9" s="13"/>
       <c r="AE9" s="13"/>
       <c r="AF9" s="13"/>
-      <c r="AG9" s="4"/>
-      <c r="AH9" s="13"/>
+      <c r="AG9" s="13"/>
+      <c r="AH9" s="4"/>
       <c r="AI9" s="13"/>
-      <c r="AJ9" s="6"/>
-      <c r="AK9" s="13"/>
+      <c r="AJ9" s="13"/>
+      <c r="AK9" s="6"/>
       <c r="AL9" s="13"/>
       <c r="AM9" s="13"/>
       <c r="AN9" s="13"/>
@@ -1524,9 +1561,9 @@
       <c r="AQ9" s="13"/>
       <c r="AR9" s="13"/>
       <c r="AS9" s="13"/>
-      <c r="AT9" s="4"/>
+      <c r="AT9" s="13"/>
       <c r="AU9" s="4"/>
-      <c r="AV9" s="6"/>
+      <c r="AV9" s="4"/>
       <c r="AW9" s="6"/>
       <c r="AX9" s="6"/>
       <c r="AY9" s="6"/>
@@ -1534,8 +1571,8 @@
       <c r="BA9" s="6"/>
       <c r="BB9" s="6"/>
       <c r="BC9" s="6"/>
-      <c r="BD9" s="4"/>
-      <c r="BE9" s="1"/>
+      <c r="BD9" s="6"/>
+      <c r="BE9" s="4"/>
       <c r="BF9" s="1"/>
       <c r="BG9" s="1"/>
       <c r="BH9" s="1"/>
@@ -1543,40 +1580,41 @@
       <c r="BJ9" s="1"/>
       <c r="BK9" s="1"/>
       <c r="BL9" s="1"/>
+      <c r="BM9" s="1"/>
     </row>
-    <row r="10" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A10" s="15" t="s">
+    <row r="10" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="A10" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="16">
+      <c r="B10" s="24">
         <v>1</v>
       </c>
-      <c r="C10" s="17">
-        <f>SUM(M10:AI10)</f>
+      <c r="C10" s="25">
+        <f>SUM(N10:AJ10)</f>
         <v>63.3</v>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="19">
         <v>46084</v>
       </c>
-      <c r="E10" s="18">
+      <c r="F10" s="19">
         <v>46125</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="G10" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="13"/>
       <c r="H10" s="13"/>
       <c r="I10" s="13"/>
       <c r="J10" s="13"/>
-      <c r="K10" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="L10" s="6"/>
-      <c r="M10" s="3">
+      <c r="K10" s="13"/>
+      <c r="L10" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M10" s="6"/>
+      <c r="N10" s="3">
         <v>4.8</v>
-      </c>
-      <c r="N10" s="3">
-        <v>5</v>
       </c>
       <c r="O10" s="3">
         <v>5</v>
@@ -1585,64 +1623,66 @@
         <v>5</v>
       </c>
       <c r="Q10" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R10" s="3">
         <v>1</v>
       </c>
       <c r="S10" s="3">
+        <v>1</v>
+      </c>
+      <c r="T10" s="3">
         <v>2</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>0</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>5</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2</v>
       </c>
-      <c r="AG10" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH10" s="3">
+      <c r="AH10" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI10" s="3">
         <v>2</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>4.5</v>
       </c>
-      <c r="AJ10" s="6"/>
-      <c r="AK10" s="13"/>
+      <c r="AK10" s="6"/>
       <c r="AL10" s="13"/>
       <c r="AM10" s="13"/>
       <c r="AN10" s="13"/>
@@ -1651,13 +1691,13 @@
       <c r="AQ10" s="13"/>
       <c r="AR10" s="13"/>
       <c r="AS10" s="13"/>
-      <c r="AT10" s="6" t="s">
-        <v>19</v>
-      </c>
+      <c r="AT10" s="13"/>
       <c r="AU10" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="AV10" s="6"/>
+      <c r="AV10" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="AW10" s="6"/>
       <c r="AX10" s="6"/>
       <c r="AY10" s="6"/>
@@ -1665,10 +1705,10 @@
       <c r="BA10" s="6"/>
       <c r="BB10" s="6"/>
       <c r="BC10" s="6"/>
-      <c r="BD10" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="BE10" s="1"/>
+      <c r="BD10" s="6"/>
+      <c r="BE10" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="BF10" s="1"/>
       <c r="BG10" s="1"/>
       <c r="BH10" s="1"/>
@@ -1676,24 +1716,25 @@
       <c r="BJ10" s="1"/>
       <c r="BK10" s="1"/>
       <c r="BL10" s="1"/>
+      <c r="BM10" s="1"/>
     </row>
-    <row r="11" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A11" s="15"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="11" t="s">
+    <row r="11" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="A11" s="16"/>
+      <c r="B11" s="24"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="6"/>
       <c r="H11" s="6"/>
-      <c r="I11" s="13"/>
+      <c r="I11" s="6"/>
       <c r="J11" s="13"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="4"/>
       <c r="M11" s="13"/>
-      <c r="N11" s="6"/>
+      <c r="N11" s="13"/>
       <c r="O11" s="6"/>
       <c r="P11" s="6"/>
       <c r="Q11" s="6"/>
@@ -1706,17 +1747,17 @@
       <c r="X11" s="6"/>
       <c r="Y11" s="6"/>
       <c r="Z11" s="6"/>
-      <c r="AA11" s="13"/>
+      <c r="AA11" s="6"/>
       <c r="AB11" s="13"/>
       <c r="AC11" s="13"/>
       <c r="AD11" s="13"/>
       <c r="AE11" s="13"/>
       <c r="AF11" s="13"/>
-      <c r="AG11" s="4"/>
-      <c r="AH11" s="13"/>
+      <c r="AG11" s="13"/>
+      <c r="AH11" s="4"/>
       <c r="AI11" s="13"/>
-      <c r="AJ11" s="6"/>
-      <c r="AK11" s="13"/>
+      <c r="AJ11" s="13"/>
+      <c r="AK11" s="6"/>
       <c r="AL11" s="13"/>
       <c r="AM11" s="13"/>
       <c r="AN11" s="13"/>
@@ -1725,9 +1766,9 @@
       <c r="AQ11" s="13"/>
       <c r="AR11" s="13"/>
       <c r="AS11" s="13"/>
-      <c r="AT11" s="4"/>
+      <c r="AT11" s="13"/>
       <c r="AU11" s="4"/>
-      <c r="AV11" s="6"/>
+      <c r="AV11" s="4"/>
       <c r="AW11" s="6"/>
       <c r="AX11" s="6"/>
       <c r="AY11" s="6"/>
@@ -1735,8 +1776,8 @@
       <c r="BA11" s="6"/>
       <c r="BB11" s="6"/>
       <c r="BC11" s="6"/>
-      <c r="BD11" s="4"/>
-      <c r="BE11" s="1"/>
+      <c r="BD11" s="6"/>
+      <c r="BE11" s="4"/>
       <c r="BF11" s="1"/>
       <c r="BG11" s="1"/>
       <c r="BH11" s="1"/>
@@ -1744,69 +1785,70 @@
       <c r="BJ11" s="1"/>
       <c r="BK11" s="1"/>
       <c r="BL11" s="1"/>
+      <c r="BM11" s="1"/>
     </row>
-    <row r="12" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A12" s="15" t="s">
+    <row r="12" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="A12" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="16">
+      <c r="B12" s="24">
         <v>1</v>
       </c>
-      <c r="C12" s="17">
-        <f>SUM(L12:AK12)</f>
+      <c r="C12" s="25">
+        <f>SUM(M12:AL12)</f>
         <v>400</v>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="19">
         <v>46085</v>
       </c>
-      <c r="E12" s="18">
+      <c r="F12" s="19">
         <v>46126</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="G12" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="6"/>
       <c r="H12" s="6"/>
-      <c r="I12" s="13"/>
+      <c r="I12" s="6"/>
       <c r="J12" s="13"/>
-      <c r="K12" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="L12" s="3">
+      <c r="K12" s="13"/>
+      <c r="L12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M12" s="3">
         <v>30</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>6</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>30</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>12</v>
-      </c>
-      <c r="P12" s="3">
-        <v>6</v>
       </c>
       <c r="Q12" s="3">
         <v>6</v>
       </c>
       <c r="R12" s="3">
+        <v>6</v>
+      </c>
+      <c r="S12" s="3">
         <v>24</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>12</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>0</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>42</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>12</v>
-      </c>
-      <c r="W12" s="3">
-        <v>16</v>
       </c>
       <c r="X12" s="3">
         <v>16</v>
@@ -1835,11 +1877,11 @@
       <c r="AF12" s="3">
         <v>16</v>
       </c>
-      <c r="AG12" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH12" s="3">
+      <c r="AG12" s="3">
         <v>16</v>
+      </c>
+      <c r="AH12" s="6" t="s">
+        <v>19</v>
       </c>
       <c r="AI12" s="3">
         <v>16</v>
@@ -1848,9 +1890,11 @@
         <v>16</v>
       </c>
       <c r="AK12" s="3">
+        <v>16</v>
+      </c>
+      <c r="AL12" s="3">
         <v>12</v>
       </c>
-      <c r="AL12" s="13"/>
       <c r="AM12" s="13"/>
       <c r="AN12" s="13"/>
       <c r="AO12" s="13"/>
@@ -1858,13 +1902,13 @@
       <c r="AQ12" s="13"/>
       <c r="AR12" s="13"/>
       <c r="AS12" s="13"/>
-      <c r="AT12" s="6" t="s">
-        <v>19</v>
-      </c>
+      <c r="AT12" s="13"/>
       <c r="AU12" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="AV12" s="6"/>
+      <c r="AV12" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="AW12" s="6"/>
       <c r="AX12" s="6"/>
       <c r="AY12" s="6"/>
@@ -1872,10 +1916,10 @@
       <c r="BA12" s="6"/>
       <c r="BB12" s="6"/>
       <c r="BC12" s="6"/>
-      <c r="BD12" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="BE12" s="1"/>
+      <c r="BD12" s="6"/>
+      <c r="BE12" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="BF12" s="1"/>
       <c r="BG12" s="1"/>
       <c r="BH12" s="1"/>
@@ -1883,24 +1927,25 @@
       <c r="BJ12" s="1"/>
       <c r="BK12" s="1"/>
       <c r="BL12" s="1"/>
+      <c r="BM12" s="1"/>
     </row>
-    <row r="13" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A13" s="15"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="11" t="s">
+    <row r="13" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="A13" s="16"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G13" s="6"/>
       <c r="H13" s="6"/>
-      <c r="I13" s="13"/>
+      <c r="I13" s="6"/>
       <c r="J13" s="13"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="13"/>
+      <c r="K13" s="13"/>
+      <c r="L13" s="4"/>
       <c r="M13" s="13"/>
-      <c r="N13" s="6"/>
+      <c r="N13" s="13"/>
       <c r="O13" s="6"/>
       <c r="P13" s="6"/>
       <c r="Q13" s="6"/>
@@ -1913,17 +1958,17 @@
       <c r="X13" s="6"/>
       <c r="Y13" s="6"/>
       <c r="Z13" s="6"/>
-      <c r="AA13" s="13"/>
+      <c r="AA13" s="6"/>
       <c r="AB13" s="13"/>
       <c r="AC13" s="13"/>
       <c r="AD13" s="13"/>
       <c r="AE13" s="13"/>
       <c r="AF13" s="13"/>
-      <c r="AG13" s="4"/>
-      <c r="AH13" s="13"/>
+      <c r="AG13" s="13"/>
+      <c r="AH13" s="4"/>
       <c r="AI13" s="13"/>
-      <c r="AJ13" s="6"/>
-      <c r="AK13" s="13"/>
+      <c r="AJ13" s="13"/>
+      <c r="AK13" s="6"/>
       <c r="AL13" s="13"/>
       <c r="AM13" s="13"/>
       <c r="AN13" s="13"/>
@@ -1932,9 +1977,9 @@
       <c r="AQ13" s="13"/>
       <c r="AR13" s="13"/>
       <c r="AS13" s="13"/>
-      <c r="AT13" s="4"/>
+      <c r="AT13" s="13"/>
       <c r="AU13" s="4"/>
-      <c r="AV13" s="6"/>
+      <c r="AV13" s="4"/>
       <c r="AW13" s="6"/>
       <c r="AX13" s="6"/>
       <c r="AY13" s="6"/>
@@ -1942,8 +1987,8 @@
       <c r="BA13" s="6"/>
       <c r="BB13" s="6"/>
       <c r="BC13" s="6"/>
-      <c r="BD13" s="4"/>
-      <c r="BE13" s="1"/>
+      <c r="BD13" s="6"/>
+      <c r="BE13" s="4"/>
       <c r="BF13" s="1"/>
       <c r="BG13" s="1"/>
       <c r="BH13" s="1"/>
@@ -1951,73 +1996,76 @@
       <c r="BJ13" s="1"/>
       <c r="BK13" s="1"/>
       <c r="BL13" s="1"/>
+      <c r="BM13" s="1"/>
     </row>
-    <row r="14" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A14" s="15" t="s">
+    <row r="14" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="A14" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="16">
+      <c r="B14" s="24">
         <v>1</v>
       </c>
-      <c r="C14" s="17">
-        <f>SUM(P14:AK14)</f>
+      <c r="C14" s="25">
+        <f>SUM(Q14:AL14)</f>
         <v>5</v>
       </c>
-      <c r="D14" s="18">
+      <c r="D14" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" s="19">
         <v>46090</v>
       </c>
-      <c r="E14" s="18">
+      <c r="F14" s="19">
         <v>46126</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="G14" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G14" s="6"/>
       <c r="H14" s="6"/>
-      <c r="I14" s="13"/>
+      <c r="I14" s="6"/>
       <c r="J14" s="13"/>
-      <c r="K14" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="L14" s="13"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="M14" s="13"/>
-      <c r="N14" s="6"/>
+      <c r="N14" s="13"/>
       <c r="O14" s="6"/>
-      <c r="P14" s="3">
+      <c r="P14" s="6"/>
+      <c r="Q14" s="3">
         <v>1</v>
       </c>
-      <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
       <c r="S14" s="3"/>
-      <c r="T14" s="3">
+      <c r="T14" s="3"/>
+      <c r="U14" s="3">
         <v>1</v>
       </c>
-      <c r="U14" s="3"/>
       <c r="V14" s="3"/>
       <c r="W14" s="3"/>
-      <c r="X14" s="3">
+      <c r="X14" s="3"/>
+      <c r="Y14" s="3">
         <v>1</v>
       </c>
-      <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
       <c r="AA14" s="3"/>
       <c r="AB14" s="3"/>
       <c r="AC14" s="3"/>
       <c r="AD14" s="3"/>
-      <c r="AE14" s="3">
+      <c r="AE14" s="3"/>
+      <c r="AF14" s="3">
         <v>1</v>
       </c>
-      <c r="AF14" s="13"/>
-      <c r="AG14" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH14" s="13"/>
+      <c r="AG14" s="13"/>
+      <c r="AH14" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="AI14" s="13"/>
-      <c r="AJ14" s="6"/>
-      <c r="AK14" s="3">
+      <c r="AJ14" s="13"/>
+      <c r="AK14" s="6"/>
+      <c r="AL14" s="3">
         <v>1</v>
       </c>
-      <c r="AL14" s="13"/>
       <c r="AM14" s="13"/>
       <c r="AN14" s="13"/>
       <c r="AO14" s="13"/>
@@ -2025,13 +2073,13 @@
       <c r="AQ14" s="13"/>
       <c r="AR14" s="13"/>
       <c r="AS14" s="13"/>
-      <c r="AT14" s="6" t="s">
-        <v>19</v>
-      </c>
+      <c r="AT14" s="13"/>
       <c r="AU14" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="AV14" s="6"/>
+      <c r="AV14" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="AW14" s="6"/>
       <c r="AX14" s="6"/>
       <c r="AY14" s="6"/>
@@ -2039,10 +2087,10 @@
       <c r="BA14" s="6"/>
       <c r="BB14" s="6"/>
       <c r="BC14" s="6"/>
-      <c r="BD14" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="BE14" s="1"/>
+      <c r="BD14" s="6"/>
+      <c r="BE14" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="BF14" s="1"/>
       <c r="BG14" s="1"/>
       <c r="BH14" s="1"/>
@@ -2050,24 +2098,25 @@
       <c r="BJ14" s="1"/>
       <c r="BK14" s="1"/>
       <c r="BL14" s="1"/>
+      <c r="BM14" s="1"/>
     </row>
-    <row r="15" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A15" s="15"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="11" t="s">
+    <row r="15" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="A15" s="16"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G15" s="6"/>
       <c r="H15" s="6"/>
-      <c r="I15" s="13"/>
+      <c r="I15" s="6"/>
       <c r="J15" s="13"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="13"/>
+      <c r="K15" s="13"/>
+      <c r="L15" s="4"/>
       <c r="M15" s="13"/>
-      <c r="N15" s="6"/>
+      <c r="N15" s="13"/>
       <c r="O15" s="6"/>
       <c r="P15" s="6"/>
       <c r="Q15" s="6"/>
@@ -2080,17 +2129,17 @@
       <c r="X15" s="6"/>
       <c r="Y15" s="6"/>
       <c r="Z15" s="6"/>
-      <c r="AA15" s="13"/>
+      <c r="AA15" s="6"/>
       <c r="AB15" s="13"/>
       <c r="AC15" s="13"/>
       <c r="AD15" s="13"/>
       <c r="AE15" s="13"/>
       <c r="AF15" s="13"/>
-      <c r="AG15" s="4"/>
-      <c r="AH15" s="13"/>
+      <c r="AG15" s="13"/>
+      <c r="AH15" s="4"/>
       <c r="AI15" s="13"/>
-      <c r="AJ15" s="6"/>
-      <c r="AK15" s="13"/>
+      <c r="AJ15" s="13"/>
+      <c r="AK15" s="6"/>
       <c r="AL15" s="13"/>
       <c r="AM15" s="13"/>
       <c r="AN15" s="13"/>
@@ -2099,9 +2148,9 @@
       <c r="AQ15" s="13"/>
       <c r="AR15" s="13"/>
       <c r="AS15" s="13"/>
-      <c r="AT15" s="4"/>
+      <c r="AT15" s="13"/>
       <c r="AU15" s="4"/>
-      <c r="AV15" s="6"/>
+      <c r="AV15" s="4"/>
       <c r="AW15" s="6"/>
       <c r="AX15" s="6"/>
       <c r="AY15" s="6"/>
@@ -2109,8 +2158,8 @@
       <c r="BA15" s="6"/>
       <c r="BB15" s="6"/>
       <c r="BC15" s="6"/>
-      <c r="BD15" s="4"/>
-      <c r="BE15" s="1"/>
+      <c r="BD15" s="6"/>
+      <c r="BE15" s="4"/>
       <c r="BF15" s="1"/>
       <c r="BG15" s="1"/>
       <c r="BH15" s="1"/>
@@ -2118,69 +2167,70 @@
       <c r="BJ15" s="1"/>
       <c r="BK15" s="1"/>
       <c r="BL15" s="1"/>
+      <c r="BM15" s="1"/>
     </row>
-    <row r="16" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A16" s="15" t="s">
+    <row r="16" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="A16" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="16">
+      <c r="B16" s="24">
         <v>1</v>
       </c>
-      <c r="C16" s="17">
-        <f>SUM(L16:AL16)</f>
+      <c r="C16" s="25">
+        <f>SUM(M16:AM16)</f>
         <v>372</v>
       </c>
-      <c r="D16" s="18">
+      <c r="D16" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" s="19">
         <v>46085</v>
       </c>
-      <c r="E16" s="18">
+      <c r="F16" s="19">
         <v>46127</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="G16" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G16" s="6"/>
       <c r="H16" s="6"/>
-      <c r="I16" s="13"/>
+      <c r="I16" s="6"/>
       <c r="J16" s="13"/>
-      <c r="K16" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="L16" s="3">
+      <c r="K16" s="13"/>
+      <c r="L16" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M16" s="3">
         <v>27</v>
       </c>
-      <c r="M16" s="3">
+      <c r="N16" s="3">
         <v>0</v>
       </c>
-      <c r="N16" s="3">
+      <c r="O16" s="3">
         <v>28</v>
       </c>
-      <c r="O16" s="3">
+      <c r="P16" s="3">
         <v>8</v>
       </c>
-      <c r="P16" s="3">
+      <c r="Q16" s="3">
         <v>6</v>
-      </c>
-      <c r="Q16" s="3">
-        <v>0</v>
       </c>
       <c r="R16" s="3">
         <v>0</v>
       </c>
       <c r="S16" s="3">
+        <v>0</v>
+      </c>
+      <c r="T16" s="3">
         <v>17</v>
       </c>
-      <c r="T16" s="3">
+      <c r="U16" s="3">
         <v>20</v>
       </c>
-      <c r="U16" s="3">
+      <c r="V16" s="3">
         <v>17</v>
       </c>
-      <c r="V16" s="3">
+      <c r="W16" s="3">
         <v>31</v>
-      </c>
-      <c r="W16" s="3">
-        <v>14</v>
       </c>
       <c r="X16" s="3">
         <v>14</v>
@@ -2201,7 +2251,7 @@
         <v>14</v>
       </c>
       <c r="AD16" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE16" s="3">
         <v>15</v>
@@ -2209,11 +2259,11 @@
       <c r="AF16" s="3">
         <v>15</v>
       </c>
-      <c r="AG16" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH16" s="3">
+      <c r="AG16" s="3">
         <v>15</v>
+      </c>
+      <c r="AH16" s="6" t="s">
+        <v>19</v>
       </c>
       <c r="AI16" s="3">
         <v>15</v>
@@ -2227,20 +2277,22 @@
       <c r="AL16" s="3">
         <v>15</v>
       </c>
-      <c r="AM16" s="13"/>
+      <c r="AM16" s="3">
+        <v>15</v>
+      </c>
       <c r="AN16" s="13"/>
       <c r="AO16" s="13"/>
       <c r="AP16" s="13"/>
       <c r="AQ16" s="13"/>
       <c r="AR16" s="13"/>
       <c r="AS16" s="13"/>
-      <c r="AT16" s="6" t="s">
-        <v>19</v>
-      </c>
+      <c r="AT16" s="13"/>
       <c r="AU16" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="AV16" s="6"/>
+      <c r="AV16" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="AW16" s="6"/>
       <c r="AX16" s="6"/>
       <c r="AY16" s="6"/>
@@ -2248,10 +2300,10 @@
       <c r="BA16" s="6"/>
       <c r="BB16" s="6"/>
       <c r="BC16" s="6"/>
-      <c r="BD16" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="BE16" s="1"/>
+      <c r="BD16" s="6"/>
+      <c r="BE16" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="BF16" s="1"/>
       <c r="BG16" s="1"/>
       <c r="BH16" s="1"/>
@@ -2259,26 +2311,27 @@
       <c r="BJ16" s="1"/>
       <c r="BK16" s="1"/>
       <c r="BL16" s="1"/>
+      <c r="BM16" s="1"/>
     </row>
-    <row r="17" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A17" s="15"/>
-      <c r="B17" s="16"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="11" t="s">
+    <row r="17" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="A17" s="16"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G17" s="6"/>
       <c r="H17" s="6"/>
       <c r="I17" s="6"/>
       <c r="J17" s="6"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="13"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="4"/>
       <c r="M17" s="13"/>
       <c r="N17" s="13"/>
       <c r="O17" s="13"/>
-      <c r="P17" s="6"/>
+      <c r="P17" s="13"/>
       <c r="Q17" s="6"/>
       <c r="R17" s="6"/>
       <c r="S17" s="6"/>
@@ -2289,17 +2342,17 @@
       <c r="X17" s="6"/>
       <c r="Y17" s="6"/>
       <c r="Z17" s="6"/>
-      <c r="AA17" s="13"/>
+      <c r="AA17" s="6"/>
       <c r="AB17" s="13"/>
       <c r="AC17" s="13"/>
       <c r="AD17" s="13"/>
       <c r="AE17" s="13"/>
       <c r="AF17" s="13"/>
-      <c r="AG17" s="4"/>
-      <c r="AH17" s="13"/>
+      <c r="AG17" s="13"/>
+      <c r="AH17" s="4"/>
       <c r="AI17" s="13"/>
-      <c r="AJ17" s="6"/>
-      <c r="AK17" s="13"/>
+      <c r="AJ17" s="13"/>
+      <c r="AK17" s="6"/>
       <c r="AL17" s="13"/>
       <c r="AM17" s="13"/>
       <c r="AN17" s="13"/>
@@ -2308,9 +2361,9 @@
       <c r="AQ17" s="13"/>
       <c r="AR17" s="13"/>
       <c r="AS17" s="13"/>
-      <c r="AT17" s="4"/>
+      <c r="AT17" s="13"/>
       <c r="AU17" s="4"/>
-      <c r="AV17" s="6"/>
+      <c r="AV17" s="4"/>
       <c r="AW17" s="6"/>
       <c r="AX17" s="6"/>
       <c r="AY17" s="6"/>
@@ -2318,8 +2371,8 @@
       <c r="BA17" s="6"/>
       <c r="BB17" s="6"/>
       <c r="BC17" s="6"/>
-      <c r="BD17" s="4"/>
-      <c r="BE17" s="1"/>
+      <c r="BD17" s="6"/>
+      <c r="BE17" s="4"/>
       <c r="BF17" s="1"/>
       <c r="BG17" s="1"/>
       <c r="BH17" s="1"/>
@@ -2327,41 +2380,42 @@
       <c r="BJ17" s="1"/>
       <c r="BK17" s="1"/>
       <c r="BL17" s="1"/>
+      <c r="BM17" s="1"/>
     </row>
-    <row r="18" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A18" s="15" t="s">
+    <row r="18" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="A18" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="16">
+      <c r="B18" s="24">
         <v>1</v>
       </c>
-      <c r="C18" s="17">
-        <f>SUM(P18:AM18)</f>
+      <c r="C18" s="25">
+        <f>SUM(Q18:AN18)</f>
         <v>325</v>
       </c>
-      <c r="D18" s="18">
+      <c r="D18" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" s="19">
         <v>46090</v>
       </c>
-      <c r="E18" s="18">
+      <c r="F18" s="19">
         <v>46129</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="G18" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G18" s="6"/>
       <c r="H18" s="6"/>
       <c r="I18" s="6"/>
       <c r="J18" s="6"/>
-      <c r="K18" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="L18" s="13"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="M18" s="13"/>
       <c r="N18" s="13"/>
       <c r="O18" s="13"/>
-      <c r="P18" s="3">
-        <v>0</v>
-      </c>
+      <c r="P18" s="13"/>
       <c r="Q18" s="3">
         <v>0</v>
       </c>
@@ -2392,50 +2446,52 @@
       <c r="Z18" s="3">
         <v>0</v>
       </c>
-      <c r="AA18" s="13"/>
+      <c r="AA18" s="3">
+        <v>0</v>
+      </c>
       <c r="AB18" s="13"/>
       <c r="AC18" s="13"/>
       <c r="AD18" s="13"/>
-      <c r="AE18" s="3">
+      <c r="AE18" s="13"/>
+      <c r="AF18" s="3">
         <v>40</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>41.25</v>
       </c>
-      <c r="AG18" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH18" s="3">
+      <c r="AH18" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI18" s="3">
         <v>40</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>41.25</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>40</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>41.25</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>40</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>41.25</v>
       </c>
-      <c r="AN18" s="13"/>
       <c r="AO18" s="13"/>
       <c r="AP18" s="13"/>
       <c r="AQ18" s="13"/>
       <c r="AR18" s="13"/>
       <c r="AS18" s="13"/>
-      <c r="AT18" s="6" t="s">
-        <v>19</v>
-      </c>
+      <c r="AT18" s="13"/>
       <c r="AU18" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="AV18" s="6"/>
+      <c r="AV18" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="AW18" s="6"/>
       <c r="AX18" s="6"/>
       <c r="AY18" s="6"/>
@@ -2443,10 +2499,10 @@
       <c r="BA18" s="6"/>
       <c r="BB18" s="6"/>
       <c r="BC18" s="6"/>
-      <c r="BD18" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="BE18" s="1"/>
+      <c r="BD18" s="6"/>
+      <c r="BE18" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="BF18" s="1"/>
       <c r="BG18" s="1"/>
       <c r="BH18" s="1"/>
@@ -2454,26 +2510,27 @@
       <c r="BJ18" s="1"/>
       <c r="BK18" s="1"/>
       <c r="BL18" s="1"/>
+      <c r="BM18" s="1"/>
     </row>
-    <row r="19" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A19" s="15"/>
-      <c r="B19" s="16"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="11" t="s">
+    <row r="19" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="A19" s="16"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G19" s="6"/>
       <c r="H19" s="6"/>
       <c r="I19" s="6"/>
       <c r="J19" s="6"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="13"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="4"/>
       <c r="M19" s="13"/>
       <c r="N19" s="13"/>
       <c r="O19" s="13"/>
-      <c r="P19" s="6"/>
+      <c r="P19" s="13"/>
       <c r="Q19" s="6"/>
       <c r="R19" s="6"/>
       <c r="S19" s="6"/>
@@ -2484,17 +2541,17 @@
       <c r="X19" s="6"/>
       <c r="Y19" s="6"/>
       <c r="Z19" s="6"/>
-      <c r="AA19" s="13"/>
+      <c r="AA19" s="6"/>
       <c r="AB19" s="13"/>
       <c r="AC19" s="13"/>
       <c r="AD19" s="13"/>
       <c r="AE19" s="13"/>
       <c r="AF19" s="13"/>
-      <c r="AG19" s="4"/>
-      <c r="AH19" s="13"/>
+      <c r="AG19" s="13"/>
+      <c r="AH19" s="4"/>
       <c r="AI19" s="13"/>
-      <c r="AJ19" s="6"/>
-      <c r="AK19" s="13"/>
+      <c r="AJ19" s="13"/>
+      <c r="AK19" s="6"/>
       <c r="AL19" s="13"/>
       <c r="AM19" s="13"/>
       <c r="AN19" s="13"/>
@@ -2503,9 +2560,9 @@
       <c r="AQ19" s="13"/>
       <c r="AR19" s="13"/>
       <c r="AS19" s="13"/>
-      <c r="AT19" s="4"/>
+      <c r="AT19" s="13"/>
       <c r="AU19" s="4"/>
-      <c r="AV19" s="6"/>
+      <c r="AV19" s="4"/>
       <c r="AW19" s="6"/>
       <c r="AX19" s="6"/>
       <c r="AY19" s="6"/>
@@ -2513,8 +2570,8 @@
       <c r="BA19" s="6"/>
       <c r="BB19" s="6"/>
       <c r="BC19" s="6"/>
-      <c r="BD19" s="4"/>
-      <c r="BE19" s="1"/>
+      <c r="BD19" s="6"/>
+      <c r="BE19" s="4"/>
       <c r="BF19" s="1"/>
       <c r="BG19" s="1"/>
       <c r="BH19" s="1"/>
@@ -2522,88 +2579,91 @@
       <c r="BJ19" s="1"/>
       <c r="BK19" s="1"/>
       <c r="BL19" s="1"/>
+      <c r="BM19" s="1"/>
     </row>
-    <row r="20" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A20" s="15" t="s">
+    <row r="20" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="A20" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="16">
+      <c r="B20" s="24">
         <v>1</v>
       </c>
-      <c r="C20" s="17">
-        <f>SUM(X20:AQ20)</f>
+      <c r="C20" s="25">
+        <f>SUM(Y20:AR20)</f>
         <v>800</v>
       </c>
-      <c r="D20" s="18">
+      <c r="D20" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20" s="19">
         <v>46097</v>
       </c>
-      <c r="E20" s="18">
+      <c r="F20" s="19">
         <v>46134</v>
       </c>
-      <c r="F20" s="11" t="s">
+      <c r="G20" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G20" s="6"/>
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
       <c r="J20" s="6"/>
-      <c r="K20" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="L20" s="13"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="M20" s="13"/>
       <c r="N20" s="13"/>
       <c r="O20" s="13"/>
-      <c r="P20" s="6"/>
+      <c r="P20" s="13"/>
       <c r="Q20" s="6"/>
       <c r="R20" s="6"/>
       <c r="S20" s="6"/>
       <c r="T20" s="6"/>
       <c r="U20" s="6"/>
       <c r="V20" s="6"/>
-      <c r="X20" s="6"/>
+      <c r="W20" s="6"/>
       <c r="Y20" s="6"/>
       <c r="Z20" s="6"/>
       <c r="AA20" s="6"/>
       <c r="AB20" s="6"/>
       <c r="AC20" s="6"/>
-      <c r="AD20" s="3">
+      <c r="AD20" s="6"/>
+      <c r="AE20" s="3">
         <v>360</v>
       </c>
-      <c r="AE20" s="6"/>
       <c r="AF20" s="6"/>
-      <c r="AG20" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH20" s="13"/>
-      <c r="AJ20" s="13"/>
+      <c r="AG20" s="6"/>
+      <c r="AH20" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI20" s="13"/>
       <c r="AK20" s="13"/>
       <c r="AL20" s="13"/>
       <c r="AM20" s="13"/>
       <c r="AN20" s="13"/>
       <c r="AO20" s="13"/>
-      <c r="AQ20" s="3">
+      <c r="AP20" s="13"/>
+      <c r="AR20" s="3">
         <v>440</v>
       </c>
-      <c r="AS20" s="6"/>
-      <c r="AT20" s="6" t="s">
-        <v>19</v>
-      </c>
+      <c r="AT20" s="6"/>
       <c r="AU20" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="AV20" s="13"/>
-      <c r="AW20" s="6"/>
+      <c r="AV20" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="AW20" s="13"/>
       <c r="AX20" s="6"/>
       <c r="AY20" s="6"/>
       <c r="AZ20" s="6"/>
       <c r="BA20" s="6"/>
       <c r="BB20" s="6"/>
       <c r="BC20" s="6"/>
-      <c r="BD20" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="BE20" s="1"/>
+      <c r="BD20" s="6"/>
+      <c r="BE20" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="BF20" s="1"/>
       <c r="BG20" s="1"/>
       <c r="BH20" s="1"/>
@@ -2611,26 +2671,27 @@
       <c r="BJ20" s="1"/>
       <c r="BK20" s="1"/>
       <c r="BL20" s="1"/>
+      <c r="BM20" s="1"/>
     </row>
-    <row r="21" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A21" s="15"/>
-      <c r="B21" s="16"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="11" t="s">
+    <row r="21" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="A21" s="16"/>
+      <c r="B21" s="24"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G21" s="6"/>
       <c r="H21" s="6"/>
       <c r="I21" s="6"/>
       <c r="J21" s="6"/>
-      <c r="K21" s="4"/>
-      <c r="L21" s="13"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="4"/>
       <c r="M21" s="13"/>
       <c r="N21" s="13"/>
       <c r="O21" s="13"/>
-      <c r="P21" s="6"/>
+      <c r="P21" s="13"/>
       <c r="Q21" s="6"/>
       <c r="R21" s="6"/>
       <c r="S21" s="6"/>
@@ -2647,8 +2708,8 @@
       <c r="AD21" s="6"/>
       <c r="AE21" s="6"/>
       <c r="AF21" s="6"/>
-      <c r="AG21" s="4"/>
-      <c r="AH21" s="13"/>
+      <c r="AG21" s="6"/>
+      <c r="AH21" s="4"/>
       <c r="AI21" s="13"/>
       <c r="AJ21" s="13"/>
       <c r="AK21" s="13"/>
@@ -2656,50 +2717,53 @@
       <c r="AM21" s="13"/>
       <c r="AN21" s="13"/>
       <c r="AO21" s="13"/>
-      <c r="AP21" s="6"/>
+      <c r="AP21" s="13"/>
       <c r="AQ21" s="6"/>
       <c r="AR21" s="6"/>
       <c r="AS21" s="6"/>
-      <c r="AT21" s="4"/>
+      <c r="AT21" s="6"/>
       <c r="AU21" s="4"/>
-      <c r="AV21" s="13"/>
-      <c r="AW21" s="6"/>
+      <c r="AV21" s="4"/>
+      <c r="AW21" s="13"/>
       <c r="AX21" s="6"/>
       <c r="AY21" s="6"/>
       <c r="AZ21" s="6"/>
       <c r="BA21" s="6"/>
       <c r="BB21" s="6"/>
       <c r="BC21" s="6"/>
-      <c r="BD21" s="4"/>
+      <c r="BD21" s="6"/>
+      <c r="BE21" s="4"/>
     </row>
-    <row r="22" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A22" s="15" t="s">
+    <row r="22" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="A22" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="26">
+      <c r="B22" s="17">
         <v>2</v>
       </c>
-      <c r="C22" s="27">
-        <f>Y22</f>
+      <c r="C22" s="18">
+        <f>Z22</f>
         <v>5</v>
       </c>
-      <c r="D22" s="18">
+      <c r="D22" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="19">
         <v>46097</v>
       </c>
-      <c r="E22" s="18">
+      <c r="F22" s="19">
         <v>46134</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="G22" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G22" s="13"/>
       <c r="H22" s="13"/>
       <c r="I22" s="13"/>
       <c r="J22" s="13"/>
-      <c r="K22" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="L22" s="13"/>
+      <c r="K22" s="13"/>
+      <c r="L22" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="M22" s="13"/>
       <c r="N22" s="13"/>
       <c r="O22" s="13"/>
@@ -2712,20 +2776,20 @@
       <c r="V22" s="13"/>
       <c r="W22" s="13"/>
       <c r="X22" s="13"/>
-      <c r="Y22" s="5">
+      <c r="Y22" s="13"/>
+      <c r="Z22" s="5">
         <v>5</v>
       </c>
-      <c r="Z22" s="6"/>
       <c r="AA22" s="6"/>
       <c r="AB22" s="6"/>
       <c r="AC22" s="6"/>
       <c r="AD22" s="6"/>
       <c r="AE22" s="6"/>
       <c r="AF22" s="6"/>
-      <c r="AG22" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH22" s="13"/>
+      <c r="AG22" s="6"/>
+      <c r="AH22" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="AI22" s="13"/>
       <c r="AJ22" s="13"/>
       <c r="AK22" s="13"/>
@@ -2737,13 +2801,13 @@
       <c r="AQ22" s="13"/>
       <c r="AR22" s="13"/>
       <c r="AS22" s="13"/>
-      <c r="AT22" s="6" t="s">
-        <v>19</v>
-      </c>
+      <c r="AT22" s="13"/>
       <c r="AU22" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="AV22" s="13"/>
+      <c r="AV22" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="AW22" s="13"/>
       <c r="AX22" s="13"/>
       <c r="AY22" s="13"/>
@@ -2751,25 +2815,26 @@
       <c r="BA22" s="13"/>
       <c r="BB22" s="13"/>
       <c r="BC22" s="13"/>
-      <c r="BD22" s="6" t="s">
+      <c r="BD22" s="13"/>
+      <c r="BE22" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A23" s="15"/>
-      <c r="B23" s="26"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="11" t="s">
+    <row r="23" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="A23" s="16"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G23" s="13"/>
       <c r="H23" s="13"/>
       <c r="I23" s="13"/>
       <c r="J23" s="13"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="13"/>
+      <c r="K23" s="13"/>
+      <c r="L23" s="4"/>
       <c r="M23" s="13"/>
       <c r="N23" s="13"/>
       <c r="O23" s="13"/>
@@ -2784,7 +2849,7 @@
       <c r="X23" s="13"/>
       <c r="Y23" s="13"/>
       <c r="Z23" s="13"/>
-      <c r="AA23" s="4"/>
+      <c r="AA23" s="13"/>
       <c r="AB23" s="4"/>
       <c r="AC23" s="4"/>
       <c r="AD23" s="4"/>
@@ -2793,7 +2858,7 @@
       <c r="AG23" s="4"/>
       <c r="AH23" s="4"/>
       <c r="AI23" s="4"/>
-      <c r="AJ23" s="13"/>
+      <c r="AJ23" s="4"/>
       <c r="AK23" s="13"/>
       <c r="AL23" s="13"/>
       <c r="AM23" s="13"/>
@@ -2803,9 +2868,9 @@
       <c r="AQ23" s="13"/>
       <c r="AR23" s="13"/>
       <c r="AS23" s="13"/>
-      <c r="AT23" s="4"/>
+      <c r="AT23" s="13"/>
       <c r="AU23" s="4"/>
-      <c r="AV23" s="13"/>
+      <c r="AV23" s="4"/>
       <c r="AW23" s="13"/>
       <c r="AX23" s="13"/>
       <c r="AY23" s="13"/>
@@ -2813,36 +2878,39 @@
       <c r="BA23" s="13"/>
       <c r="BB23" s="13"/>
       <c r="BC23" s="13"/>
-      <c r="BD23" s="4"/>
+      <c r="BD23" s="13"/>
+      <c r="BE23" s="4"/>
     </row>
-    <row r="24" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A24" s="15" t="s">
+    <row r="24" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="A24" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B24" s="26">
+      <c r="B24" s="17">
         <v>2</v>
       </c>
-      <c r="C24" s="27">
-        <f>SUM(Z24:AI24)</f>
+      <c r="C24" s="18">
+        <f>SUM(AA24:AJ24)</f>
         <v>476</v>
       </c>
-      <c r="D24" s="18">
+      <c r="D24" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="E24" s="19">
         <v>46097</v>
       </c>
-      <c r="E24" s="18">
+      <c r="F24" s="19">
         <v>46134</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="G24" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G24" s="13"/>
       <c r="H24" s="13"/>
       <c r="I24" s="13"/>
       <c r="J24" s="13"/>
-      <c r="K24" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="L24" s="13"/>
+      <c r="K24" s="13"/>
+      <c r="L24" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="M24" s="13"/>
       <c r="N24" s="13"/>
       <c r="O24" s="13"/>
@@ -2856,9 +2924,7 @@
       <c r="W24" s="13"/>
       <c r="X24" s="13"/>
       <c r="Y24" s="13"/>
-      <c r="Z24" s="5">
-        <v>68</v>
-      </c>
+      <c r="Z24" s="13"/>
       <c r="AA24" s="5">
         <v>68</v>
       </c>
@@ -2877,12 +2943,14 @@
       <c r="AF24" s="5">
         <v>68</v>
       </c>
-      <c r="AG24" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH24" s="5"/>
+      <c r="AG24" s="5">
+        <v>68</v>
+      </c>
+      <c r="AH24" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="AI24" s="5"/>
-      <c r="AJ24" s="13"/>
+      <c r="AJ24" s="5"/>
       <c r="AK24" s="13"/>
       <c r="AL24" s="13"/>
       <c r="AM24" s="13"/>
@@ -2892,13 +2960,13 @@
       <c r="AQ24" s="13"/>
       <c r="AR24" s="13"/>
       <c r="AS24" s="13"/>
-      <c r="AT24" s="6" t="s">
-        <v>19</v>
-      </c>
+      <c r="AT24" s="13"/>
       <c r="AU24" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="AV24" s="13"/>
+      <c r="AV24" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="AW24" s="13"/>
       <c r="AX24" s="13"/>
       <c r="AY24" s="13"/>
@@ -2906,25 +2974,26 @@
       <c r="BA24" s="13"/>
       <c r="BB24" s="13"/>
       <c r="BC24" s="13"/>
-      <c r="BD24" s="6" t="s">
+      <c r="BD24" s="13"/>
+      <c r="BE24" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A25" s="15"/>
-      <c r="B25" s="26"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="11" t="s">
+    <row r="25" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="A25" s="16"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G25" s="13"/>
       <c r="H25" s="13"/>
       <c r="I25" s="13"/>
       <c r="J25" s="13"/>
-      <c r="K25" s="4"/>
-      <c r="L25" s="13"/>
+      <c r="K25" s="13"/>
+      <c r="L25" s="4"/>
       <c r="M25" s="13"/>
       <c r="N25" s="13"/>
       <c r="O25" s="13"/>
@@ -2939,7 +3008,7 @@
       <c r="X25" s="13"/>
       <c r="Y25" s="13"/>
       <c r="Z25" s="13"/>
-      <c r="AA25" s="4"/>
+      <c r="AA25" s="13"/>
       <c r="AB25" s="4"/>
       <c r="AC25" s="4"/>
       <c r="AD25" s="4"/>
@@ -2948,7 +3017,7 @@
       <c r="AG25" s="4"/>
       <c r="AH25" s="4"/>
       <c r="AI25" s="4"/>
-      <c r="AJ25" s="13"/>
+      <c r="AJ25" s="4"/>
       <c r="AK25" s="13"/>
       <c r="AL25" s="13"/>
       <c r="AM25" s="13"/>
@@ -2958,9 +3027,9 @@
       <c r="AQ25" s="13"/>
       <c r="AR25" s="13"/>
       <c r="AS25" s="13"/>
-      <c r="AT25" s="4"/>
+      <c r="AT25" s="13"/>
       <c r="AU25" s="4"/>
-      <c r="AV25" s="13"/>
+      <c r="AV25" s="4"/>
       <c r="AW25" s="13"/>
       <c r="AX25" s="13"/>
       <c r="AY25" s="13"/>
@@ -2968,36 +3037,39 @@
       <c r="BA25" s="13"/>
       <c r="BB25" s="13"/>
       <c r="BC25" s="13"/>
-      <c r="BD25" s="4"/>
+      <c r="BD25" s="13"/>
+      <c r="BE25" s="4"/>
     </row>
-    <row r="26" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A26" s="15" t="s">
+    <row r="26" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="A26" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B26" s="26">
+      <c r="B26" s="17">
         <v>2</v>
       </c>
-      <c r="C26" s="27">
-        <f>SUM(Z26:AI26)</f>
+      <c r="C26" s="18">
+        <f>SUM(AA26:AJ26)</f>
         <v>476</v>
       </c>
-      <c r="D26" s="18">
+      <c r="D26" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="E26" s="19">
         <v>46097</v>
       </c>
-      <c r="E26" s="18">
+      <c r="F26" s="19">
         <v>46134</v>
       </c>
-      <c r="F26" s="11" t="s">
+      <c r="G26" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G26" s="13"/>
       <c r="H26" s="13"/>
       <c r="I26" s="13"/>
       <c r="J26" s="13"/>
-      <c r="K26" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="L26" s="13"/>
+      <c r="K26" s="13"/>
+      <c r="L26" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="M26" s="13"/>
       <c r="N26" s="13"/>
       <c r="O26" s="13"/>
@@ -3011,9 +3083,7 @@
       <c r="W26" s="13"/>
       <c r="X26" s="13"/>
       <c r="Y26" s="13"/>
-      <c r="Z26" s="5">
-        <v>68</v>
-      </c>
+      <c r="Z26" s="13"/>
       <c r="AA26" s="5">
         <v>68</v>
       </c>
@@ -3032,12 +3102,14 @@
       <c r="AF26" s="5">
         <v>68</v>
       </c>
-      <c r="AG26" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH26" s="5"/>
+      <c r="AG26" s="5">
+        <v>68</v>
+      </c>
+      <c r="AH26" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="AI26" s="5"/>
-      <c r="AJ26" s="13"/>
+      <c r="AJ26" s="5"/>
       <c r="AK26" s="13"/>
       <c r="AL26" s="13"/>
       <c r="AM26" s="13"/>
@@ -3047,13 +3119,13 @@
       <c r="AQ26" s="13"/>
       <c r="AR26" s="13"/>
       <c r="AS26" s="13"/>
-      <c r="AT26" s="6" t="s">
-        <v>19</v>
-      </c>
+      <c r="AT26" s="13"/>
       <c r="AU26" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="AV26" s="13"/>
+      <c r="AV26" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="AW26" s="13"/>
       <c r="AX26" s="13"/>
       <c r="AY26" s="13"/>
@@ -3061,25 +3133,26 @@
       <c r="BA26" s="13"/>
       <c r="BB26" s="13"/>
       <c r="BC26" s="13"/>
-      <c r="BD26" s="6" t="s">
+      <c r="BD26" s="13"/>
+      <c r="BE26" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A27" s="15"/>
-      <c r="B27" s="26"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="11" t="s">
+    <row r="27" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="A27" s="16"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G27" s="13"/>
       <c r="H27" s="13"/>
       <c r="I27" s="13"/>
       <c r="J27" s="13"/>
-      <c r="K27" s="4"/>
-      <c r="L27" s="13"/>
+      <c r="K27" s="13"/>
+      <c r="L27" s="4"/>
       <c r="M27" s="13"/>
       <c r="N27" s="13"/>
       <c r="O27" s="13"/>
@@ -3094,7 +3167,7 @@
       <c r="X27" s="13"/>
       <c r="Y27" s="13"/>
       <c r="Z27" s="13"/>
-      <c r="AA27" s="4"/>
+      <c r="AA27" s="13"/>
       <c r="AB27" s="4"/>
       <c r="AC27" s="4"/>
       <c r="AD27" s="4"/>
@@ -3103,7 +3176,7 @@
       <c r="AG27" s="4"/>
       <c r="AH27" s="4"/>
       <c r="AI27" s="4"/>
-      <c r="AJ27" s="13"/>
+      <c r="AJ27" s="4"/>
       <c r="AK27" s="13"/>
       <c r="AL27" s="13"/>
       <c r="AM27" s="13"/>
@@ -3113,9 +3186,9 @@
       <c r="AQ27" s="13"/>
       <c r="AR27" s="13"/>
       <c r="AS27" s="13"/>
-      <c r="AT27" s="4"/>
+      <c r="AT27" s="13"/>
       <c r="AU27" s="4"/>
-      <c r="AV27" s="13"/>
+      <c r="AV27" s="4"/>
       <c r="AW27" s="13"/>
       <c r="AX27" s="13"/>
       <c r="AY27" s="13"/>
@@ -3123,36 +3196,39 @@
       <c r="BA27" s="13"/>
       <c r="BB27" s="13"/>
       <c r="BC27" s="13"/>
-      <c r="BD27" s="4"/>
+      <c r="BD27" s="13"/>
+      <c r="BE27" s="4"/>
     </row>
-    <row r="28" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A28" s="15" t="s">
+    <row r="28" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="A28" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B28" s="26">
+      <c r="B28" s="17">
         <v>2</v>
       </c>
-      <c r="C28" s="27">
-        <f>SUM(AA28:AF28,AI28:AN28)</f>
+      <c r="C28" s="18">
+        <f>SUM(AB28:AG28,AJ28:AO28)</f>
         <v>233.6</v>
       </c>
-      <c r="D28" s="18">
+      <c r="D28" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="E28" s="19">
         <v>46097</v>
       </c>
-      <c r="E28" s="18">
+      <c r="F28" s="19">
         <v>46134</v>
       </c>
-      <c r="F28" s="11" t="s">
+      <c r="G28" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G28" s="13"/>
       <c r="H28" s="13"/>
       <c r="I28" s="13"/>
       <c r="J28" s="13"/>
-      <c r="K28" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="L28" s="13"/>
+      <c r="K28" s="13"/>
+      <c r="L28" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="M28" s="13"/>
       <c r="N28" s="13"/>
       <c r="O28" s="13"/>
@@ -3167,17 +3243,15 @@
       <c r="X28" s="13"/>
       <c r="Y28" s="13"/>
       <c r="Z28" s="13"/>
-      <c r="AA28" s="5">
-        <v>26</v>
-      </c>
+      <c r="AA28" s="13"/>
       <c r="AB28" s="5">
         <v>26</v>
       </c>
       <c r="AC28" s="5">
+        <v>26</v>
+      </c>
+      <c r="AD28" s="5">
         <v>25.6</v>
-      </c>
-      <c r="AD28" s="5">
-        <v>26</v>
       </c>
       <c r="AE28" s="5">
         <v>26</v>
@@ -3185,11 +3259,11 @@
       <c r="AF28" s="5">
         <v>26</v>
       </c>
-      <c r="AG28" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH28" s="5">
+      <c r="AG28" s="5">
         <v>26</v>
+      </c>
+      <c r="AH28" s="6" t="s">
+        <v>19</v>
       </c>
       <c r="AI28" s="5">
         <v>26</v>
@@ -3200,20 +3274,22 @@
       <c r="AK28" s="5">
         <v>26</v>
       </c>
-      <c r="AM28" s="13"/>
+      <c r="AL28" s="5">
+        <v>26</v>
+      </c>
       <c r="AN28" s="13"/>
       <c r="AO28" s="13"/>
       <c r="AP28" s="13"/>
       <c r="AQ28" s="13"/>
       <c r="AR28" s="13"/>
       <c r="AS28" s="13"/>
-      <c r="AT28" s="6" t="s">
-        <v>19</v>
-      </c>
+      <c r="AT28" s="13"/>
       <c r="AU28" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="AV28" s="13"/>
+      <c r="AV28" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="AW28" s="13"/>
       <c r="AX28" s="13"/>
       <c r="AY28" s="13"/>
@@ -3221,25 +3297,26 @@
       <c r="BA28" s="13"/>
       <c r="BB28" s="13"/>
       <c r="BC28" s="13"/>
-      <c r="BD28" s="6" t="s">
+      <c r="BD28" s="13"/>
+      <c r="BE28" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A29" s="15"/>
-      <c r="B29" s="26"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="11" t="s">
+    <row r="29" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="A29" s="16"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G29" s="13"/>
       <c r="H29" s="13"/>
       <c r="I29" s="13"/>
       <c r="J29" s="13"/>
-      <c r="K29" s="4"/>
-      <c r="L29" s="13"/>
+      <c r="K29" s="13"/>
+      <c r="L29" s="4"/>
       <c r="M29" s="13"/>
       <c r="N29" s="13"/>
       <c r="O29" s="13"/>
@@ -3254,17 +3331,17 @@
       <c r="X29" s="13"/>
       <c r="Y29" s="13"/>
       <c r="Z29" s="13"/>
-      <c r="AA29" s="6"/>
+      <c r="AA29" s="13"/>
       <c r="AB29" s="6"/>
       <c r="AC29" s="6"/>
       <c r="AD29" s="6"/>
       <c r="AE29" s="6"/>
       <c r="AF29" s="6"/>
-      <c r="AG29" s="4"/>
-      <c r="AH29" s="6"/>
+      <c r="AG29" s="6"/>
+      <c r="AH29" s="4"/>
       <c r="AI29" s="6"/>
       <c r="AJ29" s="6"/>
-      <c r="AK29" s="13"/>
+      <c r="AK29" s="6"/>
       <c r="AL29" s="13"/>
       <c r="AM29" s="13"/>
       <c r="AN29" s="13"/>
@@ -3273,9 +3350,9 @@
       <c r="AQ29" s="13"/>
       <c r="AR29" s="13"/>
       <c r="AS29" s="13"/>
-      <c r="AT29" s="4"/>
+      <c r="AT29" s="13"/>
       <c r="AU29" s="4"/>
-      <c r="AV29" s="13"/>
+      <c r="AV29" s="4"/>
       <c r="AW29" s="13"/>
       <c r="AX29" s="13"/>
       <c r="AY29" s="13"/>
@@ -3283,36 +3360,39 @@
       <c r="BA29" s="13"/>
       <c r="BB29" s="13"/>
       <c r="BC29" s="13"/>
-      <c r="BD29" s="4"/>
+      <c r="BD29" s="13"/>
+      <c r="BE29" s="4"/>
     </row>
-    <row r="30" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A30" s="15" t="s">
+    <row r="30" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="A30" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B30" s="26">
+      <c r="B30" s="17">
         <v>2</v>
       </c>
-      <c r="C30" s="27">
-        <f>SUM(AB30:AF30,AH30:BC30)</f>
+      <c r="C30" s="18">
+        <f>SUM(AC30:AG30,AI30:BD30)</f>
         <v>43.3</v>
       </c>
-      <c r="D30" s="18">
+      <c r="D30" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="E30" s="19">
         <v>46097</v>
       </c>
-      <c r="E30" s="18">
+      <c r="F30" s="19">
         <v>46134</v>
       </c>
-      <c r="F30" s="11" t="s">
+      <c r="G30" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G30" s="13"/>
       <c r="H30" s="13"/>
       <c r="I30" s="13"/>
       <c r="J30" s="13"/>
-      <c r="K30" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="L30" s="13"/>
+      <c r="K30" s="13"/>
+      <c r="L30" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="M30" s="13"/>
       <c r="N30" s="13"/>
       <c r="O30" s="13"/>
@@ -3327,62 +3407,62 @@
       <c r="X30" s="13"/>
       <c r="Y30" s="13"/>
       <c r="Z30" s="13"/>
-      <c r="AA30" s="6"/>
-      <c r="AB30" s="8">
+      <c r="AA30" s="13"/>
+      <c r="AB30" s="6"/>
+      <c r="AC30" s="8">
         <v>3.94</v>
       </c>
-      <c r="AC30" s="8">
+      <c r="AD30" s="8">
         <v>3.76</v>
       </c>
-      <c r="AD30" s="8">
+      <c r="AE30" s="8">
         <v>3.94</v>
       </c>
-      <c r="AE30" s="8">
+      <c r="AF30" s="8">
         <v>2</v>
       </c>
-      <c r="AF30" s="8">
+      <c r="AG30" s="8">
         <v>3.94</v>
       </c>
-      <c r="AG30" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH30" s="8">
+      <c r="AH30" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI30" s="8">
         <v>2</v>
       </c>
-      <c r="AI30" s="8">
+      <c r="AJ30" s="8">
         <v>3.94</v>
       </c>
-      <c r="AJ30" s="8">
+      <c r="AK30" s="8">
         <v>2</v>
       </c>
-      <c r="AK30" s="8">
+      <c r="AL30" s="8">
         <v>3.94</v>
       </c>
-      <c r="AL30" s="8">
+      <c r="AM30" s="8">
         <v>2</v>
       </c>
-      <c r="AM30" s="8">
+      <c r="AN30" s="8">
         <v>3.94</v>
       </c>
-      <c r="AN30" s="8">
+      <c r="AO30" s="8">
         <v>2</v>
       </c>
-      <c r="AO30" s="8">
+      <c r="AP30" s="8">
         <v>3.9</v>
       </c>
-      <c r="AP30" s="8">
+      <c r="AQ30" s="8">
         <v>2</v>
       </c>
-      <c r="AQ30" s="13"/>
       <c r="AR30" s="13"/>
       <c r="AS30" s="13"/>
-      <c r="AT30" s="6" t="s">
-        <v>19</v>
-      </c>
+      <c r="AT30" s="13"/>
       <c r="AU30" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="AV30" s="13"/>
+      <c r="AV30" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="AW30" s="13"/>
       <c r="AX30" s="13"/>
       <c r="AY30" s="13"/>
@@ -3390,25 +3470,26 @@
       <c r="BA30" s="13"/>
       <c r="BB30" s="13"/>
       <c r="BC30" s="13"/>
-      <c r="BD30" s="6" t="s">
+      <c r="BD30" s="13"/>
+      <c r="BE30" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A31" s="15"/>
-      <c r="B31" s="26"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="11" t="s">
+    <row r="31" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="A31" s="16"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G31" s="13"/>
       <c r="H31" s="13"/>
       <c r="I31" s="13"/>
       <c r="J31" s="13"/>
-      <c r="K31" s="4"/>
-      <c r="L31" s="13"/>
+      <c r="K31" s="13"/>
+      <c r="L31" s="4"/>
       <c r="M31" s="13"/>
       <c r="N31" s="13"/>
       <c r="O31" s="13"/>
@@ -3423,28 +3504,28 @@
       <c r="X31" s="13"/>
       <c r="Y31" s="13"/>
       <c r="Z31" s="13"/>
-      <c r="AA31" s="6"/>
+      <c r="AA31" s="13"/>
       <c r="AB31" s="6"/>
       <c r="AC31" s="6"/>
       <c r="AD31" s="6"/>
       <c r="AE31" s="6"/>
       <c r="AF31" s="6"/>
-      <c r="AG31" s="4"/>
-      <c r="AH31" s="6"/>
+      <c r="AG31" s="6"/>
+      <c r="AH31" s="4"/>
       <c r="AI31" s="6"/>
       <c r="AJ31" s="6"/>
       <c r="AK31" s="6"/>
       <c r="AL31" s="6"/>
-      <c r="AM31" s="13"/>
+      <c r="AM31" s="6"/>
       <c r="AN31" s="13"/>
       <c r="AO31" s="13"/>
       <c r="AP31" s="13"/>
       <c r="AQ31" s="13"/>
       <c r="AR31" s="13"/>
       <c r="AS31" s="13"/>
-      <c r="AT31" s="4"/>
+      <c r="AT31" s="13"/>
       <c r="AU31" s="4"/>
-      <c r="AV31" s="13"/>
+      <c r="AV31" s="4"/>
       <c r="AW31" s="13"/>
       <c r="AX31" s="13"/>
       <c r="AY31" s="13"/>
@@ -3452,36 +3533,39 @@
       <c r="BA31" s="13"/>
       <c r="BB31" s="13"/>
       <c r="BC31" s="13"/>
-      <c r="BD31" s="4"/>
+      <c r="BD31" s="13"/>
+      <c r="BE31" s="4"/>
     </row>
-    <row r="32" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A32" s="15" t="s">
+    <row r="32" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="A32" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B32" s="26">
+      <c r="B32" s="17">
         <v>2</v>
       </c>
-      <c r="C32" s="27">
-        <f>SUM(AC32:AF32,AH32:AU32)</f>
+      <c r="C32" s="18">
+        <f>SUM(AD32:AG32,AI32:AV32)</f>
         <v>238</v>
       </c>
-      <c r="D32" s="18">
+      <c r="D32" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="E32" s="19">
         <v>46097</v>
       </c>
-      <c r="E32" s="18">
+      <c r="F32" s="19">
         <v>46134</v>
       </c>
-      <c r="F32" s="11" t="s">
+      <c r="G32" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G32" s="13"/>
       <c r="H32" s="13"/>
       <c r="I32" s="13"/>
       <c r="J32" s="13"/>
-      <c r="K32" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="L32" s="13"/>
+      <c r="K32" s="13"/>
+      <c r="L32" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="M32" s="13"/>
       <c r="N32" s="13"/>
       <c r="O32" s="13"/>
@@ -3496,11 +3580,9 @@
       <c r="X32" s="13"/>
       <c r="Y32" s="13"/>
       <c r="Z32" s="13"/>
-      <c r="AA32" s="6"/>
+      <c r="AA32" s="13"/>
       <c r="AB32" s="6"/>
-      <c r="AC32" s="8">
-        <v>16</v>
-      </c>
+      <c r="AC32" s="6"/>
       <c r="AD32" s="8">
         <v>16</v>
       </c>
@@ -3510,11 +3592,11 @@
       <c r="AF32" s="8">
         <v>16</v>
       </c>
-      <c r="AG32" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH32" s="8">
+      <c r="AG32" s="8">
         <v>16</v>
+      </c>
+      <c r="AH32" s="6" t="s">
+        <v>19</v>
       </c>
       <c r="AI32" s="8">
         <v>16</v>
@@ -3544,41 +3626,44 @@
         <v>16</v>
       </c>
       <c r="AR32" s="8">
+        <v>16</v>
+      </c>
+      <c r="AS32" s="8">
         <v>14</v>
       </c>
-      <c r="AS32" s="13"/>
-      <c r="AT32" s="6" t="s">
-        <v>19</v>
-      </c>
+      <c r="AT32" s="13"/>
       <c r="AU32" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="AW32" s="13"/>
+      <c r="AV32" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="AX32" s="13"/>
       <c r="AY32" s="13"/>
       <c r="AZ32" s="13"/>
       <c r="BA32" s="13"/>
       <c r="BB32" s="13"/>
       <c r="BC32" s="13"/>
-      <c r="BD32" s="6" t="s">
+      <c r="BD32" s="13"/>
+      <c r="BE32" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="33" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A33" s="15"/>
-      <c r="B33" s="26"/>
-      <c r="C33" s="27"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="11" t="s">
+    <row r="33" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A33" s="16"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G33" s="13"/>
       <c r="H33" s="13"/>
       <c r="I33" s="13"/>
       <c r="J33" s="13"/>
-      <c r="K33" s="4"/>
-      <c r="L33" s="13"/>
+      <c r="K33" s="13"/>
+      <c r="L33" s="4"/>
       <c r="M33" s="13"/>
       <c r="N33" s="13"/>
       <c r="O33" s="13"/>
@@ -3593,28 +3678,28 @@
       <c r="X33" s="13"/>
       <c r="Y33" s="13"/>
       <c r="Z33" s="13"/>
-      <c r="AA33" s="6"/>
+      <c r="AA33" s="13"/>
       <c r="AB33" s="6"/>
       <c r="AC33" s="6"/>
       <c r="AD33" s="6"/>
       <c r="AE33" s="6"/>
       <c r="AF33" s="6"/>
-      <c r="AG33" s="4"/>
-      <c r="AH33" s="6"/>
+      <c r="AG33" s="6"/>
+      <c r="AH33" s="4"/>
       <c r="AI33" s="6"/>
       <c r="AJ33" s="6"/>
       <c r="AK33" s="6"/>
       <c r="AL33" s="6"/>
-      <c r="AM33" s="13"/>
+      <c r="AM33" s="6"/>
       <c r="AN33" s="13"/>
       <c r="AO33" s="13"/>
       <c r="AP33" s="13"/>
       <c r="AQ33" s="13"/>
       <c r="AR33" s="13"/>
       <c r="AS33" s="13"/>
-      <c r="AT33" s="4"/>
+      <c r="AT33" s="13"/>
       <c r="AU33" s="4"/>
-      <c r="AV33" s="13"/>
+      <c r="AV33" s="4"/>
       <c r="AW33" s="13"/>
       <c r="AX33" s="13"/>
       <c r="AY33" s="13"/>
@@ -3622,36 +3707,39 @@
       <c r="BA33" s="13"/>
       <c r="BB33" s="13"/>
       <c r="BC33" s="13"/>
-      <c r="BD33" s="4"/>
+      <c r="BD33" s="13"/>
+      <c r="BE33" s="4"/>
     </row>
-    <row r="34" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A34" s="15" t="s">
+    <row r="34" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A34" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B34" s="26">
+      <c r="B34" s="17">
         <v>2</v>
       </c>
-      <c r="C34" s="27">
-        <f>SUM(AH34:AU34)</f>
+      <c r="C34" s="18">
+        <f>SUM(AI34:AV34)</f>
         <v>3</v>
       </c>
-      <c r="D34" s="18">
+      <c r="D34" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="E34" s="19">
         <v>46097</v>
       </c>
-      <c r="E34" s="18">
+      <c r="F34" s="19">
         <v>46134</v>
       </c>
-      <c r="F34" s="11" t="s">
+      <c r="G34" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G34" s="13"/>
       <c r="H34" s="13"/>
       <c r="I34" s="13"/>
       <c r="J34" s="13"/>
-      <c r="K34" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="L34" s="13"/>
+      <c r="K34" s="13"/>
+      <c r="L34" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="M34" s="13"/>
       <c r="N34" s="13"/>
       <c r="O34" s="13"/>
@@ -3666,65 +3754,66 @@
       <c r="X34" s="13"/>
       <c r="Y34" s="13"/>
       <c r="Z34" s="13"/>
-      <c r="AA34" s="6"/>
+      <c r="AA34" s="13"/>
       <c r="AB34" s="6"/>
       <c r="AC34" s="6"/>
       <c r="AD34" s="6"/>
       <c r="AE34" s="6"/>
       <c r="AF34" s="6"/>
-      <c r="AG34" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH34" s="8">
+      <c r="AG34" s="6"/>
+      <c r="AH34" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI34" s="8">
         <v>1</v>
       </c>
-      <c r="AI34" s="8"/>
       <c r="AJ34" s="8"/>
       <c r="AK34" s="8"/>
       <c r="AL34" s="8"/>
-      <c r="AM34" s="8">
+      <c r="AM34" s="8"/>
+      <c r="AN34" s="8">
         <v>1</v>
       </c>
-      <c r="AN34" s="8"/>
       <c r="AO34" s="8"/>
       <c r="AP34" s="8"/>
       <c r="AQ34" s="8"/>
-      <c r="AR34" s="8">
+      <c r="AR34" s="8"/>
+      <c r="AS34" s="8">
         <v>1</v>
       </c>
-      <c r="AS34" s="13"/>
-      <c r="AT34" s="6" t="s">
-        <v>19</v>
-      </c>
+      <c r="AT34" s="13"/>
       <c r="AU34" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="AW34" s="13"/>
+      <c r="AV34" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="AX34" s="13"/>
       <c r="AY34" s="13"/>
       <c r="AZ34" s="13"/>
       <c r="BA34" s="13"/>
       <c r="BB34" s="13"/>
       <c r="BC34" s="13"/>
-      <c r="BD34" s="6" t="s">
+      <c r="BD34" s="13"/>
+      <c r="BE34" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="35" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A35" s="15"/>
-      <c r="B35" s="26"/>
-      <c r="C35" s="27"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
-      <c r="F35" s="11" t="s">
+    <row r="35" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A35" s="16"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="18"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G35" s="13"/>
       <c r="H35" s="13"/>
       <c r="I35" s="13"/>
       <c r="J35" s="13"/>
-      <c r="K35" s="4"/>
-      <c r="L35" s="13"/>
+      <c r="K35" s="13"/>
+      <c r="L35" s="4"/>
       <c r="M35" s="13"/>
       <c r="N35" s="13"/>
       <c r="O35" s="13"/>
@@ -3739,28 +3828,28 @@
       <c r="X35" s="13"/>
       <c r="Y35" s="13"/>
       <c r="Z35" s="13"/>
-      <c r="AA35" s="6"/>
+      <c r="AA35" s="13"/>
       <c r="AB35" s="6"/>
       <c r="AC35" s="6"/>
       <c r="AD35" s="6"/>
       <c r="AE35" s="6"/>
       <c r="AF35" s="6"/>
-      <c r="AG35" s="4"/>
-      <c r="AH35" s="6"/>
+      <c r="AG35" s="6"/>
+      <c r="AH35" s="4"/>
       <c r="AI35" s="6"/>
       <c r="AJ35" s="6"/>
       <c r="AK35" s="6"/>
       <c r="AL35" s="6"/>
-      <c r="AM35" s="13"/>
+      <c r="AM35" s="6"/>
       <c r="AN35" s="13"/>
       <c r="AO35" s="13"/>
       <c r="AP35" s="13"/>
       <c r="AQ35" s="13"/>
       <c r="AR35" s="13"/>
       <c r="AS35" s="13"/>
-      <c r="AT35" s="4"/>
+      <c r="AT35" s="13"/>
       <c r="AU35" s="4"/>
-      <c r="AV35" s="13"/>
+      <c r="AV35" s="4"/>
       <c r="AW35" s="13"/>
       <c r="AX35" s="13"/>
       <c r="AY35" s="13"/>
@@ -3768,36 +3857,39 @@
       <c r="BA35" s="13"/>
       <c r="BB35" s="13"/>
       <c r="BC35" s="13"/>
-      <c r="BD35" s="4"/>
+      <c r="BD35" s="13"/>
+      <c r="BE35" s="4"/>
     </row>
-    <row r="36" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A36" s="15" t="s">
+    <row r="36" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A36" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B36" s="26">
+      <c r="B36" s="17">
         <v>2</v>
       </c>
-      <c r="C36" s="27">
-        <f>SUM(AC36:AF36,AH36:AS36)</f>
+      <c r="C36" s="18">
+        <f>SUM(AD36:AG36,AI36:AT36)</f>
         <v>256</v>
       </c>
-      <c r="D36" s="18">
+      <c r="D36" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="E36" s="19">
         <v>46097</v>
       </c>
-      <c r="E36" s="18">
+      <c r="F36" s="19">
         <v>46134</v>
       </c>
-      <c r="F36" s="11" t="s">
+      <c r="G36" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G36" s="13"/>
       <c r="H36" s="13"/>
       <c r="I36" s="13"/>
       <c r="J36" s="13"/>
-      <c r="K36" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="L36" s="13"/>
+      <c r="K36" s="13"/>
+      <c r="L36" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="M36" s="13"/>
       <c r="N36" s="13"/>
       <c r="O36" s="13"/>
@@ -3812,11 +3904,9 @@
       <c r="X36" s="13"/>
       <c r="Y36" s="13"/>
       <c r="Z36" s="13"/>
-      <c r="AA36" s="6"/>
+      <c r="AA36" s="13"/>
       <c r="AB36" s="6"/>
-      <c r="AC36" s="8">
-        <v>16</v>
-      </c>
+      <c r="AC36" s="6"/>
       <c r="AD36" s="8">
         <v>16</v>
       </c>
@@ -3826,11 +3916,11 @@
       <c r="AF36" s="8">
         <v>16</v>
       </c>
-      <c r="AG36" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH36" s="8">
+      <c r="AG36" s="8">
         <v>16</v>
+      </c>
+      <c r="AH36" s="6" t="s">
+        <v>19</v>
       </c>
       <c r="AI36" s="8">
         <v>16</v>
@@ -3865,13 +3955,15 @@
       <c r="AS36" s="8">
         <v>16</v>
       </c>
-      <c r="AT36" s="6" t="s">
-        <v>19</v>
+      <c r="AT36" s="8">
+        <v>16</v>
       </c>
       <c r="AU36" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="AV36" s="13"/>
+      <c r="AV36" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="AW36" s="13"/>
       <c r="AX36" s="13"/>
       <c r="AY36" s="13"/>
@@ -3879,25 +3971,26 @@
       <c r="BA36" s="13"/>
       <c r="BB36" s="13"/>
       <c r="BC36" s="13"/>
-      <c r="BD36" s="6" t="s">
+      <c r="BD36" s="13"/>
+      <c r="BE36" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="37" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A37" s="15"/>
-      <c r="B37" s="26"/>
-      <c r="C37" s="27"/>
-      <c r="D37" s="19"/>
-      <c r="E37" s="19"/>
-      <c r="F37" s="11" t="s">
+    <row r="37" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A37" s="16"/>
+      <c r="B37" s="17"/>
+      <c r="C37" s="18"/>
+      <c r="D37" s="34"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G37" s="13"/>
       <c r="H37" s="13"/>
       <c r="I37" s="13"/>
       <c r="J37" s="13"/>
-      <c r="K37" s="4"/>
-      <c r="L37" s="13"/>
+      <c r="K37" s="13"/>
+      <c r="L37" s="4"/>
       <c r="M37" s="13"/>
       <c r="N37" s="13"/>
       <c r="O37" s="13"/>
@@ -3912,14 +4005,14 @@
       <c r="X37" s="13"/>
       <c r="Y37" s="13"/>
       <c r="Z37" s="13"/>
-      <c r="AA37" s="6"/>
+      <c r="AA37" s="13"/>
       <c r="AB37" s="6"/>
       <c r="AC37" s="6"/>
       <c r="AD37" s="6"/>
       <c r="AE37" s="6"/>
       <c r="AF37" s="6"/>
-      <c r="AG37" s="4"/>
-      <c r="AH37" s="6"/>
+      <c r="AG37" s="6"/>
+      <c r="AH37" s="4"/>
       <c r="AI37" s="6"/>
       <c r="AJ37" s="6"/>
       <c r="AK37" s="6"/>
@@ -3927,13 +4020,13 @@
       <c r="AM37" s="6"/>
       <c r="AN37" s="6"/>
       <c r="AO37" s="6"/>
-      <c r="AP37" s="13"/>
+      <c r="AP37" s="6"/>
       <c r="AQ37" s="13"/>
       <c r="AR37" s="13"/>
       <c r="AS37" s="13"/>
-      <c r="AT37" s="4"/>
+      <c r="AT37" s="13"/>
       <c r="AU37" s="4"/>
-      <c r="AV37" s="13"/>
+      <c r="AV37" s="4"/>
       <c r="AW37" s="13"/>
       <c r="AX37" s="13"/>
       <c r="AY37" s="13"/>
@@ -3941,36 +4034,39 @@
       <c r="BA37" s="13"/>
       <c r="BB37" s="13"/>
       <c r="BC37" s="13"/>
-      <c r="BD37" s="4"/>
+      <c r="BD37" s="13"/>
+      <c r="BE37" s="4"/>
     </row>
-    <row r="38" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A38" s="15" t="s">
+    <row r="38" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A38" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="B38" s="26">
+      <c r="B38" s="17">
         <v>2</v>
       </c>
-      <c r="C38" s="27">
-        <f>SUM(AH38:AS38)</f>
+      <c r="C38" s="18">
+        <f>SUM(AI38:AT38)</f>
         <v>476</v>
       </c>
-      <c r="D38" s="18">
+      <c r="D38" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="E38" s="19">
         <v>46097</v>
       </c>
-      <c r="E38" s="18">
+      <c r="F38" s="19">
         <v>46134</v>
       </c>
-      <c r="F38" s="11" t="s">
+      <c r="G38" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G38" s="13"/>
       <c r="H38" s="13"/>
       <c r="I38" s="13"/>
       <c r="J38" s="13"/>
-      <c r="K38" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="L38" s="13"/>
+      <c r="K38" s="13"/>
+      <c r="L38" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="M38" s="13"/>
       <c r="N38" s="13"/>
       <c r="O38" s="13"/>
@@ -3985,20 +4081,18 @@
       <c r="X38" s="13"/>
       <c r="Y38" s="13"/>
       <c r="Z38" s="13"/>
-      <c r="AA38" s="6"/>
+      <c r="AA38" s="13"/>
       <c r="AB38" s="6"/>
       <c r="AC38" s="6"/>
       <c r="AD38" s="6"/>
       <c r="AE38" s="6"/>
-      <c r="AF38" s="8"/>
-      <c r="AG38" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH38" s="8"/>
+      <c r="AF38" s="6"/>
+      <c r="AG38" s="8"/>
+      <c r="AH38" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="AI38" s="8"/>
-      <c r="AJ38" s="8">
-        <v>40</v>
-      </c>
+      <c r="AJ38" s="8"/>
       <c r="AK38" s="8">
         <v>40</v>
       </c>
@@ -4008,29 +4102,31 @@
       <c r="AM38" s="8">
         <v>40</v>
       </c>
-      <c r="AN38" s="8"/>
-      <c r="AO38" s="8">
+      <c r="AN38" s="8">
         <v>40</v>
       </c>
+      <c r="AO38" s="8"/>
       <c r="AP38" s="8">
         <v>40</v>
       </c>
       <c r="AQ38" s="8">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AR38" s="8">
         <v>80</v>
       </c>
       <c r="AS38" s="8">
+        <v>80</v>
+      </c>
+      <c r="AT38" s="8">
         <v>76</v>
       </c>
-      <c r="AT38" s="6" t="s">
-        <v>19</v>
-      </c>
       <c r="AU38" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="AV38" s="13"/>
+      <c r="AV38" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="AW38" s="13"/>
       <c r="AX38" s="13"/>
       <c r="AY38" s="13"/>
@@ -4038,25 +4134,26 @@
       <c r="BA38" s="13"/>
       <c r="BB38" s="13"/>
       <c r="BC38" s="13"/>
-      <c r="BD38" s="6" t="s">
+      <c r="BD38" s="13"/>
+      <c r="BE38" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="39" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A39" s="15"/>
-      <c r="B39" s="26"/>
-      <c r="C39" s="27"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="19"/>
-      <c r="F39" s="11" t="s">
+    <row r="39" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A39" s="16"/>
+      <c r="B39" s="17"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="34"/>
+      <c r="E39" s="20"/>
+      <c r="F39" s="20"/>
+      <c r="G39" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G39" s="13"/>
       <c r="H39" s="13"/>
       <c r="I39" s="13"/>
       <c r="J39" s="13"/>
-      <c r="K39" s="4"/>
-      <c r="L39" s="13"/>
+      <c r="K39" s="13"/>
+      <c r="L39" s="4"/>
       <c r="M39" s="13"/>
       <c r="N39" s="13"/>
       <c r="O39" s="13"/>
@@ -4069,16 +4166,16 @@
       <c r="V39" s="13"/>
       <c r="W39" s="13"/>
       <c r="X39" s="13"/>
-      <c r="Y39" s="6"/>
+      <c r="Y39" s="13"/>
       <c r="Z39" s="6"/>
       <c r="AA39" s="6"/>
       <c r="AB39" s="6"/>
       <c r="AC39" s="6"/>
       <c r="AD39" s="6"/>
-      <c r="AE39" s="13"/>
+      <c r="AE39" s="6"/>
       <c r="AF39" s="13"/>
-      <c r="AG39" s="4"/>
-      <c r="AH39" s="6"/>
+      <c r="AG39" s="13"/>
+      <c r="AH39" s="4"/>
       <c r="AI39" s="6"/>
       <c r="AJ39" s="6"/>
       <c r="AK39" s="6"/>
@@ -4086,13 +4183,13 @@
       <c r="AM39" s="6"/>
       <c r="AN39" s="6"/>
       <c r="AO39" s="6"/>
-      <c r="AP39" s="13"/>
+      <c r="AP39" s="6"/>
       <c r="AQ39" s="13"/>
       <c r="AR39" s="13"/>
       <c r="AS39" s="13"/>
-      <c r="AT39" s="4"/>
+      <c r="AT39" s="13"/>
       <c r="AU39" s="4"/>
-      <c r="AV39" s="13"/>
+      <c r="AV39" s="4"/>
       <c r="AW39" s="13"/>
       <c r="AX39" s="13"/>
       <c r="AY39" s="13"/>
@@ -4100,36 +4197,39 @@
       <c r="BA39" s="13"/>
       <c r="BB39" s="13"/>
       <c r="BC39" s="13"/>
-      <c r="BD39" s="4"/>
+      <c r="BD39" s="13"/>
+      <c r="BE39" s="4"/>
     </row>
-    <row r="40" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A40" s="15" t="s">
+    <row r="40" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A40" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B40" s="26">
+      <c r="B40" s="17">
         <v>2</v>
       </c>
-      <c r="C40" s="27">
-        <f>SUM(AS40:AX40)</f>
+      <c r="C40" s="18">
+        <f>SUM(AT40:AY40)</f>
         <v>476</v>
       </c>
-      <c r="D40" s="18">
+      <c r="D40" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="E40" s="19">
         <v>46097</v>
       </c>
-      <c r="E40" s="18">
+      <c r="F40" s="19">
         <v>46134</v>
       </c>
-      <c r="F40" s="11" t="s">
+      <c r="G40" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G40" s="13"/>
       <c r="H40" s="13"/>
       <c r="I40" s="13"/>
       <c r="J40" s="13"/>
-      <c r="K40" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="L40" s="13"/>
+      <c r="K40" s="13"/>
+      <c r="L40" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="M40" s="13"/>
       <c r="N40" s="13"/>
       <c r="O40" s="13"/>
@@ -4150,10 +4250,10 @@
       <c r="AD40" s="13"/>
       <c r="AE40" s="13"/>
       <c r="AF40" s="13"/>
-      <c r="AG40" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH40" s="6"/>
+      <c r="AG40" s="13"/>
+      <c r="AH40" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="AI40" s="6"/>
       <c r="AJ40" s="6"/>
       <c r="AK40" s="6"/>
@@ -4161,45 +4261,46 @@
       <c r="AM40" s="6"/>
       <c r="AN40" s="6"/>
       <c r="AO40" s="6"/>
-      <c r="AQ40" s="6"/>
-      <c r="AS40" s="8">
+      <c r="AP40" s="6"/>
+      <c r="AR40" s="6"/>
+      <c r="AT40" s="8">
         <v>160</v>
       </c>
-      <c r="AT40" s="6" t="s">
-        <v>19</v>
-      </c>
       <c r="AU40" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="AV40" s="13"/>
+      <c r="AV40" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="AW40" s="13"/>
-      <c r="AX40" s="8">
+      <c r="AX40" s="13"/>
+      <c r="AY40" s="8">
         <v>316</v>
       </c>
-      <c r="AY40" s="13"/>
       <c r="AZ40" s="13"/>
       <c r="BA40" s="13"/>
       <c r="BB40" s="13"/>
       <c r="BC40" s="13"/>
-      <c r="BD40" s="6" t="s">
+      <c r="BD40" s="13"/>
+      <c r="BE40" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="41" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A41" s="15"/>
-      <c r="B41" s="26"/>
-      <c r="C41" s="27"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="11" t="s">
+    <row r="41" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A41" s="16"/>
+      <c r="B41" s="17"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="34"/>
+      <c r="E41" s="20"/>
+      <c r="F41" s="20"/>
+      <c r="G41" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G41" s="13"/>
       <c r="H41" s="13"/>
       <c r="I41" s="13"/>
       <c r="J41" s="13"/>
-      <c r="K41" s="4"/>
-      <c r="L41" s="13"/>
+      <c r="K41" s="13"/>
+      <c r="L41" s="4"/>
       <c r="M41" s="13"/>
       <c r="N41" s="13"/>
       <c r="O41" s="13"/>
@@ -4216,16 +4317,16 @@
       <c r="Z41" s="13"/>
       <c r="AA41" s="13"/>
       <c r="AB41" s="13"/>
-      <c r="AC41" s="6"/>
+      <c r="AC41" s="13"/>
       <c r="AD41" s="6"/>
       <c r="AE41" s="6"/>
       <c r="AF41" s="6"/>
-      <c r="AG41" s="4"/>
-      <c r="AH41" s="13"/>
+      <c r="AG41" s="6"/>
+      <c r="AH41" s="4"/>
       <c r="AI41" s="13"/>
       <c r="AJ41" s="13"/>
       <c r="AK41" s="13"/>
-      <c r="AL41" s="6"/>
+      <c r="AL41" s="13"/>
       <c r="AM41" s="6"/>
       <c r="AN41" s="6"/>
       <c r="AO41" s="6"/>
@@ -4233,46 +4334,49 @@
       <c r="AQ41" s="6"/>
       <c r="AR41" s="6"/>
       <c r="AS41" s="6"/>
-      <c r="AT41" s="4"/>
+      <c r="AT41" s="6"/>
       <c r="AU41" s="4"/>
-      <c r="AV41" s="6"/>
-      <c r="AW41" s="13"/>
+      <c r="AV41" s="4"/>
+      <c r="AW41" s="6"/>
       <c r="AX41" s="13"/>
       <c r="AY41" s="13"/>
       <c r="AZ41" s="13"/>
       <c r="BA41" s="13"/>
       <c r="BB41" s="13"/>
       <c r="BC41" s="13"/>
-      <c r="BD41" s="4"/>
+      <c r="BD41" s="13"/>
+      <c r="BE41" s="4"/>
     </row>
-    <row r="42" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A42" s="15" t="s">
+    <row r="42" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A42" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B42" s="28">
+      <c r="B42" s="21">
         <v>3</v>
       </c>
-      <c r="C42" s="29">
-        <f>SUM(AH42:AI42)</f>
+      <c r="C42" s="22">
+        <f>SUM(AI42:AJ42)</f>
         <v>126</v>
       </c>
-      <c r="D42" s="18">
+      <c r="D42" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="E42" s="19">
         <v>46097</v>
       </c>
-      <c r="E42" s="18">
+      <c r="F42" s="19">
         <v>46134</v>
       </c>
-      <c r="F42" s="11" t="s">
+      <c r="G42" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G42" s="13"/>
       <c r="H42" s="13"/>
       <c r="I42" s="13"/>
       <c r="J42" s="13"/>
-      <c r="K42" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="L42" s="13"/>
+      <c r="K42" s="13"/>
+      <c r="L42" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="M42" s="13"/>
       <c r="N42" s="13"/>
       <c r="O42" s="13"/>
@@ -4293,58 +4397,59 @@
       <c r="AD42" s="13"/>
       <c r="AE42" s="13"/>
       <c r="AF42" s="13"/>
-      <c r="AG42" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH42" s="7">
-        <v>63</v>
+      <c r="AG42" s="13"/>
+      <c r="AH42" s="6" t="s">
+        <v>19</v>
       </c>
       <c r="AI42" s="7">
         <v>63</v>
       </c>
-      <c r="AJ42" s="4"/>
-      <c r="AK42" s="13"/>
+      <c r="AJ42" s="7">
+        <v>63</v>
+      </c>
+      <c r="AK42" s="4"/>
       <c r="AL42" s="13"/>
       <c r="AM42" s="13"/>
       <c r="AN42" s="13"/>
       <c r="AO42" s="13"/>
       <c r="AP42" s="13"/>
-      <c r="AQ42" s="6"/>
+      <c r="AQ42" s="13"/>
       <c r="AR42" s="6"/>
       <c r="AS42" s="6"/>
-      <c r="AT42" s="6" t="s">
-        <v>19</v>
-      </c>
+      <c r="AT42" s="6"/>
       <c r="AU42" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="AV42" s="4"/>
+      <c r="AV42" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="AW42" s="4"/>
-      <c r="AX42" s="13"/>
+      <c r="AX42" s="4"/>
       <c r="AY42" s="13"/>
       <c r="AZ42" s="13"/>
       <c r="BA42" s="13"/>
       <c r="BB42" s="13"/>
       <c r="BC42" s="13"/>
-      <c r="BD42" s="6" t="s">
+      <c r="BD42" s="13"/>
+      <c r="BE42" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="43" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A43" s="15"/>
-      <c r="B43" s="28"/>
-      <c r="C43" s="30"/>
-      <c r="D43" s="19"/>
-      <c r="E43" s="19"/>
-      <c r="F43" s="11" t="s">
+    <row r="43" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A43" s="16"/>
+      <c r="B43" s="21"/>
+      <c r="C43" s="23"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="20"/>
+      <c r="F43" s="20"/>
+      <c r="G43" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G43" s="13"/>
       <c r="H43" s="13"/>
       <c r="I43" s="13"/>
       <c r="J43" s="13"/>
-      <c r="K43" s="4"/>
-      <c r="L43" s="13"/>
+      <c r="K43" s="13"/>
+      <c r="L43" s="4"/>
       <c r="M43" s="13"/>
       <c r="N43" s="13"/>
       <c r="O43" s="13"/>
@@ -4365,59 +4470,62 @@
       <c r="AD43" s="13"/>
       <c r="AE43" s="13"/>
       <c r="AF43" s="13"/>
-      <c r="AG43" s="4"/>
+      <c r="AG43" s="13"/>
       <c r="AH43" s="4"/>
       <c r="AI43" s="4"/>
       <c r="AJ43" s="4"/>
-      <c r="AK43" s="13"/>
+      <c r="AK43" s="4"/>
       <c r="AL43" s="13"/>
       <c r="AM43" s="13"/>
       <c r="AN43" s="13"/>
       <c r="AO43" s="13"/>
       <c r="AP43" s="13"/>
-      <c r="AQ43" s="6"/>
+      <c r="AQ43" s="13"/>
       <c r="AR43" s="6"/>
       <c r="AS43" s="6"/>
-      <c r="AT43" s="4"/>
+      <c r="AT43" s="6"/>
       <c r="AU43" s="4"/>
       <c r="AV43" s="4"/>
       <c r="AW43" s="4"/>
-      <c r="AX43" s="13"/>
+      <c r="AX43" s="4"/>
       <c r="AY43" s="13"/>
       <c r="AZ43" s="13"/>
       <c r="BA43" s="13"/>
       <c r="BB43" s="13"/>
       <c r="BC43" s="13"/>
-      <c r="BD43" s="4"/>
+      <c r="BD43" s="13"/>
+      <c r="BE43" s="4"/>
     </row>
-    <row r="44" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A44" s="15" t="s">
+    <row r="44" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A44" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B44" s="28">
+      <c r="B44" s="21">
         <v>3</v>
       </c>
-      <c r="C44" s="29">
-        <f>SUM(AH44:AI44)</f>
+      <c r="C44" s="22">
+        <f>SUM(AI44:AJ44)</f>
         <v>126</v>
       </c>
-      <c r="D44" s="18">
+      <c r="D44" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="E44" s="19">
         <v>46097</v>
       </c>
-      <c r="E44" s="18">
+      <c r="F44" s="19">
         <v>46134</v>
       </c>
-      <c r="F44" s="11" t="s">
+      <c r="G44" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G44" s="13"/>
       <c r="H44" s="13"/>
       <c r="I44" s="13"/>
       <c r="J44" s="13"/>
-      <c r="K44" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="L44" s="13"/>
+      <c r="K44" s="13"/>
+      <c r="L44" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="M44" s="13"/>
       <c r="N44" s="13"/>
       <c r="O44" s="13"/>
@@ -4438,58 +4546,59 @@
       <c r="AD44" s="13"/>
       <c r="AE44" s="13"/>
       <c r="AF44" s="13"/>
-      <c r="AG44" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH44" s="7">
-        <v>63</v>
+      <c r="AG44" s="13"/>
+      <c r="AH44" s="6" t="s">
+        <v>19</v>
       </c>
       <c r="AI44" s="7">
         <v>63</v>
       </c>
-      <c r="AJ44" s="4"/>
-      <c r="AK44" s="13"/>
+      <c r="AJ44" s="7">
+        <v>63</v>
+      </c>
+      <c r="AK44" s="4"/>
       <c r="AL44" s="13"/>
       <c r="AM44" s="13"/>
       <c r="AN44" s="13"/>
       <c r="AO44" s="13"/>
       <c r="AP44" s="13"/>
-      <c r="AQ44" s="6"/>
+      <c r="AQ44" s="13"/>
       <c r="AR44" s="6"/>
       <c r="AS44" s="6"/>
-      <c r="AT44" s="6" t="s">
-        <v>19</v>
-      </c>
+      <c r="AT44" s="6"/>
       <c r="AU44" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="AV44" s="4"/>
+      <c r="AV44" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="AW44" s="4"/>
-      <c r="AX44" s="13"/>
+      <c r="AX44" s="4"/>
       <c r="AY44" s="13"/>
       <c r="AZ44" s="13"/>
       <c r="BA44" s="13"/>
       <c r="BB44" s="13"/>
       <c r="BC44" s="13"/>
-      <c r="BD44" s="6" t="s">
+      <c r="BD44" s="13"/>
+      <c r="BE44" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="45" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A45" s="15"/>
-      <c r="B45" s="28"/>
-      <c r="C45" s="30"/>
-      <c r="D45" s="19"/>
-      <c r="E45" s="19"/>
-      <c r="F45" s="11" t="s">
+    <row r="45" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A45" s="16"/>
+      <c r="B45" s="21"/>
+      <c r="C45" s="23"/>
+      <c r="D45" s="23"/>
+      <c r="E45" s="20"/>
+      <c r="F45" s="20"/>
+      <c r="G45" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G45" s="13"/>
       <c r="H45" s="13"/>
       <c r="I45" s="13"/>
       <c r="J45" s="13"/>
-      <c r="K45" s="4"/>
-      <c r="L45" s="13"/>
+      <c r="K45" s="13"/>
+      <c r="L45" s="4"/>
       <c r="M45" s="13"/>
       <c r="N45" s="13"/>
       <c r="O45" s="13"/>
@@ -4510,59 +4619,62 @@
       <c r="AD45" s="13"/>
       <c r="AE45" s="13"/>
       <c r="AF45" s="13"/>
-      <c r="AG45" s="4"/>
+      <c r="AG45" s="13"/>
       <c r="AH45" s="4"/>
       <c r="AI45" s="4"/>
       <c r="AJ45" s="4"/>
-      <c r="AK45" s="13"/>
+      <c r="AK45" s="4"/>
       <c r="AL45" s="13"/>
       <c r="AM45" s="13"/>
       <c r="AN45" s="13"/>
       <c r="AO45" s="13"/>
       <c r="AP45" s="13"/>
-      <c r="AQ45" s="6"/>
+      <c r="AQ45" s="13"/>
       <c r="AR45" s="6"/>
       <c r="AS45" s="6"/>
-      <c r="AT45" s="4"/>
+      <c r="AT45" s="6"/>
       <c r="AU45" s="4"/>
       <c r="AV45" s="4"/>
       <c r="AW45" s="4"/>
-      <c r="AX45" s="13"/>
+      <c r="AX45" s="4"/>
       <c r="AY45" s="13"/>
       <c r="AZ45" s="13"/>
       <c r="BA45" s="13"/>
       <c r="BB45" s="13"/>
       <c r="BC45" s="13"/>
-      <c r="BD45" s="4"/>
+      <c r="BD45" s="13"/>
+      <c r="BE45" s="4"/>
     </row>
-    <row r="46" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A46" s="15" t="s">
+    <row r="46" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A46" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B46" s="28">
+      <c r="B46" s="21">
         <v>3</v>
       </c>
-      <c r="C46" s="29">
-        <f>SUM(AH46:AJ46)</f>
+      <c r="C46" s="22">
+        <f>SUM(AI46:AK46)</f>
         <v>75.599999999999994</v>
       </c>
-      <c r="D46" s="18">
+      <c r="D46" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="E46" s="19">
         <v>46097</v>
       </c>
-      <c r="E46" s="18">
+      <c r="F46" s="19">
         <v>46134</v>
       </c>
-      <c r="F46" s="11" t="s">
+      <c r="G46" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G46" s="13"/>
       <c r="H46" s="13"/>
       <c r="I46" s="13"/>
       <c r="J46" s="13"/>
-      <c r="K46" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="L46" s="13"/>
+      <c r="K46" s="13"/>
+      <c r="L46" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="M46" s="13"/>
       <c r="N46" s="13"/>
       <c r="O46" s="13"/>
@@ -4583,11 +4695,9 @@
       <c r="AD46" s="13"/>
       <c r="AE46" s="13"/>
       <c r="AF46" s="13"/>
-      <c r="AG46" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH46" s="7">
-        <v>25.2</v>
+      <c r="AG46" s="13"/>
+      <c r="AH46" s="6" t="s">
+        <v>19</v>
       </c>
       <c r="AI46" s="7">
         <v>25.2</v>
@@ -4595,48 +4705,51 @@
       <c r="AJ46" s="7">
         <v>25.2</v>
       </c>
-      <c r="AK46" s="13"/>
+      <c r="AK46" s="7">
+        <v>25.2</v>
+      </c>
       <c r="AL46" s="13"/>
       <c r="AM46" s="13"/>
       <c r="AN46" s="13"/>
       <c r="AO46" s="13"/>
       <c r="AP46" s="13"/>
-      <c r="AQ46" s="6"/>
+      <c r="AQ46" s="13"/>
       <c r="AR46" s="6"/>
       <c r="AS46" s="6"/>
-      <c r="AT46" s="6" t="s">
-        <v>19</v>
-      </c>
+      <c r="AT46" s="6"/>
       <c r="AU46" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="AV46" s="6"/>
+      <c r="AV46" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="AW46" s="6"/>
-      <c r="AX46" s="13"/>
+      <c r="AX46" s="6"/>
       <c r="AY46" s="13"/>
       <c r="AZ46" s="13"/>
       <c r="BA46" s="13"/>
       <c r="BB46" s="13"/>
       <c r="BC46" s="13"/>
-      <c r="BD46" s="6" t="s">
+      <c r="BD46" s="13"/>
+      <c r="BE46" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A47" s="15"/>
-      <c r="B47" s="28"/>
-      <c r="C47" s="30"/>
-      <c r="D47" s="19"/>
-      <c r="E47" s="19"/>
-      <c r="F47" s="11" t="s">
+    <row r="47" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A47" s="16"/>
+      <c r="B47" s="21"/>
+      <c r="C47" s="23"/>
+      <c r="D47" s="23"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="20"/>
+      <c r="G47" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G47" s="13"/>
       <c r="H47" s="13"/>
       <c r="I47" s="13"/>
       <c r="J47" s="13"/>
-      <c r="K47" s="4"/>
-      <c r="L47" s="13"/>
+      <c r="K47" s="13"/>
+      <c r="L47" s="4"/>
       <c r="M47" s="13"/>
       <c r="N47" s="13"/>
       <c r="O47" s="13"/>
@@ -4657,59 +4770,62 @@
       <c r="AD47" s="13"/>
       <c r="AE47" s="13"/>
       <c r="AF47" s="13"/>
-      <c r="AG47" s="4"/>
-      <c r="AH47" s="6"/>
+      <c r="AG47" s="13"/>
+      <c r="AH47" s="4"/>
       <c r="AI47" s="6"/>
       <c r="AJ47" s="6"/>
-      <c r="AK47" s="13"/>
+      <c r="AK47" s="6"/>
       <c r="AL47" s="13"/>
       <c r="AM47" s="13"/>
       <c r="AN47" s="13"/>
       <c r="AO47" s="13"/>
       <c r="AP47" s="13"/>
-      <c r="AQ47" s="6"/>
+      <c r="AQ47" s="13"/>
       <c r="AR47" s="6"/>
       <c r="AS47" s="6"/>
-      <c r="AT47" s="4"/>
+      <c r="AT47" s="6"/>
       <c r="AU47" s="4"/>
-      <c r="AV47" s="6"/>
+      <c r="AV47" s="4"/>
       <c r="AW47" s="6"/>
-      <c r="AX47" s="13"/>
+      <c r="AX47" s="6"/>
       <c r="AY47" s="13"/>
       <c r="AZ47" s="13"/>
       <c r="BA47" s="13"/>
       <c r="BB47" s="13"/>
       <c r="BC47" s="13"/>
-      <c r="BD47" s="4"/>
+      <c r="BD47" s="13"/>
+      <c r="BE47" s="4"/>
     </row>
-    <row r="48" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A48" s="15" t="s">
+    <row r="48" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A48" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B48" s="28">
+      <c r="B48" s="21">
         <v>3</v>
       </c>
-      <c r="C48" s="29">
-        <f>SUM(AI48:AJ48,AK48)</f>
+      <c r="C48" s="22">
+        <f>SUM(AJ48:AK48,AL48)</f>
         <v>11.399999999999999</v>
       </c>
-      <c r="D48" s="18">
+      <c r="D48" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="E48" s="19">
         <v>46097</v>
       </c>
-      <c r="E48" s="18">
+      <c r="F48" s="19">
         <v>46134</v>
       </c>
-      <c r="F48" s="11" t="s">
+      <c r="G48" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G48" s="13"/>
       <c r="H48" s="13"/>
       <c r="I48" s="13"/>
       <c r="J48" s="13"/>
-      <c r="K48" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="L48" s="13"/>
+      <c r="K48" s="13"/>
+      <c r="L48" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="M48" s="13"/>
       <c r="N48" s="13"/>
       <c r="O48" s="13"/>
@@ -4730,60 +4846,61 @@
       <c r="AD48" s="13"/>
       <c r="AE48" s="13"/>
       <c r="AF48" s="13"/>
-      <c r="AG48" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH48" s="9"/>
-      <c r="AI48" s="7">
-        <v>3.8</v>
-      </c>
+      <c r="AG48" s="13"/>
+      <c r="AH48" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI48" s="9"/>
       <c r="AJ48" s="7">
         <v>3.8</v>
       </c>
       <c r="AK48" s="7">
         <v>3.8</v>
       </c>
-      <c r="AL48" s="6"/>
-      <c r="AM48" s="13"/>
+      <c r="AL48" s="7">
+        <v>3.8</v>
+      </c>
+      <c r="AM48" s="6"/>
       <c r="AN48" s="13"/>
       <c r="AO48" s="13"/>
       <c r="AP48" s="13"/>
-      <c r="AQ48" s="6"/>
+      <c r="AQ48" s="13"/>
       <c r="AR48" s="6"/>
       <c r="AS48" s="6"/>
-      <c r="AT48" s="6" t="s">
-        <v>19</v>
-      </c>
+      <c r="AT48" s="6"/>
       <c r="AU48" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="AV48" s="6"/>
+      <c r="AV48" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="AW48" s="6"/>
-      <c r="AX48" s="13"/>
+      <c r="AX48" s="6"/>
       <c r="AY48" s="13"/>
       <c r="AZ48" s="13"/>
       <c r="BA48" s="13"/>
       <c r="BB48" s="13"/>
       <c r="BC48" s="13"/>
-      <c r="BD48" s="6" t="s">
+      <c r="BD48" s="13"/>
+      <c r="BE48" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="49" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A49" s="15"/>
-      <c r="B49" s="28"/>
-      <c r="C49" s="30"/>
-      <c r="D49" s="19"/>
-      <c r="E49" s="19"/>
-      <c r="F49" s="11" t="s">
+    <row r="49" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A49" s="16"/>
+      <c r="B49" s="21"/>
+      <c r="C49" s="23"/>
+      <c r="D49" s="23"/>
+      <c r="E49" s="20"/>
+      <c r="F49" s="20"/>
+      <c r="G49" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G49" s="13"/>
       <c r="H49" s="13"/>
       <c r="I49" s="13"/>
       <c r="J49" s="13"/>
-      <c r="K49" s="4"/>
-      <c r="L49" s="13"/>
+      <c r="K49" s="13"/>
+      <c r="L49" s="4"/>
       <c r="M49" s="13"/>
       <c r="N49" s="13"/>
       <c r="O49" s="13"/>
@@ -4804,59 +4921,62 @@
       <c r="AD49" s="13"/>
       <c r="AE49" s="13"/>
       <c r="AF49" s="13"/>
-      <c r="AG49" s="4"/>
-      <c r="AH49" s="6"/>
+      <c r="AG49" s="13"/>
+      <c r="AH49" s="4"/>
       <c r="AI49" s="6"/>
       <c r="AJ49" s="6"/>
       <c r="AK49" s="6"/>
       <c r="AL49" s="6"/>
-      <c r="AM49" s="13"/>
+      <c r="AM49" s="6"/>
       <c r="AN49" s="13"/>
       <c r="AO49" s="13"/>
       <c r="AP49" s="13"/>
-      <c r="AQ49" s="6"/>
+      <c r="AQ49" s="13"/>
       <c r="AR49" s="6"/>
       <c r="AS49" s="6"/>
-      <c r="AT49" s="4"/>
+      <c r="AT49" s="6"/>
       <c r="AU49" s="4"/>
-      <c r="AV49" s="6"/>
+      <c r="AV49" s="4"/>
       <c r="AW49" s="6"/>
-      <c r="AX49" s="13"/>
+      <c r="AX49" s="6"/>
       <c r="AY49" s="13"/>
       <c r="AZ49" s="13"/>
       <c r="BA49" s="13"/>
       <c r="BB49" s="13"/>
       <c r="BC49" s="13"/>
-      <c r="BD49" s="4"/>
+      <c r="BD49" s="13"/>
+      <c r="BE49" s="4"/>
     </row>
-    <row r="50" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A50" s="15" t="s">
+    <row r="50" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A50" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B50" s="28">
+      <c r="B50" s="21">
         <v>3</v>
       </c>
-      <c r="C50" s="29">
-        <f>SUM(AJ50:AM50)</f>
+      <c r="C50" s="22">
+        <f>SUM(AK50:AN50)</f>
         <v>63</v>
       </c>
-      <c r="D50" s="18">
+      <c r="D50" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="E50" s="19">
         <v>46097</v>
       </c>
-      <c r="E50" s="18">
+      <c r="F50" s="19">
         <v>46134</v>
       </c>
-      <c r="F50" s="11" t="s">
+      <c r="G50" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G50" s="13"/>
       <c r="H50" s="13"/>
       <c r="I50" s="13"/>
       <c r="J50" s="13"/>
-      <c r="K50" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="L50" s="13"/>
+      <c r="K50" s="13"/>
+      <c r="L50" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="M50" s="13"/>
       <c r="N50" s="13"/>
       <c r="O50" s="13"/>
@@ -4877,14 +4997,12 @@
       <c r="AD50" s="13"/>
       <c r="AE50" s="13"/>
       <c r="AF50" s="13"/>
-      <c r="AG50" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH50" s="6"/>
+      <c r="AG50" s="13"/>
+      <c r="AH50" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="AI50" s="6"/>
-      <c r="AJ50" s="10">
-        <v>15.75</v>
-      </c>
+      <c r="AJ50" s="6"/>
       <c r="AK50" s="10">
         <v>15.75</v>
       </c>
@@ -4894,45 +5012,48 @@
       <c r="AM50" s="10">
         <v>15.75</v>
       </c>
-      <c r="AN50" s="13"/>
+      <c r="AN50" s="10">
+        <v>15.75</v>
+      </c>
       <c r="AO50" s="13"/>
       <c r="AP50" s="13"/>
-      <c r="AQ50" s="6"/>
+      <c r="AQ50" s="13"/>
       <c r="AR50" s="6"/>
       <c r="AS50" s="6"/>
-      <c r="AT50" s="6" t="s">
-        <v>19</v>
-      </c>
+      <c r="AT50" s="6"/>
       <c r="AU50" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="AV50" s="6"/>
+      <c r="AV50" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="AW50" s="6"/>
-      <c r="AX50" s="13"/>
+      <c r="AX50" s="6"/>
       <c r="AY50" s="13"/>
       <c r="AZ50" s="13"/>
       <c r="BA50" s="13"/>
       <c r="BB50" s="13"/>
       <c r="BC50" s="13"/>
-      <c r="BD50" s="6" t="s">
+      <c r="BD50" s="13"/>
+      <c r="BE50" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="51" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A51" s="15"/>
-      <c r="B51" s="28"/>
-      <c r="C51" s="30"/>
-      <c r="D51" s="19"/>
-      <c r="E51" s="19"/>
-      <c r="F51" s="11" t="s">
+    <row r="51" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A51" s="16"/>
+      <c r="B51" s="21"/>
+      <c r="C51" s="23"/>
+      <c r="D51" s="23"/>
+      <c r="E51" s="20"/>
+      <c r="F51" s="20"/>
+      <c r="G51" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G51" s="13"/>
       <c r="H51" s="13"/>
       <c r="I51" s="13"/>
       <c r="J51" s="13"/>
-      <c r="K51" s="4"/>
-      <c r="L51" s="13"/>
+      <c r="K51" s="13"/>
+      <c r="L51" s="4"/>
       <c r="M51" s="13"/>
       <c r="N51" s="13"/>
       <c r="O51" s="13"/>
@@ -4953,59 +5074,62 @@
       <c r="AD51" s="13"/>
       <c r="AE51" s="13"/>
       <c r="AF51" s="13"/>
-      <c r="AG51" s="4"/>
-      <c r="AH51" s="13"/>
+      <c r="AG51" s="13"/>
+      <c r="AH51" s="4"/>
       <c r="AI51" s="13"/>
       <c r="AJ51" s="13"/>
-      <c r="AK51" s="6"/>
+      <c r="AK51" s="13"/>
       <c r="AL51" s="6"/>
-      <c r="AM51" s="13"/>
+      <c r="AM51" s="6"/>
       <c r="AN51" s="13"/>
       <c r="AO51" s="13"/>
       <c r="AP51" s="13"/>
       <c r="AQ51" s="13"/>
       <c r="AR51" s="13"/>
       <c r="AS51" s="13"/>
-      <c r="AT51" s="4"/>
+      <c r="AT51" s="13"/>
       <c r="AU51" s="4"/>
-      <c r="AV51" s="6"/>
+      <c r="AV51" s="4"/>
       <c r="AW51" s="6"/>
-      <c r="AX51" s="13"/>
+      <c r="AX51" s="6"/>
       <c r="AY51" s="13"/>
       <c r="AZ51" s="13"/>
       <c r="BA51" s="13"/>
       <c r="BB51" s="13"/>
       <c r="BC51" s="13"/>
-      <c r="BD51" s="4"/>
+      <c r="BD51" s="13"/>
+      <c r="BE51" s="4"/>
     </row>
-    <row r="52" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A52" s="15" t="s">
+    <row r="52" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A52" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B52" s="28">
+      <c r="B52" s="21">
         <v>3</v>
       </c>
-      <c r="C52" s="29">
-        <f>SUM(AM52)</f>
+      <c r="C52" s="22">
+        <f>SUM(AN52)</f>
         <v>1</v>
       </c>
-      <c r="D52" s="18">
+      <c r="D52" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="E52" s="19">
         <v>46097</v>
       </c>
-      <c r="E52" s="18">
+      <c r="F52" s="19">
         <v>46134</v>
       </c>
-      <c r="F52" s="11" t="s">
+      <c r="G52" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G52" s="13"/>
       <c r="H52" s="13"/>
       <c r="I52" s="13"/>
       <c r="J52" s="13"/>
-      <c r="K52" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="L52" s="13"/>
+      <c r="K52" s="13"/>
+      <c r="L52" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="M52" s="13"/>
       <c r="N52" s="13"/>
       <c r="O52" s="13"/>
@@ -5026,56 +5150,57 @@
       <c r="AD52" s="13"/>
       <c r="AE52" s="13"/>
       <c r="AF52" s="13"/>
-      <c r="AG52" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH52" s="13"/>
+      <c r="AG52" s="13"/>
+      <c r="AH52" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="AI52" s="13"/>
       <c r="AJ52" s="13"/>
       <c r="AK52" s="13"/>
       <c r="AL52" s="13"/>
-      <c r="AM52" s="10">
+      <c r="AM52" s="13"/>
+      <c r="AN52" s="10">
         <v>1</v>
       </c>
-      <c r="AN52" s="13"/>
       <c r="AO52" s="13"/>
       <c r="AP52" s="13"/>
       <c r="AQ52" s="13"/>
       <c r="AR52" s="13"/>
       <c r="AS52" s="13"/>
-      <c r="AT52" s="6" t="s">
-        <v>19</v>
-      </c>
+      <c r="AT52" s="13"/>
       <c r="AU52" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="AV52" s="6"/>
+      <c r="AV52" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="AW52" s="6"/>
-      <c r="AX52" s="13"/>
+      <c r="AX52" s="6"/>
       <c r="AY52" s="13"/>
       <c r="AZ52" s="13"/>
       <c r="BA52" s="13"/>
       <c r="BB52" s="13"/>
       <c r="BC52" s="13"/>
-      <c r="BD52" s="6" t="s">
+      <c r="BD52" s="13"/>
+      <c r="BE52" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="53" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A53" s="15"/>
-      <c r="B53" s="28"/>
-      <c r="C53" s="30"/>
-      <c r="D53" s="19"/>
-      <c r="E53" s="19"/>
-      <c r="F53" s="11" t="s">
+    <row r="53" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A53" s="16"/>
+      <c r="B53" s="21"/>
+      <c r="C53" s="23"/>
+      <c r="D53" s="23"/>
+      <c r="E53" s="20"/>
+      <c r="F53" s="20"/>
+      <c r="G53" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G53" s="13"/>
       <c r="H53" s="13"/>
       <c r="I53" s="13"/>
       <c r="J53" s="13"/>
-      <c r="K53" s="4"/>
-      <c r="L53" s="13"/>
+      <c r="K53" s="13"/>
+      <c r="L53" s="4"/>
       <c r="M53" s="13"/>
       <c r="N53" s="13"/>
       <c r="O53" s="13"/>
@@ -5096,59 +5221,62 @@
       <c r="AD53" s="13"/>
       <c r="AE53" s="13"/>
       <c r="AF53" s="13"/>
-      <c r="AG53" s="4"/>
-      <c r="AH53" s="13"/>
+      <c r="AG53" s="13"/>
+      <c r="AH53" s="4"/>
       <c r="AI53" s="13"/>
       <c r="AJ53" s="13"/>
-      <c r="AK53" s="6"/>
+      <c r="AK53" s="13"/>
       <c r="AL53" s="6"/>
-      <c r="AM53" s="13"/>
+      <c r="AM53" s="6"/>
       <c r="AN53" s="13"/>
       <c r="AO53" s="13"/>
       <c r="AP53" s="13"/>
       <c r="AQ53" s="13"/>
       <c r="AR53" s="13"/>
       <c r="AS53" s="13"/>
-      <c r="AT53" s="4"/>
+      <c r="AT53" s="13"/>
       <c r="AU53" s="4"/>
-      <c r="AV53" s="6"/>
+      <c r="AV53" s="4"/>
       <c r="AW53" s="6"/>
-      <c r="AX53" s="13"/>
+      <c r="AX53" s="6"/>
       <c r="AY53" s="13"/>
       <c r="AZ53" s="13"/>
       <c r="BA53" s="13"/>
       <c r="BB53" s="13"/>
       <c r="BC53" s="13"/>
-      <c r="BD53" s="4"/>
+      <c r="BD53" s="13"/>
+      <c r="BE53" s="4"/>
     </row>
-    <row r="54" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A54" s="15" t="s">
+    <row r="54" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A54" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B54" s="28">
+      <c r="B54" s="21">
         <v>3</v>
       </c>
-      <c r="C54" s="29">
-        <f>SUM(AK54:AN54)</f>
+      <c r="C54" s="22">
+        <f>SUM(AL54:AO54)</f>
         <v>55</v>
       </c>
-      <c r="D54" s="18">
+      <c r="D54" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="E54" s="19">
         <v>46097</v>
       </c>
-      <c r="E54" s="18">
+      <c r="F54" s="19">
         <v>46134</v>
       </c>
-      <c r="F54" s="11" t="s">
+      <c r="G54" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G54" s="13"/>
       <c r="H54" s="13"/>
       <c r="I54" s="13"/>
       <c r="J54" s="13"/>
-      <c r="K54" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="L54" s="13"/>
+      <c r="K54" s="13"/>
+      <c r="L54" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="M54" s="13"/>
       <c r="N54" s="13"/>
       <c r="O54" s="13"/>
@@ -5169,60 +5297,61 @@
       <c r="AD54" s="13"/>
       <c r="AE54" s="13"/>
       <c r="AF54" s="13"/>
-      <c r="AG54" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH54" s="13"/>
+      <c r="AG54" s="13"/>
+      <c r="AH54" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="AI54" s="13"/>
       <c r="AJ54" s="13"/>
-      <c r="AK54" s="10">
-        <v>18.399999999999999</v>
-      </c>
+      <c r="AK54" s="13"/>
       <c r="AL54" s="10">
         <v>18.399999999999999</v>
       </c>
       <c r="AM54" s="10">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="AN54" s="10">
         <v>18.2</v>
       </c>
-      <c r="AN54" s="13"/>
       <c r="AO54" s="13"/>
       <c r="AP54" s="13"/>
       <c r="AQ54" s="13"/>
       <c r="AR54" s="13"/>
       <c r="AS54" s="13"/>
-      <c r="AT54" s="6" t="s">
-        <v>19</v>
-      </c>
+      <c r="AT54" s="13"/>
       <c r="AU54" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="AV54" s="6"/>
+      <c r="AV54" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="AW54" s="6"/>
-      <c r="AX54" s="13"/>
+      <c r="AX54" s="6"/>
       <c r="AY54" s="13"/>
       <c r="AZ54" s="13"/>
       <c r="BA54" s="13"/>
       <c r="BB54" s="13"/>
       <c r="BC54" s="13"/>
-      <c r="BD54" s="6" t="s">
+      <c r="BD54" s="13"/>
+      <c r="BE54" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="55" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A55" s="15"/>
-      <c r="B55" s="28"/>
-      <c r="C55" s="30"/>
-      <c r="D55" s="19"/>
-      <c r="E55" s="19"/>
-      <c r="F55" s="11" t="s">
+    <row r="55" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A55" s="16"/>
+      <c r="B55" s="21"/>
+      <c r="C55" s="23"/>
+      <c r="D55" s="23"/>
+      <c r="E55" s="20"/>
+      <c r="F55" s="20"/>
+      <c r="G55" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G55" s="13"/>
       <c r="H55" s="13"/>
       <c r="I55" s="13"/>
       <c r="J55" s="13"/>
-      <c r="K55" s="4"/>
-      <c r="L55" s="13"/>
+      <c r="K55" s="13"/>
+      <c r="L55" s="4"/>
       <c r="M55" s="13"/>
       <c r="N55" s="13"/>
       <c r="O55" s="13"/>
@@ -5243,59 +5372,62 @@
       <c r="AD55" s="13"/>
       <c r="AE55" s="13"/>
       <c r="AF55" s="13"/>
-      <c r="AG55" s="4"/>
-      <c r="AH55" s="13"/>
+      <c r="AG55" s="13"/>
+      <c r="AH55" s="4"/>
       <c r="AI55" s="13"/>
       <c r="AJ55" s="13"/>
-      <c r="AK55" s="6"/>
+      <c r="AK55" s="13"/>
       <c r="AL55" s="6"/>
-      <c r="AM55" s="13"/>
+      <c r="AM55" s="6"/>
       <c r="AN55" s="13"/>
       <c r="AO55" s="13"/>
       <c r="AP55" s="13"/>
       <c r="AQ55" s="13"/>
       <c r="AR55" s="13"/>
       <c r="AS55" s="13"/>
-      <c r="AT55" s="4"/>
+      <c r="AT55" s="13"/>
       <c r="AU55" s="4"/>
-      <c r="AV55" s="6"/>
+      <c r="AV55" s="4"/>
       <c r="AW55" s="6"/>
-      <c r="AX55" s="13"/>
+      <c r="AX55" s="6"/>
       <c r="AY55" s="13"/>
       <c r="AZ55" s="13"/>
       <c r="BA55" s="13"/>
       <c r="BB55" s="13"/>
       <c r="BC55" s="13"/>
-      <c r="BD55" s="4"/>
+      <c r="BD55" s="13"/>
+      <c r="BE55" s="4"/>
     </row>
-    <row r="56" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A56" s="15" t="s">
+    <row r="56" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A56" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="B56" s="28">
+      <c r="B56" s="21">
         <v>3</v>
       </c>
-      <c r="C56" s="29">
-        <f>SUM(AM56:AO56)</f>
+      <c r="C56" s="22">
+        <f>SUM(AN56:AP56)</f>
         <v>126</v>
       </c>
-      <c r="D56" s="18">
+      <c r="D56" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="E56" s="19">
         <v>46097</v>
       </c>
-      <c r="E56" s="18">
+      <c r="F56" s="19">
         <v>46134</v>
       </c>
-      <c r="F56" s="11" t="s">
+      <c r="G56" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G56" s="13"/>
       <c r="H56" s="13"/>
       <c r="I56" s="13"/>
       <c r="J56" s="13"/>
-      <c r="K56" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="L56" s="13"/>
+      <c r="K56" s="13"/>
+      <c r="L56" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="M56" s="13"/>
       <c r="N56" s="13"/>
       <c r="O56" s="13"/>
@@ -5316,60 +5448,61 @@
       <c r="AD56" s="13"/>
       <c r="AE56" s="13"/>
       <c r="AF56" s="13"/>
-      <c r="AG56" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH56" s="13"/>
+      <c r="AG56" s="13"/>
+      <c r="AH56" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="AI56" s="13"/>
       <c r="AJ56" s="13"/>
-      <c r="AK56" s="6"/>
+      <c r="AK56" s="13"/>
       <c r="AL56" s="6"/>
-      <c r="AM56" s="10">
-        <v>42</v>
-      </c>
+      <c r="AM56" s="6"/>
       <c r="AN56" s="10">
         <v>42</v>
       </c>
       <c r="AO56" s="10">
         <v>42</v>
       </c>
-      <c r="AP56" s="13"/>
+      <c r="AP56" s="10">
+        <v>42</v>
+      </c>
       <c r="AQ56" s="13"/>
       <c r="AR56" s="13"/>
       <c r="AS56" s="13"/>
-      <c r="AT56" s="6" t="s">
-        <v>19</v>
-      </c>
+      <c r="AT56" s="13"/>
       <c r="AU56" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="AV56" s="6"/>
+      <c r="AV56" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="AW56" s="6"/>
-      <c r="AX56" s="13"/>
+      <c r="AX56" s="6"/>
       <c r="AY56" s="13"/>
       <c r="AZ56" s="13"/>
       <c r="BA56" s="13"/>
       <c r="BB56" s="13"/>
       <c r="BC56" s="13"/>
-      <c r="BD56" s="6" t="s">
+      <c r="BD56" s="13"/>
+      <c r="BE56" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="57" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A57" s="15"/>
-      <c r="B57" s="28"/>
-      <c r="C57" s="30"/>
-      <c r="D57" s="19"/>
-      <c r="E57" s="19"/>
-      <c r="F57" s="11" t="s">
+    <row r="57" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A57" s="16"/>
+      <c r="B57" s="21"/>
+      <c r="C57" s="23"/>
+      <c r="D57" s="23"/>
+      <c r="E57" s="20"/>
+      <c r="F57" s="20"/>
+      <c r="G57" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G57" s="13"/>
       <c r="H57" s="13"/>
       <c r="I57" s="13"/>
       <c r="J57" s="13"/>
-      <c r="K57" s="4"/>
-      <c r="L57" s="13"/>
+      <c r="K57" s="13"/>
+      <c r="L57" s="4"/>
       <c r="M57" s="13"/>
       <c r="N57" s="13"/>
       <c r="O57" s="13"/>
@@ -5390,8 +5523,8 @@
       <c r="AD57" s="13"/>
       <c r="AE57" s="13"/>
       <c r="AF57" s="13"/>
-      <c r="AG57" s="4"/>
-      <c r="AH57" s="13"/>
+      <c r="AG57" s="13"/>
+      <c r="AH57" s="4"/>
       <c r="AI57" s="13"/>
       <c r="AJ57" s="13"/>
       <c r="AK57" s="13"/>
@@ -5400,49 +5533,52 @@
       <c r="AN57" s="13"/>
       <c r="AO57" s="13"/>
       <c r="AP57" s="13"/>
-      <c r="AQ57" s="6"/>
+      <c r="AQ57" s="13"/>
       <c r="AR57" s="6"/>
       <c r="AS57" s="6"/>
-      <c r="AT57" s="4"/>
+      <c r="AT57" s="6"/>
       <c r="AU57" s="4"/>
-      <c r="AV57" s="6"/>
+      <c r="AV57" s="4"/>
       <c r="AW57" s="6"/>
-      <c r="AX57" s="13"/>
+      <c r="AX57" s="6"/>
       <c r="AY57" s="13"/>
       <c r="AZ57" s="13"/>
       <c r="BA57" s="13"/>
       <c r="BB57" s="13"/>
       <c r="BC57" s="13"/>
-      <c r="BD57" s="4"/>
+      <c r="BD57" s="13"/>
+      <c r="BE57" s="4"/>
     </row>
-    <row r="58" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A58" s="15" t="s">
+    <row r="58" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A58" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B58" s="28">
+      <c r="B58" s="21">
         <v>3</v>
       </c>
-      <c r="C58" s="29">
-        <f>SUM(AS58)</f>
+      <c r="C58" s="22">
+        <f>SUM(AT58)</f>
         <v>126</v>
       </c>
-      <c r="D58" s="18">
+      <c r="D58" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="E58" s="19">
         <v>46097</v>
       </c>
-      <c r="E58" s="18">
+      <c r="F58" s="19">
         <v>46134</v>
       </c>
-      <c r="F58" s="11" t="s">
+      <c r="G58" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G58" s="13"/>
       <c r="H58" s="13"/>
       <c r="I58" s="13"/>
       <c r="J58" s="13"/>
-      <c r="K58" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="L58" s="13"/>
+      <c r="K58" s="13"/>
+      <c r="L58" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="M58" s="13"/>
       <c r="N58" s="13"/>
       <c r="O58" s="13"/>
@@ -5463,55 +5599,56 @@
       <c r="AD58" s="13"/>
       <c r="AE58" s="13"/>
       <c r="AF58" s="13"/>
-      <c r="AG58" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH58" s="13"/>
+      <c r="AG58" s="13"/>
+      <c r="AH58" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="AI58" s="13"/>
       <c r="AJ58" s="13"/>
       <c r="AK58" s="13"/>
       <c r="AL58" s="13"/>
       <c r="AM58" s="13"/>
       <c r="AN58" s="13"/>
-      <c r="AO58" s="6"/>
-      <c r="AQ58" s="13"/>
+      <c r="AO58" s="13"/>
+      <c r="AP58" s="6"/>
       <c r="AR58" s="13"/>
-      <c r="AS58" s="10">
+      <c r="AS58" s="13"/>
+      <c r="AT58" s="10">
         <v>126</v>
       </c>
-      <c r="AT58" s="6" t="s">
-        <v>19</v>
-      </c>
       <c r="AU58" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="AV58" s="6"/>
+      <c r="AV58" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="AW58" s="6"/>
-      <c r="AX58" s="13"/>
+      <c r="AX58" s="6"/>
       <c r="AY58" s="13"/>
       <c r="AZ58" s="13"/>
       <c r="BA58" s="13"/>
       <c r="BB58" s="13"/>
       <c r="BC58" s="13"/>
-      <c r="BD58" s="6" t="s">
+      <c r="BD58" s="13"/>
+      <c r="BE58" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="59" spans="1:56" x14ac:dyDescent="0.3">
-      <c r="A59" s="15"/>
-      <c r="B59" s="28"/>
-      <c r="C59" s="30"/>
-      <c r="D59" s="19"/>
-      <c r="E59" s="19"/>
-      <c r="F59" s="11" t="s">
+    <row r="59" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A59" s="16"/>
+      <c r="B59" s="21"/>
+      <c r="C59" s="23"/>
+      <c r="D59" s="23"/>
+      <c r="E59" s="20"/>
+      <c r="F59" s="20"/>
+      <c r="G59" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G59" s="13"/>
       <c r="H59" s="13"/>
       <c r="I59" s="13"/>
       <c r="J59" s="13"/>
-      <c r="K59" s="4"/>
-      <c r="L59" s="13"/>
+      <c r="K59" s="13"/>
+      <c r="L59" s="4"/>
       <c r="M59" s="13"/>
       <c r="N59" s="13"/>
       <c r="O59" s="13"/>
@@ -5532,8 +5669,8 @@
       <c r="AD59" s="13"/>
       <c r="AE59" s="13"/>
       <c r="AF59" s="13"/>
-      <c r="AG59" s="4"/>
-      <c r="AH59" s="13"/>
+      <c r="AG59" s="13"/>
+      <c r="AH59" s="4"/>
       <c r="AI59" s="13"/>
       <c r="AJ59" s="13"/>
       <c r="AK59" s="13"/>
@@ -5545,175 +5682,204 @@
       <c r="AQ59" s="13"/>
       <c r="AR59" s="13"/>
       <c r="AS59" s="13"/>
-      <c r="AT59" s="4"/>
+      <c r="AT59" s="13"/>
       <c r="AU59" s="4"/>
-      <c r="AV59" s="6"/>
-      <c r="AW59" s="13"/>
+      <c r="AV59" s="4"/>
+      <c r="AW59" s="6"/>
       <c r="AX59" s="13"/>
       <c r="AY59" s="13"/>
       <c r="AZ59" s="13"/>
       <c r="BA59" s="13"/>
       <c r="BB59" s="13"/>
       <c r="BC59" s="13"/>
-      <c r="BD59" s="4"/>
+      <c r="BD59" s="13"/>
+      <c r="BE59" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="155">
+  <mergeCells count="183">
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="D56:D57"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="AO2:AT2"/>
+    <mergeCell ref="AU2:AZ2"/>
+    <mergeCell ref="BA2:BE2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="M2:Q2"/>
+    <mergeCell ref="R2:W2"/>
+    <mergeCell ref="X2:AC2"/>
+    <mergeCell ref="AD2:AH2"/>
+    <mergeCell ref="AI2:AN2"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="F44:F45"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="E46:E47"/>
+    <mergeCell ref="F46:F47"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="E52:E53"/>
+    <mergeCell ref="F52:F53"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="E54:E55"/>
+    <mergeCell ref="F54:F55"/>
     <mergeCell ref="A22:A23"/>
     <mergeCell ref="B22:B23"/>
     <mergeCell ref="C22:C23"/>
-    <mergeCell ref="D22:D23"/>
     <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
     <mergeCell ref="A56:A57"/>
     <mergeCell ref="B56:B57"/>
     <mergeCell ref="C56:C57"/>
-    <mergeCell ref="D56:D57"/>
     <mergeCell ref="E56:E57"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="E58:E59"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="D52:D53"/>
-    <mergeCell ref="E52:E53"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="E54:E55"/>
+    <mergeCell ref="F56:F57"/>
     <mergeCell ref="A50:A51"/>
     <mergeCell ref="B50:B51"/>
     <mergeCell ref="C50:C51"/>
-    <mergeCell ref="D50:D51"/>
     <mergeCell ref="E50:E51"/>
+    <mergeCell ref="F50:F51"/>
     <mergeCell ref="A48:A49"/>
     <mergeCell ref="B48:B49"/>
     <mergeCell ref="C48:C49"/>
-    <mergeCell ref="D48:D49"/>
     <mergeCell ref="E48:E49"/>
+    <mergeCell ref="F48:F49"/>
     <mergeCell ref="A44:A45"/>
     <mergeCell ref="B44:B45"/>
     <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
     <mergeCell ref="E44:E45"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="E46:E47"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="AN2:AS2"/>
-    <mergeCell ref="AT2:AY2"/>
-    <mergeCell ref="AZ2:BD2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="G2:K2"/>
-    <mergeCell ref="L2:P2"/>
-    <mergeCell ref="Q2:V2"/>
-    <mergeCell ref="W2:AB2"/>
-    <mergeCell ref="AC2:AG2"/>
-    <mergeCell ref="AH2:AM2"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
